--- a/TSLA.xlsx
+++ b/TSLA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B098BD1-193B-4777-B6F2-5CC6085B23EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BBF530E-7689-4017-AA09-39AAEEA2B7DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -618,13 +618,19 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -761,92 +767,95 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="4" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -924,15 +933,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>34</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>29766</xdr:rowOff>
+      <xdr:colOff>547688</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>113110</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>17860</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>53578</xdr:rowOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>5954</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>136923</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -947,7 +956,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="21347906" y="190500"/>
+          <a:off x="21895594" y="113110"/>
           <a:ext cx="17860" cy="12078891"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1305,7 +1314,7 @@
         <v>0</v>
       </c>
       <c r="K2" s="41">
-        <v>419.17</v>
+        <v>373.72</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
@@ -1313,10 +1322,10 @@
         <v>1</v>
       </c>
       <c r="K3" s="4">
-        <v>3225</v>
-      </c>
-      <c r="L3" s="44" t="s">
-        <v>121</v>
+        <v>3755.7238710000001</v>
+      </c>
+      <c r="L3" s="47" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
@@ -1331,7 +1340,7 @@
       </c>
       <c r="K4" s="10">
         <f>K2*K3</f>
-        <v>1351823.25</v>
+        <v>1403589.1250701202</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
@@ -1342,11 +1351,11 @@
         <v>3</v>
       </c>
       <c r="K5" s="10">
-        <f>18289+23358</f>
-        <v>41647</v>
-      </c>
-      <c r="L5" s="44" t="s">
-        <v>121</v>
+        <f>16603+28140</f>
+        <v>44743</v>
+      </c>
+      <c r="L5" s="47" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
@@ -1357,11 +1366,11 @@
         <v>4</v>
       </c>
       <c r="K6" s="17">
-        <f>1924+5778</f>
-        <v>7702</v>
-      </c>
-      <c r="L6" s="44" t="s">
-        <v>121</v>
+        <f>1447+7782</f>
+        <v>9229</v>
+      </c>
+      <c r="L6" s="47" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
@@ -1370,7 +1379,7 @@
       </c>
       <c r="K7" s="10">
         <f>K4-K5+K6</f>
-        <v>1317878.25</v>
+        <v>1368075.1250701202</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
@@ -2870,7 +2879,9 @@
       <c r="AH35" s="5">
         <v>11642</v>
       </c>
-      <c r="AI35" s="5"/>
+      <c r="AI35" s="5">
+        <v>16130</v>
+      </c>
       <c r="AJ35" s="5"/>
       <c r="AK35" s="5"/>
       <c r="AL35" s="5"/>
@@ -3008,7 +3019,9 @@
       <c r="AH36" s="5">
         <v>406585</v>
       </c>
-      <c r="AI36" s="5"/>
+      <c r="AI36" s="5">
+        <v>341893</v>
+      </c>
       <c r="AJ36" s="5"/>
       <c r="AK36" s="5"/>
       <c r="AL36" s="5"/>
@@ -3172,7 +3185,9 @@
         <f t="shared" si="12"/>
         <v>418227</v>
       </c>
-      <c r="AI37" s="7"/>
+      <c r="AI37" s="7">
+        <v>358023</v>
+      </c>
       <c r="AJ37" s="7"/>
       <c r="AK37" s="7"/>
       <c r="AL37" s="7"/>
@@ -3197,51 +3212,51 @@
         <v>1808581</v>
       </c>
       <c r="AY37" s="6">
-        <f>+AY35+AY36</f>
+        <f t="shared" ref="AY37:BD37" si="14">+AY35+AY36</f>
         <v>1848441.7</v>
       </c>
       <c r="AZ37" s="6">
-        <f>+AZ35+AZ36</f>
+        <f t="shared" si="14"/>
         <v>1636129</v>
       </c>
       <c r="BA37" s="6">
-        <f>+BA35+BA36</f>
+        <f t="shared" si="14"/>
         <v>1750243</v>
       </c>
       <c r="BB37" s="6">
-        <f>+BB35+BB36</f>
+        <f t="shared" si="14"/>
         <v>2010459</v>
       </c>
       <c r="BC37" s="6">
-        <f>+BC35+BC36</f>
+        <f t="shared" si="14"/>
         <v>2350452</v>
       </c>
       <c r="BD37" s="6">
-        <f>+BD35+BD36</f>
+        <f t="shared" si="14"/>
         <v>3019901</v>
       </c>
       <c r="BE37" s="6">
-        <f t="shared" ref="BE37" si="14">BE42</f>
+        <f t="shared" ref="BE37" si="15">BE42</f>
         <v>3767676.7590000001</v>
       </c>
       <c r="BF37" s="6">
-        <f t="shared" ref="BF37:BJ37" si="15">BF42</f>
+        <f t="shared" ref="BF37:BJ37" si="16">BF42</f>
         <v>3956060.5969500002</v>
       </c>
       <c r="BG37" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>4153863.6267975005</v>
       </c>
       <c r="BH37" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>4361556.8081373759</v>
       </c>
       <c r="BI37" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>4579634.6485442445</v>
       </c>
       <c r="BJ37" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>4808616.3809714569</v>
       </c>
     </row>
@@ -3254,91 +3269,91 @@
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
       <c r="G38" s="5">
-        <f t="shared" ref="G38:AB38" si="16">G45*1000000/G37</f>
+        <f t="shared" ref="G38:AB38" si="17">G45*1000000/G37</f>
         <v>55681.619828940478</v>
       </c>
       <c r="H38" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>54196.904232560089</v>
       </c>
       <c r="I38" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>52805.95970613051</v>
       </c>
       <c r="J38" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>54801.730674873994</v>
       </c>
       <c r="K38" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>55290.634604953899</v>
       </c>
       <c r="L38" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>54175.399889685606</v>
       </c>
       <c r="M38" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>52735.10409188801</v>
       </c>
       <c r="N38" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>47809.713684443705</v>
       </c>
       <c r="O38" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>44301.948051948049</v>
       </c>
       <c r="P38" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>47304.34782608696</v>
       </c>
       <c r="Q38" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>47215.084956485705</v>
       </c>
       <c r="R38" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>48687.621516526247</v>
       </c>
       <c r="S38" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>50037.413561771078</v>
       </c>
       <c r="T38" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>53672.039105596894</v>
       </c>
       <c r="U38" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>51726.143733821948</v>
       </c>
       <c r="V38" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>51902.644604444358</v>
       </c>
       <c r="W38" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>44642.033697901272</v>
       </c>
       <c r="X38" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>43804.436435405674</v>
       </c>
       <c r="Y38" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>42711.448332295156</v>
       </c>
       <c r="Z38" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>42579.364178432923</v>
       </c>
       <c r="AA38" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>42553.191489361699</v>
       </c>
       <c r="AB38" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>41738.370469145593</v>
       </c>
       <c r="AC38" s="5">
@@ -3365,32 +3380,35 @@
         <f>+AD38*1.05</f>
         <v>46943.749006722304</v>
       </c>
-      <c r="AI38" s="5"/>
+      <c r="AI38" s="5">
+        <f>+AE38*1.05</f>
+        <v>46914.893617021276</v>
+      </c>
       <c r="AJ38" s="5"/>
       <c r="AK38" s="5"/>
       <c r="AL38" s="5"/>
       <c r="AT38" s="5">
-        <f t="shared" ref="AT38:AY38" si="17">AT45/AT37*1000000</f>
+        <f t="shared" ref="AT38:AY38" si="18">AT45/AT37*1000000</f>
         <v>54268.120199316756</v>
       </c>
       <c r="AU38" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>51667.681998172404</v>
       </c>
       <c r="AV38" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>47144.612425877451</v>
       </c>
       <c r="AW38" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>51759.293862089384</v>
       </c>
       <c r="AX38" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>43409.169951470241</v>
       </c>
       <c r="AY38" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>39211.407100370008</v>
       </c>
       <c r="AZ38" s="4">
@@ -3410,31 +3428,31 @@
         <v>44132.784143962999</v>
       </c>
       <c r="BD38" s="4">
-        <f t="shared" ref="BD38:BE38" si="18">BC38*1.03</f>
+        <f t="shared" ref="BD38:BE38" si="19">BC38*1.03</f>
         <v>45456.767668281893</v>
       </c>
       <c r="BE38" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>46820.470698330348</v>
       </c>
       <c r="BF38" s="4">
-        <f t="shared" ref="BF38" si="19">BE38*1.03</f>
+        <f t="shared" ref="BF38" si="20">BE38*1.03</f>
         <v>48225.084819280259</v>
       </c>
       <c r="BG38" s="4">
-        <f t="shared" ref="BG38" si="20">BF38*1.03</f>
+        <f t="shared" ref="BG38" si="21">BF38*1.03</f>
         <v>49671.837363858671</v>
       </c>
       <c r="BH38" s="4">
-        <f t="shared" ref="BH38" si="21">BG38*1.03</f>
+        <f t="shared" ref="BH38" si="22">BG38*1.03</f>
         <v>51161.992484774433</v>
       </c>
       <c r="BI38" s="4">
-        <f t="shared" ref="BI38" si="22">BH38*1.03</f>
+        <f t="shared" ref="BI38" si="23">BH38*1.03</f>
         <v>52696.852259317668</v>
       </c>
       <c r="BJ38" s="4">
-        <f t="shared" ref="BJ38" si="23">BI38*1.03</f>
+        <f t="shared" ref="BJ38" si="24">BI38*1.03</f>
         <v>54277.757827097201</v>
       </c>
     </row>
@@ -3570,7 +3588,9 @@
       <c r="AH40" s="5">
         <v>11706</v>
       </c>
-      <c r="AI40" s="5"/>
+      <c r="AI40" s="5">
+        <v>13775</v>
+      </c>
       <c r="AJ40" s="5"/>
       <c r="AK40" s="5"/>
       <c r="AL40" s="5"/>
@@ -3591,11 +3611,11 @@
         <v>71177</v>
       </c>
       <c r="AX40" s="4">
-        <f t="shared" ref="AX40:AX41" si="24">SUM(W40:Z40)</f>
+        <f t="shared" ref="AX40:AX41" si="25">SUM(W40:Z40)</f>
         <v>70826</v>
       </c>
       <c r="AY40" s="4">
-        <f t="shared" ref="AY40:AY41" si="25">SUM(AA40:AD40)</f>
+        <f t="shared" ref="AY40:AY41" si="26">SUM(AA40:AD40)</f>
         <v>89172.3</v>
       </c>
       <c r="AZ40" s="4">
@@ -3696,7 +3716,9 @@
       <c r="AH41" s="5">
         <v>422652</v>
       </c>
-      <c r="AI41" s="5"/>
+      <c r="AI41" s="5">
+        <v>394611</v>
+      </c>
       <c r="AJ41" s="5"/>
       <c r="AK41" s="5"/>
       <c r="AL41" s="5"/>
@@ -3717,11 +3739,11 @@
         <v>1298434</v>
       </c>
       <c r="AX41" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>1775159</v>
       </c>
       <c r="AY41" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>1625522.56</v>
       </c>
       <c r="AZ41" s="4">
@@ -3737,51 +3759,51 @@
       <c r="E42" s="7"/>
       <c r="F42" s="7"/>
       <c r="G42" s="7">
-        <f t="shared" ref="G42:R42" si="26">G41+G40</f>
+        <f t="shared" ref="G42:R42" si="27">G41+G40</f>
         <v>77138</v>
       </c>
       <c r="H42" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>87048</v>
       </c>
       <c r="I42" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>96155</v>
       </c>
       <c r="J42" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>104891</v>
       </c>
       <c r="K42" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>102672</v>
       </c>
       <c r="L42" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>82272</v>
       </c>
       <c r="M42" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>145036</v>
       </c>
       <c r="N42" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>179757</v>
       </c>
       <c r="O42" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>180338</v>
       </c>
       <c r="P42" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>206421</v>
       </c>
       <c r="Q42" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>237823</v>
       </c>
       <c r="R42" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>305840</v>
       </c>
       <c r="S42" s="7">
@@ -3793,35 +3815,35 @@
         <v>258580</v>
       </c>
       <c r="U42" s="7">
-        <f t="shared" ref="U42:AB42" si="27">+U40+U41</f>
+        <f t="shared" ref="U42:AB42" si="28">+U40+U41</f>
         <v>365923</v>
       </c>
       <c r="V42" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>439701</v>
       </c>
       <c r="W42" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>440808</v>
       </c>
       <c r="X42" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>479700</v>
       </c>
       <c r="Y42" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>430488</v>
       </c>
       <c r="Z42" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>494989</v>
       </c>
       <c r="AA42" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>433371</v>
       </c>
       <c r="AB42" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>410831</v>
       </c>
       <c r="AC42" s="7">
@@ -3848,7 +3870,9 @@
         <f>+AH40+AH41</f>
         <v>434358</v>
       </c>
-      <c r="AI42" s="7"/>
+      <c r="AI42" s="7">
+        <v>408386</v>
+      </c>
       <c r="AJ42" s="7"/>
       <c r="AK42" s="7"/>
       <c r="AL42" s="7"/>
@@ -3905,19 +3929,19 @@
         <v>3956060.5969500002</v>
       </c>
       <c r="BG42" s="6">
-        <f t="shared" ref="BG42:BJ42" si="28">+BF42*1.05</f>
+        <f t="shared" ref="BG42:BJ42" si="29">+BF42*1.05</f>
         <v>4153863.6267975005</v>
       </c>
       <c r="BH42" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>4361556.8081373759</v>
       </c>
       <c r="BI42" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>4579634.6485442445</v>
       </c>
       <c r="BJ42" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>4808616.3809714569</v>
       </c>
     </row>
@@ -4002,43 +4026,43 @@
       <c r="AL44" s="5"/>
       <c r="AX44" s="25"/>
       <c r="BA44" s="4">
-        <f t="shared" ref="BA44:BJ44" si="29">+BA118-$AX$118</f>
+        <f t="shared" ref="BA44:BJ44" si="30">+BA118-$AX$118</f>
         <v>1599.3888000000002</v>
       </c>
       <c r="BB44" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>2659.0812799999999</v>
       </c>
       <c r="BC44" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>4064.0124800000003</v>
       </c>
       <c r="BD44" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>6529.9465600000003</v>
       </c>
       <c r="BE44" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>9649.9090659199992</v>
       </c>
       <c r="BF44" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>10508.939366971999</v>
       </c>
       <c r="BG44" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>11426.745425464402</v>
       </c>
       <c r="BH44" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>12407.057241388613</v>
       </c>
       <c r="BI44" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>13453.830875341582</v>
       </c>
       <c r="BJ44" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>14571.261729586378</v>
       </c>
     </row>
@@ -4142,12 +4166,14 @@
         <f>+AZ45-SUM(AE45:AG45)</f>
         <v>16750</v>
       </c>
-      <c r="AI45" s="5"/>
+      <c r="AI45" s="5">
+        <v>15473</v>
+      </c>
       <c r="AJ45" s="5"/>
       <c r="AK45" s="5"/>
       <c r="AL45" s="5"/>
       <c r="AT45" s="4">
-        <f t="shared" ref="AT45:AT50" si="30">SUM(G45:J45)</f>
+        <f t="shared" ref="AT45:AT50" si="31">SUM(G45:J45)</f>
         <v>19952</v>
       </c>
       <c r="AU45" s="4">
@@ -4173,43 +4199,43 @@
         <v>65821</v>
       </c>
       <c r="BA45" s="4">
-        <f t="shared" ref="BA45:BE45" si="31">BA38*BA42/1000000</f>
+        <f t="shared" ref="BA45:BE45" si="32">BA38*BA42/1000000</f>
         <v>86041.405341147649</v>
       </c>
       <c r="BB45" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>106347.17700165848</v>
       </c>
       <c r="BC45" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>131445.11077404988</v>
       </c>
       <c r="BD45" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>155696.73371186209</v>
       </c>
       <c r="BE45" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>176404.39929553977</v>
       </c>
       <c r="BF45" s="4">
-        <f t="shared" ref="BF45:BJ45" si="32">BF38*BF42/1000000</f>
+        <f t="shared" ref="BF45:BJ45" si="33">BF38*BF42/1000000</f>
         <v>190781.35783812625</v>
       </c>
       <c r="BG45" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>206330.03850193357</v>
       </c>
       <c r="BH45" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>223145.93663984118</v>
       </c>
       <c r="BI45" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>241332.33047598824</v>
       </c>
       <c r="BJ45" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>261000.9154097813</v>
       </c>
     </row>
@@ -4267,7 +4293,7 @@
         <v>286</v>
       </c>
       <c r="V46" s="5">
-        <f t="shared" ref="V46:V47" si="33">+R46*1.4</f>
+        <f t="shared" ref="V46:V47" si="34">+R46*1.4</f>
         <v>439.59999999999997</v>
       </c>
       <c r="W46" s="5">
@@ -4293,7 +4319,7 @@
         <v>554</v>
       </c>
       <c r="AD46" s="5">
-        <f t="shared" ref="AD46:AD47" si="34">+Z46</f>
+        <f t="shared" ref="AD46:AD47" si="35">+Z46</f>
         <v>433</v>
       </c>
       <c r="AE46" s="5">
@@ -4309,12 +4335,14 @@
         <f>+AZ46-SUM(AE46:AG46)</f>
         <v>542</v>
       </c>
-      <c r="AI46" s="5"/>
+      <c r="AI46" s="5">
+        <v>380</v>
+      </c>
       <c r="AJ46" s="5"/>
       <c r="AK46" s="5"/>
       <c r="AL46" s="5"/>
       <c r="AT46" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AU46" s="4">
@@ -4322,7 +4350,7 @@
         <v>401</v>
       </c>
       <c r="AV46" s="4">
-        <f t="shared" ref="AV46:AV52" si="35">SUM(O46:R46)</f>
+        <f t="shared" ref="AV46:AV52" si="36">SUM(O46:R46)</f>
         <v>1465</v>
       </c>
       <c r="AW46" s="4">
@@ -4394,7 +4422,7 @@
         <v>621</v>
       </c>
       <c r="V47" s="5">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>879.19999999999993</v>
       </c>
       <c r="W47" s="5">
@@ -4420,7 +4448,7 @@
         <v>489</v>
       </c>
       <c r="AD47" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>500</v>
       </c>
       <c r="AE47" s="5">
@@ -4436,12 +4464,14 @@
         <f>+AZ47-SUM(AE47:AG47)</f>
         <v>401</v>
       </c>
-      <c r="AI47" s="5"/>
+      <c r="AI47" s="5">
+        <v>381</v>
+      </c>
       <c r="AJ47" s="5"/>
       <c r="AK47" s="5"/>
       <c r="AL47" s="5"/>
       <c r="AT47" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>869</v>
       </c>
       <c r="AU47" s="4">
@@ -4449,7 +4479,7 @@
         <v>1052</v>
       </c>
       <c r="AV47" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1642</v>
       </c>
       <c r="AW47" s="4">
@@ -4476,51 +4506,51 @@
       <c r="E48" s="7"/>
       <c r="F48" s="7"/>
       <c r="G48" s="7">
-        <f t="shared" ref="G48:K48" si="36">SUM(G45:G47)</f>
+        <f t="shared" ref="G48:K48" si="37">SUM(G45:G47)</f>
         <v>3724</v>
       </c>
       <c r="H48" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>5376</v>
       </c>
       <c r="I48" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>5353</v>
       </c>
       <c r="J48" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>6368</v>
       </c>
       <c r="K48" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>5132</v>
       </c>
       <c r="L48" s="7">
-        <f t="shared" ref="L48" si="37">SUM(L45:L47)</f>
+        <f t="shared" ref="L48" si="38">SUM(L45:L47)</f>
         <v>5179</v>
       </c>
       <c r="M48" s="7">
-        <f t="shared" ref="M48:R48" si="38">SUM(M45:M47)</f>
+        <f t="shared" ref="M48:R48" si="39">SUM(M45:M47)</f>
         <v>7611</v>
       </c>
       <c r="N48" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>9314</v>
       </c>
       <c r="O48" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>9002</v>
       </c>
       <c r="P48" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>10206</v>
       </c>
       <c r="Q48" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>12057</v>
       </c>
       <c r="R48" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>15967</v>
       </c>
       <c r="S48" s="7">
@@ -4536,31 +4566,31 @@
         <v>18692</v>
       </c>
       <c r="V48" s="7">
-        <f t="shared" ref="V48:AH48" si="39">SUM(V45:V47)</f>
+        <f t="shared" ref="V48:AH48" si="40">SUM(V45:V47)</f>
         <v>22353.8</v>
       </c>
       <c r="W48" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>19963</v>
       </c>
       <c r="X48" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>21268</v>
       </c>
       <c r="Y48" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>19625</v>
       </c>
       <c r="Z48" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>21563</v>
       </c>
       <c r="AA48" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>17378</v>
       </c>
       <c r="AB48" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>19878</v>
       </c>
       <c r="AC48" s="7">
@@ -4568,51 +4598,53 @@
         <v>20882.205713494131</v>
       </c>
       <c r="AD48" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>24966.031137321035</v>
       </c>
       <c r="AE48" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>13967</v>
       </c>
       <c r="AF48" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>16661</v>
       </c>
       <c r="AG48" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>21205</v>
       </c>
       <c r="AH48" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>17693</v>
       </c>
-      <c r="AI48" s="7"/>
+      <c r="AI48" s="7">
+        <v>16234</v>
+      </c>
       <c r="AJ48" s="7"/>
       <c r="AK48" s="7"/>
       <c r="AL48" s="7"/>
       <c r="AT48" s="6">
-        <f>SUM(AT45:AT47)</f>
+        <f t="shared" ref="AT48:AY48" si="41">SUM(AT45:AT47)</f>
         <v>20821</v>
       </c>
       <c r="AU48" s="6">
-        <f>SUM(AU45:AU47)</f>
+        <f t="shared" si="41"/>
         <v>27236</v>
       </c>
       <c r="AV48" s="6">
-        <f>SUM(AV45:AV47)</f>
+        <f t="shared" si="41"/>
         <v>47232</v>
       </c>
       <c r="AW48" s="6">
-        <f>SUM(AW45:AW47)</f>
+        <f t="shared" si="41"/>
         <v>72508.800000000003</v>
       </c>
       <c r="AX48" s="6">
-        <f>SUM(AX45:AX47)</f>
+        <f t="shared" si="41"/>
         <v>82419</v>
       </c>
       <c r="AY48" s="6">
-        <f>SUM(AY45:AY47)</f>
+        <f t="shared" si="41"/>
         <v>77070</v>
       </c>
       <c r="AZ48" s="6">
@@ -4632,31 +4664,31 @@
         <v>131445.11077404988</v>
       </c>
       <c r="BD48" s="6">
-        <f t="shared" ref="BD48:BJ48" si="40">BD45+BD46+BD47</f>
+        <f t="shared" ref="BD48:BJ48" si="42">BD45+BD46+BD47</f>
         <v>155696.73371186209</v>
       </c>
       <c r="BE48" s="6">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>176404.39929553977</v>
       </c>
       <c r="BF48" s="6">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>190781.35783812625</v>
       </c>
       <c r="BG48" s="6">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>206330.03850193357</v>
       </c>
       <c r="BH48" s="6">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>223145.93663984118</v>
       </c>
       <c r="BI48" s="6">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>241332.33047598824</v>
       </c>
       <c r="BJ48" s="6">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>261000.9154097813</v>
       </c>
     </row>
@@ -4714,7 +4746,7 @@
         <v>1117</v>
       </c>
       <c r="V49" s="5">
-        <f t="shared" ref="V49:V50" si="41">+R49*1.4</f>
+        <f t="shared" ref="V49:V50" si="43">+R49*1.4</f>
         <v>963.19999999999993</v>
       </c>
       <c r="W49" s="5">
@@ -4740,7 +4772,7 @@
         <v>2182.6</v>
       </c>
       <c r="AD49" s="5">
-        <f t="shared" ref="AD49:AD50" si="42">+Z49</f>
+        <f t="shared" ref="AD49:AD50" si="44">+Z49</f>
         <v>1438</v>
       </c>
       <c r="AE49" s="5">
@@ -4756,7 +4788,9 @@
         <f>+AZ49-SUM(AE49:AG49)</f>
         <v>3837</v>
       </c>
-      <c r="AI49" s="5"/>
+      <c r="AI49" s="5">
+        <v>2408</v>
+      </c>
       <c r="AJ49" s="5"/>
       <c r="AK49" s="5"/>
       <c r="AL49" s="5"/>
@@ -4770,7 +4804,7 @@
         <v>3740.973</v>
       </c>
       <c r="AT49" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1531</v>
       </c>
       <c r="AU49" s="4">
@@ -4850,7 +4884,7 @@
         <v>1645</v>
       </c>
       <c r="V50" s="5">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>1489.6</v>
       </c>
       <c r="W50" s="5">
@@ -4876,7 +4910,7 @@
         <v>3032.3999999999996</v>
       </c>
       <c r="AD50" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>2166</v>
       </c>
       <c r="AE50" s="5">
@@ -4892,7 +4926,9 @@
         <f>+AZ50-SUM(AE50:AG50)</f>
         <v>3371</v>
       </c>
-      <c r="AI50" s="5"/>
+      <c r="AI50" s="5">
+        <v>3745</v>
+      </c>
       <c r="AJ50" s="5"/>
       <c r="AK50" s="5"/>
       <c r="AL50" s="5"/>
@@ -4906,7 +4942,7 @@
         <v>305.05200000000002</v>
       </c>
       <c r="AT50" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>2226</v>
       </c>
       <c r="AU50" s="4">
@@ -4914,7 +4950,7 @@
         <v>2306</v>
       </c>
       <c r="AV50" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>3802</v>
       </c>
       <c r="AW50" s="4">
@@ -4941,51 +4977,51 @@
       <c r="E51" s="7"/>
       <c r="F51" s="7"/>
       <c r="G51" s="7">
-        <f t="shared" ref="G51:K51" si="43">SUM(G48:G50)</f>
+        <f t="shared" ref="G51:K51" si="45">SUM(G48:G50)</f>
         <v>4541</v>
       </c>
       <c r="H51" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>6350</v>
       </c>
       <c r="I51" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>6303</v>
       </c>
       <c r="J51" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>7384</v>
       </c>
       <c r="K51" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>5985</v>
       </c>
       <c r="L51" s="7">
-        <f t="shared" ref="L51" si="44">SUM(L48:L50)</f>
+        <f t="shared" ref="L51" si="46">SUM(L48:L50)</f>
         <v>6036</v>
       </c>
       <c r="M51" s="7">
-        <f t="shared" ref="M51:R51" si="45">SUM(M48:M50)</f>
+        <f t="shared" ref="M51:R51" si="47">SUM(M48:M50)</f>
         <v>8771</v>
       </c>
       <c r="N51" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>10744</v>
       </c>
       <c r="O51" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>10389</v>
       </c>
       <c r="P51" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>11958</v>
       </c>
       <c r="Q51" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>13757</v>
       </c>
       <c r="R51" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>17719</v>
       </c>
       <c r="S51" s="7">
@@ -5001,31 +5037,31 @@
         <v>21454</v>
       </c>
       <c r="V51" s="7">
-        <f t="shared" ref="V51:AH51" si="46">SUM(V48:V50)</f>
+        <f t="shared" ref="V51:AI51" si="48">SUM(V48:V50)</f>
         <v>24806.6</v>
       </c>
       <c r="W51" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>23329</v>
       </c>
       <c r="X51" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>24927</v>
       </c>
       <c r="Y51" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>23350</v>
       </c>
       <c r="Z51" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>25167</v>
       </c>
       <c r="AA51" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>21301</v>
       </c>
       <c r="AB51" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>25500</v>
       </c>
       <c r="AC51" s="7">
@@ -5033,26 +5069,29 @@
         <v>26097.205713494128</v>
       </c>
       <c r="AD51" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>28570.031137321035</v>
       </c>
       <c r="AE51" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>19335</v>
       </c>
       <c r="AF51" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>22496</v>
       </c>
       <c r="AG51" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>28095</v>
       </c>
       <c r="AH51" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>24901</v>
       </c>
-      <c r="AI51" s="7"/>
+      <c r="AI51" s="7">
+        <f t="shared" si="48"/>
+        <v>22387</v>
+      </c>
       <c r="AJ51" s="7"/>
       <c r="AK51" s="7"/>
       <c r="AL51" s="7"/>
@@ -5078,19 +5117,19 @@
         <v>21461.268</v>
       </c>
       <c r="AT51" s="6">
-        <f t="shared" ref="AT51:AW51" si="47">SUM(AT48:AT50)</f>
+        <f t="shared" ref="AT51:AW51" si="49">SUM(AT48:AT50)</f>
         <v>24578</v>
       </c>
       <c r="AU51" s="6">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>31536</v>
       </c>
       <c r="AV51" s="6">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>53823</v>
       </c>
       <c r="AW51" s="6">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>81950.600000000006</v>
       </c>
       <c r="AX51" s="6">
@@ -5110,39 +5149,39 @@
         <v>87640.794141147649</v>
       </c>
       <c r="BB51" s="6">
-        <f t="shared" ref="BB51:BE51" si="48">SUM(BB48:BB50)+BB44</f>
+        <f t="shared" ref="BB51:BE51" si="50">SUM(BB48:BB50)+BB44</f>
         <v>109006.25828165848</v>
       </c>
       <c r="BC51" s="6">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>135509.12325404989</v>
       </c>
       <c r="BD51" s="6">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>162226.6802718621</v>
       </c>
       <c r="BE51" s="6">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>186054.30836145976</v>
       </c>
       <c r="BF51" s="6">
-        <f t="shared" ref="BF51" si="49">SUM(BF48:BF50)+BF44</f>
+        <f t="shared" ref="BF51" si="51">SUM(BF48:BF50)+BF44</f>
         <v>201290.29720509824</v>
       </c>
       <c r="BG51" s="6">
-        <f t="shared" ref="BG51" si="50">SUM(BG48:BG50)+BG44</f>
+        <f t="shared" ref="BG51" si="52">SUM(BG48:BG50)+BG44</f>
         <v>217756.78392739798</v>
       </c>
       <c r="BH51" s="6">
-        <f t="shared" ref="BH51" si="51">SUM(BH48:BH50)+BH44</f>
+        <f t="shared" ref="BH51" si="53">SUM(BH48:BH50)+BH44</f>
         <v>235552.99388122981</v>
       </c>
       <c r="BI51" s="6">
-        <f t="shared" ref="BI51" si="52">SUM(BI48:BI50)+BI44</f>
+        <f t="shared" ref="BI51" si="54">SUM(BI48:BI50)+BI44</f>
         <v>254786.16135132982</v>
       </c>
       <c r="BJ51" s="6">
-        <f t="shared" ref="BJ51" si="53">SUM(BJ48:BJ50)+BJ44</f>
+        <f t="shared" ref="BJ51" si="55">SUM(BJ48:BJ50)+BJ44</f>
         <v>275572.17713936768</v>
       </c>
     </row>
@@ -5238,10 +5277,12 @@
         <v>17365</v>
       </c>
       <c r="AH52" s="5">
-        <f>+AZ52-SUM(AE52:AG52)</f>
+        <f t="shared" ref="AH52:AI58" si="56">+AZ52-SUM(AE52:AG52)</f>
         <v>13874</v>
       </c>
-      <c r="AI52" s="5"/>
+      <c r="AI52" s="5">
+        <v>12616</v>
+      </c>
       <c r="AJ52" s="5"/>
       <c r="AK52" s="5"/>
       <c r="AL52" s="5"/>
@@ -5249,7 +5290,7 @@
         <v>1483.3209999999999</v>
       </c>
       <c r="AV52" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>32415</v>
       </c>
       <c r="AW52" s="4">
@@ -5257,7 +5298,7 @@
         <v>49599</v>
       </c>
       <c r="AX52" s="4">
-        <f t="shared" ref="AX52:AX66" si="54">SUM(W52:Z52)</f>
+        <f t="shared" ref="AX52:AX66" si="57">SUM(W52:Z52)</f>
         <v>65121</v>
       </c>
       <c r="AY52" s="4">
@@ -5287,23 +5328,23 @@
         <v>139540.73127109482</v>
       </c>
       <c r="BF52" s="4">
-        <f t="shared" ref="BF52:BJ52" si="55">BF51*0.75</f>
+        <f t="shared" ref="BF52:BJ52" si="58">BF51*0.75</f>
         <v>150967.72290382368</v>
       </c>
       <c r="BG52" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="58"/>
         <v>163317.58794554847</v>
       </c>
       <c r="BH52" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="58"/>
         <v>176664.74541092236</v>
       </c>
       <c r="BI52" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="58"/>
         <v>191089.62101349735</v>
       </c>
       <c r="BJ52" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="58"/>
         <v>206679.13285452576</v>
       </c>
     </row>
@@ -5316,51 +5357,51 @@
       <c r="E53" s="5"/>
       <c r="F53" s="5"/>
       <c r="G53" s="5">
-        <f t="shared" ref="G53:N53" si="56">G45-G52</f>
+        <f t="shared" ref="G53:N53" si="59">G45-G52</f>
         <v>653</v>
       </c>
       <c r="H53" s="5">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>914</v>
       </c>
       <c r="I53" s="5">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>1118</v>
       </c>
       <c r="J53" s="5">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>1328</v>
       </c>
       <c r="K53" s="5">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>1194</v>
       </c>
       <c r="L53" s="5">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>1197</v>
       </c>
       <c r="M53" s="5">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>1985</v>
       </c>
       <c r="N53" s="5">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>1711</v>
       </c>
       <c r="O53" s="5">
-        <f t="shared" ref="O53:R53" si="57">O45-O52</f>
+        <f t="shared" ref="O53:R53" si="60">O45-O52</f>
         <v>1730</v>
       </c>
       <c r="P53" s="5">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>2401</v>
       </c>
       <c r="Q53" s="5">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>3243</v>
       </c>
       <c r="R53" s="5">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>4336</v>
       </c>
       <c r="S53" s="5">
@@ -5376,7 +5417,7 @@
         <v>4686</v>
       </c>
       <c r="V53" s="5">
-        <f t="shared" ref="V53:Z53" si="58">V45-V52</f>
+        <f t="shared" ref="V53:Z53" si="61">V45-V52</f>
         <v>5602</v>
       </c>
       <c r="W53" s="5">
@@ -5384,50 +5425,53 @@
         <v>3456</v>
       </c>
       <c r="X53" s="5">
-        <f t="shared" si="58"/>
+        <f t="shared" si="61"/>
         <v>3578</v>
       </c>
       <c r="Y53" s="5">
-        <f t="shared" si="58"/>
+        <f t="shared" si="61"/>
         <v>2926</v>
       </c>
       <c r="Z53" s="5">
-        <f t="shared" si="58"/>
+        <f t="shared" si="61"/>
         <v>3428</v>
       </c>
       <c r="AA53" s="5">
-        <f t="shared" ref="AA53:AG53" si="59">AA45-AA52</f>
+        <f t="shared" ref="AA53:AI53" si="62">AA45-AA52</f>
         <v>2563</v>
       </c>
       <c r="AB53" s="5">
-        <f t="shared" si="59"/>
+        <f t="shared" si="62"/>
         <v>2568</v>
       </c>
       <c r="AC53" s="5">
-        <f t="shared" si="59"/>
+        <f t="shared" si="62"/>
         <v>2975.8808570241199</v>
       </c>
       <c r="AD53" s="5">
-        <f t="shared" si="59"/>
+        <f t="shared" si="62"/>
         <v>3604.9546705981556</v>
       </c>
       <c r="AE53" s="5">
-        <f t="shared" si="59"/>
+        <f t="shared" si="62"/>
         <v>1464</v>
       </c>
       <c r="AF53" s="5">
-        <f t="shared" si="59"/>
+        <f t="shared" si="62"/>
         <v>2220</v>
       </c>
       <c r="AG53" s="5">
-        <f t="shared" si="59"/>
+        <f t="shared" si="62"/>
         <v>2994</v>
       </c>
       <c r="AH53" s="5">
-        <f>+AZ53-SUM(AE53:AG53)</f>
+        <f t="shared" si="56"/>
         <v>6581</v>
       </c>
-      <c r="AI53" s="5"/>
+      <c r="AI53" s="5">
+        <f>AI45-AI52</f>
+        <v>2857</v>
+      </c>
       <c r="AJ53" s="5"/>
       <c r="AK53" s="5"/>
       <c r="AL53" s="5"/>
@@ -5440,7 +5484,7 @@
         <v>18405</v>
       </c>
       <c r="AX53" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="57"/>
         <v>13388</v>
       </c>
       <c r="AY53" s="4">
@@ -5542,10 +5586,13 @@
         <v>0</v>
       </c>
       <c r="AH54" s="5">
-        <f>+AZ54-SUM(AE54:AG54)</f>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="AI54" s="5"/>
+      <c r="AI54" s="5">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
       <c r="AJ54" s="5"/>
       <c r="AK54" s="5"/>
       <c r="AL54" s="5"/>
@@ -5655,10 +5702,12 @@
         <v>225</v>
       </c>
       <c r="AH55" s="5">
-        <f>+AZ55-SUM(AE55:AG55)</f>
+        <f t="shared" si="56"/>
         <v>206</v>
       </c>
-      <c r="AI55" s="5"/>
+      <c r="AI55" s="5">
+        <v>196</v>
+      </c>
       <c r="AJ55" s="5"/>
       <c r="AK55" s="5"/>
       <c r="AL55" s="5"/>
@@ -5667,7 +5716,7 @@
         <v>1510</v>
       </c>
       <c r="AX55" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="57"/>
         <v>1268</v>
       </c>
       <c r="AY55" s="4">
@@ -5686,35 +5735,35 @@
       <c r="E56" s="5"/>
       <c r="F56" s="5"/>
       <c r="G56" s="5">
-        <f t="shared" ref="G56:K56" si="60">G48-G55-G52</f>
+        <f t="shared" ref="G56:K56" si="63">G48-G55-G52</f>
         <v>751</v>
       </c>
       <c r="H56" s="5">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v>1016</v>
       </c>
       <c r="I56" s="5">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v>1222</v>
       </c>
       <c r="J56" s="5">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v>1434</v>
       </c>
       <c r="K56" s="5">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v>1311</v>
       </c>
       <c r="L56" s="5">
-        <f t="shared" ref="L56" si="61">L48-L55-L52</f>
+        <f t="shared" ref="L56" si="64">L48-L55-L52</f>
         <v>1317</v>
       </c>
       <c r="M56" s="5">
-        <f t="shared" ref="M56:N56" si="62">M48-M55-M52</f>
+        <f t="shared" ref="M56:N56" si="65">M48-M55-M52</f>
         <v>2105</v>
       </c>
       <c r="N56" s="5">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v>2244</v>
       </c>
       <c r="O56" s="5">
@@ -5722,19 +5771,19 @@
         <v>2385</v>
       </c>
       <c r="P56" s="5">
-        <f t="shared" ref="P56:S56" si="63">P48-P55-P52</f>
+        <f t="shared" ref="P56:S56" si="66">P48-P55-P52</f>
         <v>2899</v>
       </c>
       <c r="Q56" s="5">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v>3673</v>
       </c>
       <c r="R56" s="5">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v>4882</v>
       </c>
       <c r="S56" s="5">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v>5539</v>
       </c>
       <c r="T56" s="5">
@@ -5746,7 +5795,7 @@
         <v>5212</v>
       </c>
       <c r="V56" s="5">
-        <f t="shared" ref="V56:AG56" si="64">V48-V55-V52</f>
+        <f t="shared" ref="V56:AI56" si="67">V48-V55-V52</f>
         <v>6568.7999999999993</v>
       </c>
       <c r="W56" s="5">
@@ -5754,19 +5803,19 @@
         <v>4208</v>
       </c>
       <c r="X56" s="5">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v>4089</v>
       </c>
       <c r="Y56" s="5">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v>3668</v>
       </c>
       <c r="Z56" s="5">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v>4065</v>
       </c>
       <c r="AA56" s="5">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v>3212</v>
       </c>
       <c r="AB56" s="5">
@@ -5774,30 +5823,33 @@
         <v>3671</v>
       </c>
       <c r="AC56" s="5">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v>3774.3808570241199</v>
       </c>
       <c r="AD56" s="5">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v>4287.9546705981556</v>
       </c>
       <c r="AE56" s="5">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v>2267</v>
       </c>
       <c r="AF56" s="5">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v>2866</v>
       </c>
       <c r="AG56" s="5">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v>3615</v>
       </c>
       <c r="AH56" s="5">
-        <f>+AZ56-SUM(AE56:AG56)</f>
+        <f t="shared" si="56"/>
         <v>29812</v>
       </c>
-      <c r="AI56" s="5"/>
+      <c r="AI56" s="5">
+        <f>AI48-AI55-AI52</f>
+        <v>3422</v>
+      </c>
       <c r="AJ56" s="5"/>
       <c r="AK56" s="5"/>
       <c r="AL56" s="5"/>
@@ -5818,43 +5870,43 @@
         <v>38560</v>
       </c>
       <c r="BA56" s="4">
-        <f t="shared" ref="BA56:BJ56" si="65">BA51-BA52</f>
+        <f t="shared" ref="BA56:BJ56" si="68">BA51-BA52</f>
         <v>19668.08392164101</v>
       </c>
       <c r="BB56" s="4">
-        <f t="shared" si="65"/>
+        <f t="shared" si="68"/>
         <v>23981.376821964863</v>
       </c>
       <c r="BC56" s="4">
-        <f t="shared" si="65"/>
+        <f t="shared" si="68"/>
         <v>31167.098348431478</v>
       </c>
       <c r="BD56" s="4">
-        <f t="shared" si="65"/>
+        <f t="shared" si="68"/>
         <v>38934.403265246903</v>
       </c>
       <c r="BE56" s="4">
-        <f t="shared" si="65"/>
+        <f t="shared" si="68"/>
         <v>46513.577090364939</v>
       </c>
       <c r="BF56" s="4">
-        <f t="shared" si="65"/>
+        <f t="shared" si="68"/>
         <v>50322.574301274552</v>
       </c>
       <c r="BG56" s="4">
-        <f t="shared" si="65"/>
+        <f t="shared" si="68"/>
         <v>54439.195981849509</v>
       </c>
       <c r="BH56" s="4">
-        <f t="shared" si="65"/>
+        <f t="shared" si="68"/>
         <v>58888.248470307444</v>
       </c>
       <c r="BI56" s="4">
-        <f t="shared" si="65"/>
+        <f t="shared" si="68"/>
         <v>63696.54033783247</v>
       </c>
       <c r="BJ56" s="4">
-        <f t="shared" si="65"/>
+        <f t="shared" si="68"/>
         <v>68893.044284841919</v>
       </c>
     </row>
@@ -5950,10 +6002,12 @@
         <v>2342</v>
       </c>
       <c r="AH57" s="5">
-        <f>+AZ57-SUM(AE57:AG57)</f>
+        <f t="shared" si="56"/>
         <v>2739</v>
       </c>
-      <c r="AI57" s="5"/>
+      <c r="AI57" s="5">
+        <v>1456</v>
+      </c>
       <c r="AJ57" s="5"/>
       <c r="AK57" s="5"/>
       <c r="AL57" s="5"/>
@@ -5962,7 +6016,7 @@
         <v>3621</v>
       </c>
       <c r="AX57" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="57"/>
         <v>4894</v>
       </c>
       <c r="AY57" s="4">
@@ -6064,10 +6118,12 @@
         <v>3109</v>
       </c>
       <c r="AH58" s="5">
-        <f>+AZ58-SUM(AE58:AG58)</f>
+        <f t="shared" si="56"/>
         <v>3073</v>
       </c>
-      <c r="AI58" s="5"/>
+      <c r="AI58" s="5">
+        <v>3399</v>
+      </c>
       <c r="AJ58" s="5"/>
       <c r="AK58" s="5"/>
       <c r="AL58" s="5"/>
@@ -6076,7 +6132,7 @@
         <v>5880</v>
       </c>
       <c r="AX58" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="57"/>
         <v>7830</v>
       </c>
       <c r="AY58" s="4">
@@ -6095,175 +6151,178 @@
       <c r="E59" s="5"/>
       <c r="F59" s="5"/>
       <c r="G59" s="5">
-        <f t="shared" ref="G59:K59" si="66">G56+G49+G50-G57-G58</f>
+        <f t="shared" ref="G59:K59" si="69">G56+G49+G50-G57-G58</f>
         <v>566</v>
       </c>
       <c r="H59" s="5">
-        <f t="shared" si="66"/>
+        <f t="shared" si="69"/>
         <v>921</v>
       </c>
       <c r="I59" s="5">
-        <f t="shared" si="66"/>
+        <f t="shared" si="69"/>
         <v>1191</v>
       </c>
       <c r="J59" s="5">
-        <f t="shared" si="66"/>
+        <f t="shared" si="69"/>
         <v>1391</v>
       </c>
       <c r="K59" s="5">
-        <f t="shared" si="66"/>
+        <f t="shared" si="69"/>
         <v>1234</v>
       </c>
       <c r="L59" s="5">
-        <f t="shared" ref="L59" si="67">L56+L49+L50-L57-L58</f>
+        <f t="shared" ref="L59" si="70">L56+L49+L50-L57-L58</f>
         <v>1267</v>
       </c>
       <c r="M59" s="5">
-        <f t="shared" ref="M59:T59" si="68">M56+M49+M50-M57-M58</f>
+        <f t="shared" ref="M59:T59" si="71">M56+M49+M50-M57-M58</f>
         <v>2063</v>
       </c>
       <c r="N59" s="5">
-        <f t="shared" si="68"/>
+        <f t="shared" si="71"/>
         <v>2066</v>
       </c>
       <c r="O59" s="5">
-        <f t="shared" si="68"/>
+        <f t="shared" si="71"/>
         <v>2215</v>
       </c>
       <c r="P59" s="5">
-        <f t="shared" si="68"/>
+        <f t="shared" si="71"/>
         <v>2884</v>
       </c>
       <c r="Q59" s="5">
-        <f t="shared" si="68"/>
+        <f t="shared" si="71"/>
         <v>3660</v>
       </c>
       <c r="R59" s="5">
-        <f t="shared" si="68"/>
+        <f t="shared" si="71"/>
         <v>4847</v>
       </c>
       <c r="S59" s="5">
-        <f t="shared" si="68"/>
+        <f t="shared" si="71"/>
         <v>5460</v>
       </c>
       <c r="T59" s="5">
-        <f t="shared" si="68"/>
+        <f t="shared" si="71"/>
         <v>4233</v>
       </c>
       <c r="U59" s="5">
-        <f t="shared" ref="U59:AG59" si="69">U56+U49+U50-U57-U58</f>
+        <f t="shared" ref="U59:AG59" si="72">U56+U49+U50-U57-U58</f>
         <v>5382</v>
       </c>
       <c r="V59" s="5">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>6265.5999999999985</v>
       </c>
       <c r="W59" s="5">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>4511</v>
       </c>
       <c r="X59" s="5">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>4533</v>
       </c>
       <c r="Y59" s="5">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>4178</v>
       </c>
       <c r="Z59" s="5">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>4438</v>
       </c>
       <c r="AA59" s="5">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>3696</v>
       </c>
       <c r="AB59" s="5">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>4578</v>
       </c>
       <c r="AC59" s="5">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>4101.7708570241202</v>
       </c>
       <c r="AD59" s="5">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>4431.7546705981558</v>
       </c>
       <c r="AE59" s="5">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>3153</v>
       </c>
       <c r="AF59" s="5">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>3878</v>
       </c>
       <c r="AG59" s="5">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>5054</v>
       </c>
       <c r="AH59" s="46">
         <f>+AH51-AH52-AH54-AH55-AH57-AH58</f>
         <v>5009</v>
       </c>
-      <c r="AI59" s="46"/>
+      <c r="AI59" s="46">
+        <f>+AI51-AI52-AI54-AI55-AI57-AI58</f>
+        <v>4720</v>
+      </c>
       <c r="AJ59" s="46"/>
       <c r="AK59" s="46"/>
       <c r="AL59" s="46"/>
       <c r="AW59" s="5">
-        <f t="shared" ref="AW59" si="70">+AW51*0.25</f>
+        <f t="shared" ref="AW59" si="73">+AW51*0.25</f>
         <v>20487.650000000001</v>
       </c>
       <c r="AX59" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="57"/>
         <v>17660</v>
       </c>
       <c r="AY59" s="4">
-        <f>+AY56-AY55-AY57-AY58</f>
+        <f t="shared" ref="AY59:BJ59" si="74">+AY56-AY55-AY57-AY58</f>
         <v>17450</v>
       </c>
       <c r="AZ59" s="4">
-        <f>+AZ56-AZ55-AZ57-AZ58</f>
+        <f t="shared" si="74"/>
         <v>17094</v>
       </c>
       <c r="BA59" s="4">
-        <f>+BA56-BA55-BA57-BA58</f>
+        <f t="shared" si="74"/>
         <v>19668.08392164101</v>
       </c>
       <c r="BB59" s="4">
-        <f>+BB56-BB55-BB57-BB58</f>
+        <f t="shared" si="74"/>
         <v>23981.376821964863</v>
       </c>
       <c r="BC59" s="4">
-        <f>+BC56-BC55-BC57-BC58</f>
+        <f t="shared" si="74"/>
         <v>31167.098348431478</v>
       </c>
       <c r="BD59" s="4">
-        <f>+BD56-BD55-BD57-BD58</f>
+        <f t="shared" si="74"/>
         <v>38934.403265246903</v>
       </c>
       <c r="BE59" s="4">
-        <f>+BE56-BE55-BE57-BE58</f>
+        <f t="shared" si="74"/>
         <v>46513.577090364939</v>
       </c>
       <c r="BF59" s="4">
-        <f>+BF56-BF55-BF57-BF58</f>
+        <f t="shared" si="74"/>
         <v>50322.574301274552</v>
       </c>
       <c r="BG59" s="4">
-        <f>+BG56-BG55-BG57-BG58</f>
+        <f t="shared" si="74"/>
         <v>54439.195981849509</v>
       </c>
       <c r="BH59" s="4">
-        <f>+BH56-BH55-BH57-BH58</f>
+        <f t="shared" si="74"/>
         <v>58888.248470307444</v>
       </c>
       <c r="BI59" s="4">
-        <f>+BI56-BI55-BI57-BI58</f>
+        <f t="shared" si="74"/>
         <v>63696.54033783247</v>
       </c>
       <c r="BJ59" s="4">
-        <f>+BJ56-BJ55-BJ57-BJ58</f>
+        <f t="shared" si="74"/>
         <v>68893.044284841919</v>
       </c>
     </row>
@@ -6342,11 +6401,11 @@
         <v>1074</v>
       </c>
       <c r="AC60" s="5">
-        <f t="shared" ref="AC60:AD61" si="71">+Y60*1.1</f>
+        <f t="shared" ref="AC60:AD61" si="75">+Y60*1.1</f>
         <v>1277.1000000000001</v>
       </c>
       <c r="AD60" s="5">
-        <f t="shared" si="71"/>
+        <f t="shared" si="75"/>
         <v>1203.4000000000001</v>
       </c>
       <c r="AE60" s="5">
@@ -6362,7 +6421,9 @@
         <f>+AZ60-SUM(AE60:AG60)</f>
         <v>1783</v>
       </c>
-      <c r="AI60" s="5"/>
+      <c r="AI60" s="5">
+        <v>1946</v>
+      </c>
       <c r="AJ60" s="5"/>
       <c r="AK60" s="5"/>
       <c r="AL60" s="5"/>
@@ -6381,43 +6442,43 @@
         <v>6411</v>
       </c>
       <c r="BA60" s="4">
-        <f t="shared" ref="BA60:BE60" si="72">AZ60*1.04</f>
+        <f t="shared" ref="BA60:BE60" si="76">AZ60*1.04</f>
         <v>6667.4400000000005</v>
       </c>
       <c r="BB60" s="4">
-        <f t="shared" si="72"/>
+        <f t="shared" si="76"/>
         <v>6934.1376000000009</v>
       </c>
       <c r="BC60" s="4">
-        <f t="shared" si="72"/>
+        <f t="shared" si="76"/>
         <v>7211.5031040000013</v>
       </c>
       <c r="BD60" s="4">
-        <f t="shared" si="72"/>
+        <f t="shared" si="76"/>
         <v>7499.9632281600016</v>
       </c>
       <c r="BE60" s="4">
-        <f t="shared" si="72"/>
+        <f t="shared" si="76"/>
         <v>7799.9617572864017</v>
       </c>
       <c r="BF60" s="4">
-        <f t="shared" ref="BF60:BJ60" si="73">BE60*1.04</f>
+        <f t="shared" ref="BF60:BJ60" si="77">BE60*1.04</f>
         <v>8111.9602275778579</v>
       </c>
       <c r="BG60" s="4">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>8436.4386366809722</v>
       </c>
       <c r="BH60" s="4">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>8773.8961821482117</v>
       </c>
       <c r="BI60" s="4">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>9124.8520294341397</v>
       </c>
       <c r="BJ60" s="4">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>9489.8461106115064</v>
       </c>
     </row>
@@ -6497,11 +6558,11 @@
         <v>1277</v>
       </c>
       <c r="AC61" s="5">
-        <f t="shared" si="71"/>
+        <f t="shared" si="75"/>
         <v>1378.3000000000002</v>
       </c>
       <c r="AD61" s="5">
-        <f t="shared" si="71"/>
+        <f t="shared" si="75"/>
         <v>1408</v>
       </c>
       <c r="AE61" s="5">
@@ -6519,7 +6580,9 @@
         <f>+AZ61-SUM(AE61:AG61)</f>
         <v>1817</v>
       </c>
-      <c r="AI61" s="5"/>
+      <c r="AI61" s="5">
+        <v>1833</v>
+      </c>
       <c r="AJ61" s="5"/>
       <c r="AK61" s="5"/>
       <c r="AL61" s="5"/>
@@ -6528,7 +6591,7 @@
         <v>4706.8</v>
       </c>
       <c r="AX61" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="57"/>
         <v>4800</v>
       </c>
       <c r="AY61" s="4">
@@ -6540,43 +6603,43 @@
         <v>6328</v>
       </c>
       <c r="BA61" s="4">
-        <f t="shared" ref="BA61:BE61" si="74">AZ61*1.04</f>
+        <f t="shared" ref="BA61:BE61" si="78">AZ61*1.04</f>
         <v>6581.12</v>
       </c>
       <c r="BB61" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>6844.3648000000003</v>
       </c>
       <c r="BC61" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>7118.139392000001</v>
       </c>
       <c r="BD61" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>7402.8649676800014</v>
       </c>
       <c r="BE61" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>7698.9795663872019</v>
       </c>
       <c r="BF61" s="4">
-        <f t="shared" ref="BF61:BJ61" si="75">BE61*1.04</f>
+        <f t="shared" ref="BF61:BJ61" si="79">BE61*1.04</f>
         <v>8006.9387490426907</v>
       </c>
       <c r="BG61" s="4">
-        <f t="shared" si="75"/>
+        <f t="shared" si="79"/>
         <v>8327.216299004398</v>
       </c>
       <c r="BH61" s="4">
-        <f t="shared" si="75"/>
+        <f t="shared" si="79"/>
         <v>8660.3049509645734</v>
       </c>
       <c r="BI61" s="4">
-        <f t="shared" si="75"/>
+        <f t="shared" si="79"/>
         <v>9006.717149003156</v>
       </c>
       <c r="BJ61" s="4">
-        <f t="shared" si="75"/>
+        <f t="shared" si="79"/>
         <v>9366.9858349632832</v>
       </c>
     </row>
@@ -6589,51 +6652,51 @@
       <c r="E62" s="5"/>
       <c r="F62" s="5"/>
       <c r="G62" s="5">
-        <f t="shared" ref="G62" si="76">G60+G61</f>
+        <f t="shared" ref="G62" si="80">G60+G61</f>
         <v>1044</v>
       </c>
       <c r="H62" s="5">
-        <f t="shared" ref="H62:I62" si="77">H60+H61</f>
+        <f t="shared" ref="H62:I62" si="81">H60+H61</f>
         <v>971</v>
       </c>
       <c r="I62" s="5">
-        <f t="shared" si="77"/>
+        <f t="shared" si="81"/>
         <v>930</v>
       </c>
       <c r="J62" s="5">
-        <f t="shared" ref="J62:L62" si="78">J60+J61</f>
+        <f t="shared" ref="J62:L62" si="82">J60+J61</f>
         <v>1044</v>
       </c>
       <c r="K62" s="5">
-        <f t="shared" si="78"/>
+        <f t="shared" si="82"/>
         <v>951</v>
       </c>
       <c r="L62" s="5">
-        <f t="shared" si="78"/>
+        <f t="shared" si="82"/>
         <v>940</v>
       </c>
       <c r="M62" s="5">
-        <f t="shared" ref="M62:N62" si="79">M60+M61</f>
+        <f t="shared" ref="M62:N62" si="83">M60+M61</f>
         <v>1254</v>
       </c>
       <c r="N62" s="5">
-        <f t="shared" si="79"/>
+        <f t="shared" si="83"/>
         <v>1491</v>
       </c>
       <c r="O62" s="5">
-        <f t="shared" ref="O62:R62" si="80">O60+O61</f>
+        <f t="shared" ref="O62:R62" si="84">O60+O61</f>
         <v>1722</v>
       </c>
       <c r="P62" s="5">
-        <f t="shared" si="80"/>
+        <f t="shared" si="84"/>
         <v>1549</v>
       </c>
       <c r="Q62" s="5">
-        <f t="shared" si="80"/>
+        <f t="shared" si="84"/>
         <v>1605</v>
       </c>
       <c r="R62" s="5">
-        <f t="shared" si="80"/>
+        <f t="shared" si="84"/>
         <v>2234</v>
       </c>
       <c r="S62" s="5">
@@ -6649,7 +6712,7 @@
         <v>1694</v>
       </c>
       <c r="V62" s="5">
-        <f t="shared" ref="V62:AH62" si="81">V60+V61</f>
+        <f t="shared" ref="V62:AI62" si="85">V60+V61</f>
         <v>2602.8000000000002</v>
       </c>
       <c r="W62" s="5">
@@ -6657,55 +6720,58 @@
         <v>1847</v>
       </c>
       <c r="X62" s="5">
-        <f t="shared" si="81"/>
+        <f t="shared" si="85"/>
         <v>2134</v>
       </c>
       <c r="Y62" s="5">
-        <f t="shared" si="81"/>
+        <f t="shared" si="85"/>
         <v>2414</v>
       </c>
       <c r="Z62" s="5">
-        <f t="shared" si="81"/>
+        <f t="shared" si="85"/>
         <v>2374</v>
       </c>
       <c r="AA62" s="5">
-        <f t="shared" si="81"/>
+        <f t="shared" si="85"/>
         <v>2525</v>
       </c>
       <c r="AB62" s="5">
-        <f t="shared" si="81"/>
+        <f t="shared" si="85"/>
         <v>2351</v>
       </c>
       <c r="AC62" s="5">
-        <f t="shared" si="81"/>
+        <f t="shared" si="85"/>
         <v>2655.4000000000005</v>
       </c>
       <c r="AD62" s="5">
-        <f t="shared" si="81"/>
+        <f t="shared" si="85"/>
         <v>2611.4</v>
       </c>
       <c r="AE62" s="5">
-        <f t="shared" si="81"/>
+        <f t="shared" si="85"/>
         <v>2754</v>
       </c>
       <c r="AF62" s="5">
-        <f t="shared" si="81"/>
+        <f t="shared" si="85"/>
         <v>2955</v>
       </c>
       <c r="AG62" s="5">
-        <f t="shared" si="81"/>
+        <f t="shared" si="85"/>
         <v>3430</v>
       </c>
       <c r="AH62" s="5">
-        <f t="shared" si="81"/>
+        <f t="shared" si="85"/>
         <v>3600</v>
       </c>
-      <c r="AI62" s="5"/>
+      <c r="AI62" s="5">
+        <f t="shared" si="85"/>
+        <v>3779</v>
+      </c>
       <c r="AJ62" s="5"/>
       <c r="AK62" s="5"/>
       <c r="AL62" s="5"/>
       <c r="AW62" s="4">
-        <f t="shared" ref="AW62" si="82">+AW60+AW61</f>
+        <f t="shared" ref="AW62" si="86">+AW60+AW61</f>
         <v>7781.8</v>
       </c>
       <c r="AX62" s="4">
@@ -6721,43 +6787,43 @@
         <v>12739</v>
       </c>
       <c r="BA62" s="4">
-        <f t="shared" ref="BA62:BC62" si="83">+BA60+BA61</f>
+        <f t="shared" ref="BA62:BC62" si="87">+BA60+BA61</f>
         <v>13248.560000000001</v>
       </c>
       <c r="BB62" s="4">
-        <f t="shared" si="83"/>
+        <f t="shared" si="87"/>
         <v>13778.502400000001</v>
       </c>
       <c r="BC62" s="4">
-        <f t="shared" si="83"/>
+        <f t="shared" si="87"/>
         <v>14329.642496000002</v>
       </c>
       <c r="BD62" s="4">
-        <f t="shared" ref="BD62" si="84">+BD60+BD61</f>
+        <f t="shared" ref="BD62" si="88">+BD60+BD61</f>
         <v>14902.828195840004</v>
       </c>
       <c r="BE62" s="4">
-        <f t="shared" ref="BE62:BJ62" si="85">+BE60+BE61</f>
+        <f t="shared" ref="BE62:BJ62" si="89">+BE60+BE61</f>
         <v>15498.941323673604</v>
       </c>
       <c r="BF62" s="4">
-        <f t="shared" si="85"/>
+        <f t="shared" si="89"/>
         <v>16118.898976620549</v>
       </c>
       <c r="BG62" s="4">
-        <f t="shared" si="85"/>
+        <f t="shared" si="89"/>
         <v>16763.654935685372</v>
       </c>
       <c r="BH62" s="4">
-        <f t="shared" si="85"/>
+        <f t="shared" si="89"/>
         <v>17434.201133112787</v>
       </c>
       <c r="BI62" s="4">
-        <f t="shared" si="85"/>
+        <f t="shared" si="89"/>
         <v>18131.569178437298</v>
       </c>
       <c r="BJ62" s="4">
-        <f t="shared" si="85"/>
+        <f t="shared" si="89"/>
         <v>18856.831945574791</v>
       </c>
     </row>
@@ -6770,51 +6836,51 @@
       <c r="E63" s="5"/>
       <c r="F63" s="5"/>
       <c r="G63" s="5">
-        <f t="shared" ref="G63" si="86">G59-G62</f>
+        <f t="shared" ref="G63" si="90">G59-G62</f>
         <v>-478</v>
       </c>
       <c r="H63" s="5">
-        <f t="shared" ref="H63:I63" si="87">H59-H62</f>
+        <f t="shared" ref="H63:I63" si="91">H59-H62</f>
         <v>-50</v>
       </c>
       <c r="I63" s="5">
-        <f t="shared" si="87"/>
+        <f t="shared" si="91"/>
         <v>261</v>
       </c>
       <c r="J63" s="5">
-        <f t="shared" ref="J63:L63" si="88">J59-J62</f>
+        <f t="shared" ref="J63:L63" si="92">J59-J62</f>
         <v>347</v>
       </c>
       <c r="K63" s="5">
-        <f t="shared" si="88"/>
+        <f t="shared" si="92"/>
         <v>283</v>
       </c>
       <c r="L63" s="5">
-        <f t="shared" si="88"/>
+        <f t="shared" si="92"/>
         <v>327</v>
       </c>
       <c r="M63" s="5">
-        <f t="shared" ref="M63:N63" si="89">M59-M62</f>
+        <f t="shared" ref="M63:N63" si="93">M59-M62</f>
         <v>809</v>
       </c>
       <c r="N63" s="5">
-        <f t="shared" si="89"/>
+        <f t="shared" si="93"/>
         <v>575</v>
       </c>
       <c r="O63" s="5">
-        <f t="shared" ref="O63:R63" si="90">O59-O62</f>
+        <f t="shared" ref="O63:R63" si="94">O59-O62</f>
         <v>493</v>
       </c>
       <c r="P63" s="5">
-        <f t="shared" si="90"/>
+        <f t="shared" si="94"/>
         <v>1335</v>
       </c>
       <c r="Q63" s="5">
-        <f t="shared" si="90"/>
+        <f t="shared" si="94"/>
         <v>2055</v>
       </c>
       <c r="R63" s="5">
-        <f t="shared" si="90"/>
+        <f t="shared" si="94"/>
         <v>2613</v>
       </c>
       <c r="S63" s="5">
@@ -6830,7 +6896,7 @@
         <v>3688</v>
       </c>
       <c r="V63" s="5">
-        <f t="shared" ref="V63:AD63" si="91">V59-V62</f>
+        <f t="shared" ref="V63:AD63" si="95">V59-V62</f>
         <v>3662.7999999999984</v>
       </c>
       <c r="W63" s="5">
@@ -6838,31 +6904,31 @@
         <v>2664</v>
       </c>
       <c r="X63" s="5">
-        <f t="shared" si="91"/>
+        <f t="shared" si="95"/>
         <v>2399</v>
       </c>
       <c r="Y63" s="5">
-        <f t="shared" si="91"/>
+        <f t="shared" si="95"/>
         <v>1764</v>
       </c>
       <c r="Z63" s="5">
-        <f t="shared" si="91"/>
+        <f t="shared" si="95"/>
         <v>2064</v>
       </c>
       <c r="AA63" s="5">
-        <f t="shared" si="91"/>
+        <f t="shared" si="95"/>
         <v>1171</v>
       </c>
       <c r="AB63" s="5">
-        <f t="shared" si="91"/>
+        <f t="shared" si="95"/>
         <v>2227</v>
       </c>
       <c r="AC63" s="5">
-        <f t="shared" si="91"/>
+        <f t="shared" si="95"/>
         <v>1446.3708570241197</v>
       </c>
       <c r="AD63" s="5">
-        <f t="shared" si="91"/>
+        <f t="shared" si="95"/>
         <v>1820.3546705981557</v>
       </c>
       <c r="AE63" s="5">
@@ -6881,20 +6947,23 @@
         <f>AH59-AH62</f>
         <v>1409</v>
       </c>
-      <c r="AI63" s="5"/>
+      <c r="AI63" s="5">
+        <f>AI59-AI62</f>
+        <v>941</v>
+      </c>
       <c r="AJ63" s="5"/>
       <c r="AK63" s="5"/>
       <c r="AL63" s="5"/>
       <c r="AW63" s="5">
-        <f t="shared" ref="AW63:AX63" si="92">AW59-AW62</f>
+        <f t="shared" ref="AW63:AX63" si="96">AW59-AW62</f>
         <v>12705.850000000002</v>
       </c>
       <c r="AX63" s="5">
-        <f t="shared" si="92"/>
+        <f t="shared" si="96"/>
         <v>8891</v>
       </c>
       <c r="AY63" s="5">
-        <f t="shared" ref="AY63:BE63" si="93">AY59-AY62</f>
+        <f t="shared" ref="AY63:BE63" si="97">AY59-AY62</f>
         <v>7076</v>
       </c>
       <c r="AZ63" s="5">
@@ -6902,43 +6971,43 @@
         <v>4355</v>
       </c>
       <c r="BA63" s="5">
-        <f t="shared" si="93"/>
+        <f t="shared" si="97"/>
         <v>6419.5239216410082</v>
       </c>
       <c r="BB63" s="5">
-        <f t="shared" si="93"/>
+        <f t="shared" si="97"/>
         <v>10202.874421964862</v>
       </c>
       <c r="BC63" s="5">
-        <f t="shared" si="93"/>
+        <f t="shared" si="97"/>
         <v>16837.455852431478</v>
       </c>
       <c r="BD63" s="5">
-        <f t="shared" si="93"/>
+        <f t="shared" si="97"/>
         <v>24031.575069406899</v>
       </c>
       <c r="BE63" s="5">
-        <f t="shared" si="93"/>
+        <f t="shared" si="97"/>
         <v>31014.635766691335</v>
       </c>
       <c r="BF63" s="5">
-        <f t="shared" ref="BF63:BJ63" si="94">BF59-BF62</f>
+        <f t="shared" ref="BF63:BJ63" si="98">BF59-BF62</f>
         <v>34203.675324654003</v>
       </c>
       <c r="BG63" s="5">
-        <f t="shared" si="94"/>
+        <f t="shared" si="98"/>
         <v>37675.541046164137</v>
       </c>
       <c r="BH63" s="5">
-        <f t="shared" si="94"/>
+        <f t="shared" si="98"/>
         <v>41454.047337194657</v>
       </c>
       <c r="BI63" s="5">
-        <f t="shared" si="94"/>
+        <f t="shared" si="98"/>
         <v>45564.971159395172</v>
       </c>
       <c r="BJ63" s="5">
-        <f t="shared" si="94"/>
+        <f t="shared" si="98"/>
         <v>50036.212339267127</v>
       </c>
     </row>
@@ -7056,12 +7125,15 @@
         <f>+AZ64-SUM(AE64:AG64)</f>
         <v>-228</v>
       </c>
-      <c r="AI64" s="5"/>
+      <c r="AI64" s="5">
+        <f>434-92-535</f>
+        <v>-193</v>
+      </c>
       <c r="AJ64" s="5"/>
       <c r="AK64" s="5"/>
       <c r="AL64" s="5"/>
       <c r="AX64" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="57"/>
         <v>1082</v>
       </c>
       <c r="AY64" s="4">
@@ -7073,43 +7145,43 @@
         <v>923</v>
       </c>
       <c r="BA64" s="4">
-        <f>AZ94*$BL$81</f>
+        <f t="shared" ref="BA64:BJ64" si="99">AZ94*$BL$81</f>
         <v>3474.9</v>
       </c>
       <c r="BB64" s="4">
-        <f>BA94*$BL$81</f>
+        <f t="shared" si="99"/>
         <v>4315.9260333394859</v>
       </c>
       <c r="BC64" s="4">
-        <f>BB94*$BL$81</f>
+        <f t="shared" si="99"/>
         <v>5550.0240720403563</v>
       </c>
       <c r="BD64" s="4">
-        <f>BC94*$BL$81</f>
+        <f t="shared" si="99"/>
         <v>7452.9598656204616</v>
       </c>
       <c r="BE64" s="4">
-        <f>BD94*$BL$81</f>
+        <f t="shared" si="99"/>
         <v>10129.145335097788</v>
       </c>
       <c r="BF64" s="4">
-        <f>BE94*$BL$81</f>
+        <f t="shared" si="99"/>
         <v>13626.366728749863</v>
       </c>
       <c r="BG64" s="4">
-        <f>BF94*$BL$81</f>
+        <f t="shared" si="99"/>
         <v>17691.920303289193</v>
       </c>
       <c r="BH64" s="4">
-        <f>BG94*$BL$81</f>
+        <f t="shared" si="99"/>
         <v>22398.154517992723</v>
       </c>
       <c r="BI64" s="4">
-        <f>BH94*$BL$81</f>
+        <f t="shared" si="99"/>
         <v>27825.591675683649</v>
       </c>
       <c r="BJ64" s="4">
-        <f>BI94*$BL$81</f>
+        <f t="shared" si="99"/>
         <v>34063.789516665347</v>
       </c>
     </row>
@@ -7122,51 +7194,51 @@
       <c r="E65" s="5"/>
       <c r="F65" s="5"/>
       <c r="G65" s="5">
-        <f t="shared" ref="G65:N65" si="95">G63+G64</f>
+        <f t="shared" ref="G65:N65" si="100">G63+G64</f>
         <v>-601</v>
       </c>
       <c r="H65" s="5">
-        <f t="shared" si="95"/>
+        <f t="shared" si="100"/>
         <v>-253</v>
       </c>
       <c r="I65" s="5">
-        <f t="shared" si="95"/>
+        <f t="shared" si="100"/>
         <v>176</v>
       </c>
       <c r="J65" s="5">
-        <f t="shared" si="95"/>
+        <f t="shared" si="100"/>
         <v>160</v>
       </c>
       <c r="K65" s="5">
-        <f t="shared" si="95"/>
+        <f t="shared" si="100"/>
         <v>70</v>
       </c>
       <c r="L65" s="5">
-        <f t="shared" si="95"/>
+        <f t="shared" si="100"/>
         <v>150</v>
       </c>
       <c r="M65" s="5">
-        <f t="shared" si="95"/>
+        <f t="shared" si="100"/>
         <v>555</v>
       </c>
       <c r="N65" s="5">
-        <f t="shared" si="95"/>
+        <f t="shared" si="100"/>
         <v>379</v>
       </c>
       <c r="O65" s="5">
-        <f t="shared" ref="O65:R65" si="96">O63+O64</f>
+        <f t="shared" ref="O65:R65" si="101">O63+O64</f>
         <v>432</v>
       </c>
       <c r="P65" s="5">
-        <f t="shared" si="96"/>
+        <f t="shared" si="101"/>
         <v>1316</v>
       </c>
       <c r="Q65" s="5">
-        <f t="shared" si="96"/>
+        <f t="shared" si="101"/>
         <v>1933</v>
       </c>
       <c r="R65" s="5">
-        <f t="shared" si="96"/>
+        <f t="shared" si="101"/>
         <v>2635</v>
       </c>
       <c r="S65" s="5">
@@ -7182,58 +7254,61 @@
         <v>3636</v>
       </c>
       <c r="V65" s="5">
-        <f t="shared" ref="V65:AH65" si="97">V63+V64</f>
+        <f t="shared" ref="V65:AI65" si="102">V63+V64</f>
         <v>3744.7999999999984</v>
       </c>
       <c r="W65" s="5">
-        <f t="shared" si="97"/>
+        <f t="shared" si="102"/>
         <v>2800</v>
       </c>
       <c r="X65" s="5">
-        <f t="shared" si="97"/>
+        <f t="shared" si="102"/>
         <v>2937</v>
       </c>
       <c r="Y65" s="5">
-        <f t="shared" si="97"/>
+        <f t="shared" si="102"/>
         <v>2045</v>
       </c>
       <c r="Z65" s="5">
-        <f t="shared" si="97"/>
+        <f t="shared" si="102"/>
         <v>2191</v>
       </c>
       <c r="AA65" s="5">
-        <f t="shared" si="97"/>
+        <f t="shared" si="102"/>
         <v>1553</v>
       </c>
       <c r="AB65" s="5">
-        <f t="shared" si="97"/>
+        <f t="shared" si="102"/>
         <v>2509</v>
       </c>
       <c r="AC65" s="5">
-        <f t="shared" si="97"/>
+        <f t="shared" si="102"/>
         <v>1446.3708570241197</v>
       </c>
       <c r="AD65" s="5">
-        <f t="shared" si="97"/>
+        <f t="shared" si="102"/>
         <v>1820.3546705981557</v>
       </c>
       <c r="AE65" s="5">
-        <f t="shared" si="97"/>
+        <f t="shared" si="102"/>
         <v>589</v>
       </c>
       <c r="AF65" s="5">
-        <f t="shared" si="97"/>
+        <f t="shared" si="102"/>
         <v>1549</v>
       </c>
       <c r="AG65" s="5">
-        <f t="shared" si="97"/>
+        <f t="shared" si="102"/>
         <v>1959</v>
       </c>
       <c r="AH65" s="5">
-        <f t="shared" si="97"/>
+        <f t="shared" si="102"/>
         <v>1181</v>
       </c>
-      <c r="AI65" s="5"/>
+      <c r="AI65" s="5">
+        <f t="shared" si="102"/>
+        <v>748</v>
+      </c>
       <c r="AJ65" s="5"/>
       <c r="AK65" s="5"/>
       <c r="AL65" s="5"/>
@@ -7242,51 +7317,51 @@
         <v>9973</v>
       </c>
       <c r="AY65" s="4">
-        <f t="shared" ref="AY65:BJ65" si="98">+AY63+AY64</f>
+        <f t="shared" ref="AY65:BJ65" si="103">+AY63+AY64</f>
         <v>8990</v>
       </c>
       <c r="AZ65" s="4">
-        <f t="shared" si="98"/>
+        <f t="shared" si="103"/>
         <v>5278</v>
       </c>
       <c r="BA65" s="4">
-        <f t="shared" si="98"/>
+        <f t="shared" si="103"/>
         <v>9894.4239216410078</v>
       </c>
       <c r="BB65" s="4">
-        <f t="shared" si="98"/>
+        <f t="shared" si="103"/>
         <v>14518.800455304347</v>
       </c>
       <c r="BC65" s="4">
-        <f t="shared" si="98"/>
+        <f t="shared" si="103"/>
         <v>22387.479924471834</v>
       </c>
       <c r="BD65" s="4">
-        <f t="shared" si="98"/>
+        <f t="shared" si="103"/>
         <v>31484.534935027361</v>
       </c>
       <c r="BE65" s="4">
-        <f t="shared" si="98"/>
+        <f t="shared" si="103"/>
         <v>41143.781101789122</v>
       </c>
       <c r="BF65" s="4">
-        <f t="shared" si="98"/>
+        <f t="shared" si="103"/>
         <v>47830.042053403864</v>
       </c>
       <c r="BG65" s="4">
-        <f t="shared" si="98"/>
+        <f t="shared" si="103"/>
         <v>55367.461349453326</v>
       </c>
       <c r="BH65" s="4">
-        <f t="shared" si="98"/>
+        <f t="shared" si="103"/>
         <v>63852.201855187377</v>
       </c>
       <c r="BI65" s="4">
-        <f t="shared" si="98"/>
+        <f t="shared" si="103"/>
         <v>73390.562835078817</v>
       </c>
       <c r="BJ65" s="4">
-        <f t="shared" si="98"/>
+        <f t="shared" si="103"/>
         <v>84100.001855932467</v>
       </c>
     </row>
@@ -7406,12 +7481,15 @@
         <f>+AZ66-SUM(AE66:AG66)</f>
         <v>357</v>
       </c>
-      <c r="AI66" s="5"/>
+      <c r="AI66" s="5">
+        <f>257+14</f>
+        <v>271</v>
+      </c>
       <c r="AJ66" s="5"/>
       <c r="AK66" s="5"/>
       <c r="AL66" s="5"/>
       <c r="AX66" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="57"/>
         <v>728</v>
       </c>
       <c r="AY66" s="4">
@@ -7423,43 +7501,43 @@
         <v>1484</v>
       </c>
       <c r="BA66" s="4">
-        <f t="shared" ref="BA66:BE66" si="99">+BA65*0.15</f>
+        <f t="shared" ref="BA66:BE66" si="104">+BA65*0.15</f>
         <v>1484.1635882461512</v>
       </c>
       <c r="BB66" s="4">
-        <f t="shared" si="99"/>
+        <f t="shared" si="104"/>
         <v>2177.8200682956517</v>
       </c>
       <c r="BC66" s="4">
-        <f t="shared" si="99"/>
+        <f t="shared" si="104"/>
         <v>3358.121988670775</v>
       </c>
       <c r="BD66" s="4">
-        <f t="shared" si="99"/>
+        <f t="shared" si="104"/>
         <v>4722.6802402541043</v>
       </c>
       <c r="BE66" s="4">
-        <f t="shared" si="99"/>
+        <f t="shared" si="104"/>
         <v>6171.5671652683677</v>
       </c>
       <c r="BF66" s="4">
-        <f t="shared" ref="BF66:BJ66" si="100">+BF65*0.15</f>
+        <f t="shared" ref="BF66:BJ66" si="105">+BF65*0.15</f>
         <v>7174.5063080105792</v>
       </c>
       <c r="BG66" s="4">
-        <f t="shared" si="100"/>
+        <f t="shared" si="105"/>
         <v>8305.1192024179982</v>
       </c>
       <c r="BH66" s="4">
-        <f t="shared" si="100"/>
+        <f t="shared" si="105"/>
         <v>9577.8302782781066</v>
       </c>
       <c r="BI66" s="4">
-        <f t="shared" si="100"/>
+        <f t="shared" si="105"/>
         <v>11008.584425261823</v>
       </c>
       <c r="BJ66" s="4">
-        <f t="shared" si="100"/>
+        <f t="shared" si="105"/>
         <v>12615.000278389869</v>
       </c>
     </row>
@@ -7472,51 +7550,51 @@
       <c r="E67" s="5"/>
       <c r="F67" s="5"/>
       <c r="G67" s="5">
-        <f t="shared" ref="G67:N67" si="101">G65-G66</f>
+        <f t="shared" ref="G67:N67" si="106">G65-G66</f>
         <v>-658</v>
       </c>
       <c r="H67" s="5">
-        <f t="shared" si="101"/>
+        <f t="shared" si="106"/>
         <v>-291</v>
       </c>
       <c r="I67" s="5">
-        <f t="shared" si="101"/>
+        <f t="shared" si="106"/>
         <v>143</v>
       </c>
       <c r="J67" s="5">
-        <f t="shared" si="101"/>
+        <f t="shared" si="106"/>
         <v>91</v>
       </c>
       <c r="K67" s="5">
-        <f t="shared" si="101"/>
+        <f t="shared" si="106"/>
         <v>16</v>
       </c>
       <c r="L67" s="5">
-        <f t="shared" si="101"/>
+        <f t="shared" si="106"/>
         <v>104</v>
       </c>
       <c r="M67" s="5">
-        <f t="shared" si="101"/>
+        <f t="shared" si="106"/>
         <v>300</v>
       </c>
       <c r="N67" s="5">
-        <f t="shared" si="101"/>
+        <f t="shared" si="106"/>
         <v>270</v>
       </c>
       <c r="O67" s="5">
-        <f t="shared" ref="O67:R67" si="102">O65-O66</f>
+        <f t="shared" ref="O67:R67" si="107">O65-O66</f>
         <v>337</v>
       </c>
       <c r="P67" s="5">
-        <f t="shared" si="102"/>
+        <f t="shared" si="107"/>
         <v>1165</v>
       </c>
       <c r="Q67" s="5">
-        <f t="shared" si="102"/>
+        <f t="shared" si="107"/>
         <v>1669</v>
       </c>
       <c r="R67" s="5">
-        <f t="shared" si="102"/>
+        <f t="shared" si="107"/>
         <v>2321</v>
       </c>
       <c r="S67" s="5">
@@ -7532,58 +7610,61 @@
         <v>3331</v>
       </c>
       <c r="V67" s="5">
-        <f t="shared" ref="V67:AH67" si="103">V65-V66</f>
+        <f t="shared" ref="V67:AI67" si="108">V65-V66</f>
         <v>3468.7999999999984</v>
       </c>
       <c r="W67" s="5">
-        <f t="shared" si="103"/>
+        <f t="shared" si="108"/>
         <v>2513</v>
       </c>
       <c r="X67" s="5">
-        <f t="shared" si="103"/>
+        <f t="shared" si="108"/>
         <v>2703</v>
       </c>
       <c r="Y67" s="5">
-        <f t="shared" si="103"/>
+        <f t="shared" si="108"/>
         <v>1853</v>
       </c>
       <c r="Z67" s="5">
-        <f t="shared" si="103"/>
+        <f t="shared" si="108"/>
         <v>2176</v>
       </c>
       <c r="AA67" s="5">
-        <f t="shared" si="103"/>
+        <f t="shared" si="108"/>
         <v>1129</v>
       </c>
       <c r="AB67" s="5">
-        <f t="shared" si="103"/>
+        <f t="shared" si="108"/>
         <v>2100</v>
       </c>
       <c r="AC67" s="5">
-        <f t="shared" si="103"/>
+        <f t="shared" si="108"/>
         <v>1157.0966856192958</v>
       </c>
       <c r="AD67" s="5">
-        <f t="shared" si="103"/>
+        <f t="shared" si="108"/>
         <v>1456.2837364785246</v>
       </c>
       <c r="AE67" s="5">
-        <f t="shared" si="103"/>
+        <f t="shared" si="108"/>
         <v>409</v>
       </c>
       <c r="AF67" s="5">
-        <f t="shared" si="103"/>
+        <f t="shared" si="108"/>
         <v>1172</v>
       </c>
       <c r="AG67" s="5">
-        <f t="shared" si="103"/>
+        <f t="shared" si="108"/>
         <v>1389</v>
       </c>
       <c r="AH67" s="5">
-        <f t="shared" si="103"/>
+        <f t="shared" si="108"/>
         <v>824</v>
       </c>
-      <c r="AI67" s="5"/>
+      <c r="AI67" s="5">
+        <f t="shared" si="108"/>
+        <v>477</v>
+      </c>
       <c r="AJ67" s="5"/>
       <c r="AK67" s="5"/>
       <c r="AL67" s="5"/>
@@ -7592,255 +7673,255 @@
         <v>9245</v>
       </c>
       <c r="AY67" s="4">
-        <f t="shared" ref="AY67" si="104">+AY65-AY66</f>
+        <f t="shared" ref="AY67" si="109">+AY65-AY66</f>
         <v>7091</v>
       </c>
       <c r="AZ67" s="4">
-        <f t="shared" ref="AZ67:BE67" si="105">+AZ65-AZ66</f>
+        <f t="shared" ref="AZ67:BE67" si="110">+AZ65-AZ66</f>
         <v>3794</v>
       </c>
       <c r="BA67" s="4">
-        <f t="shared" si="105"/>
+        <f t="shared" si="110"/>
         <v>8410.2603333948573</v>
       </c>
       <c r="BB67" s="4">
-        <f t="shared" si="105"/>
+        <f t="shared" si="110"/>
         <v>12340.980387008694</v>
       </c>
       <c r="BC67" s="4">
-        <f t="shared" si="105"/>
+        <f t="shared" si="110"/>
         <v>19029.357935801061</v>
       </c>
       <c r="BD67" s="4">
-        <f t="shared" si="105"/>
+        <f t="shared" si="110"/>
         <v>26761.854694773258</v>
       </c>
       <c r="BE67" s="4">
-        <f t="shared" si="105"/>
+        <f t="shared" si="110"/>
         <v>34972.213936520755</v>
       </c>
       <c r="BF67" s="4">
-        <f t="shared" ref="BF67:BJ67" si="106">+BF65-BF66</f>
+        <f t="shared" ref="BF67:BJ67" si="111">+BF65-BF66</f>
         <v>40655.535745393281</v>
       </c>
       <c r="BG67" s="4">
-        <f t="shared" si="106"/>
+        <f t="shared" si="111"/>
         <v>47062.342147035328</v>
       </c>
       <c r="BH67" s="4">
-        <f t="shared" si="106"/>
+        <f t="shared" si="111"/>
         <v>54274.371576909267</v>
       </c>
       <c r="BI67" s="4">
-        <f t="shared" si="106"/>
+        <f t="shared" si="111"/>
         <v>62381.978409816991</v>
       </c>
       <c r="BJ67" s="4">
-        <f t="shared" si="106"/>
+        <f t="shared" si="111"/>
         <v>71485.0015775426</v>
       </c>
       <c r="BK67" s="4">
-        <f t="shared" ref="BK67:CP67" si="107">BJ67*(1+$BL$78)</f>
+        <f t="shared" ref="BK67:CP67" si="112">BJ67*(1+$BL$78)</f>
         <v>70770.151561767168</v>
       </c>
       <c r="BL67" s="4">
-        <f t="shared" si="107"/>
+        <f t="shared" si="112"/>
         <v>70062.45004614949</v>
       </c>
       <c r="BM67" s="4">
-        <f t="shared" si="107"/>
+        <f t="shared" si="112"/>
         <v>69361.825545688</v>
       </c>
       <c r="BN67" s="4">
-        <f t="shared" si="107"/>
+        <f t="shared" si="112"/>
         <v>68668.207290231119</v>
       </c>
       <c r="BO67" s="4">
-        <f t="shared" si="107"/>
+        <f t="shared" si="112"/>
         <v>67981.525217328803</v>
       </c>
       <c r="BP67" s="4">
-        <f t="shared" si="107"/>
+        <f t="shared" si="112"/>
         <v>67301.709965155518</v>
       </c>
       <c r="BQ67" s="4">
-        <f t="shared" si="107"/>
+        <f t="shared" si="112"/>
         <v>66628.692865503966</v>
       </c>
       <c r="BR67" s="4">
-        <f t="shared" si="107"/>
+        <f t="shared" si="112"/>
         <v>65962.405936848925</v>
       </c>
       <c r="BS67" s="4">
-        <f t="shared" si="107"/>
+        <f t="shared" si="112"/>
         <v>65302.781877480433</v>
       </c>
       <c r="BT67" s="4">
-        <f t="shared" si="107"/>
+        <f t="shared" si="112"/>
         <v>64649.754058705628</v>
       </c>
       <c r="BU67" s="4">
-        <f t="shared" si="107"/>
+        <f t="shared" si="112"/>
         <v>64003.256518118571</v>
       </c>
       <c r="BV67" s="4">
-        <f t="shared" si="107"/>
+        <f t="shared" si="112"/>
         <v>63363.223952937384</v>
       </c>
       <c r="BW67" s="4">
-        <f t="shared" si="107"/>
+        <f t="shared" si="112"/>
         <v>62729.591713408008</v>
       </c>
       <c r="BX67" s="4">
-        <f t="shared" si="107"/>
+        <f t="shared" si="112"/>
         <v>62102.295796273931</v>
       </c>
       <c r="BY67" s="4">
-        <f t="shared" si="107"/>
+        <f t="shared" si="112"/>
         <v>61481.27283831119</v>
       </c>
       <c r="BZ67" s="4">
-        <f t="shared" si="107"/>
+        <f t="shared" si="112"/>
         <v>60866.460109928077</v>
       </c>
       <c r="CA67" s="4">
-        <f t="shared" si="107"/>
+        <f t="shared" si="112"/>
         <v>60257.795508828793</v>
       </c>
       <c r="CB67" s="4">
-        <f t="shared" si="107"/>
+        <f t="shared" si="112"/>
         <v>59655.217553740506</v>
       </c>
       <c r="CC67" s="4">
-        <f t="shared" si="107"/>
+        <f t="shared" si="112"/>
         <v>59058.665378203099</v>
       </c>
       <c r="CD67" s="4">
-        <f t="shared" si="107"/>
+        <f t="shared" si="112"/>
         <v>58468.078724421066</v>
       </c>
       <c r="CE67" s="4">
-        <f t="shared" si="107"/>
+        <f t="shared" si="112"/>
         <v>57883.397937176858</v>
       </c>
       <c r="CF67" s="4">
-        <f t="shared" si="107"/>
+        <f t="shared" si="112"/>
         <v>57304.56395780509</v>
       </c>
       <c r="CG67" s="4">
-        <f t="shared" si="107"/>
+        <f t="shared" si="112"/>
         <v>56731.518318227041</v>
       </c>
       <c r="CH67" s="4">
-        <f t="shared" si="107"/>
+        <f t="shared" si="112"/>
         <v>56164.203135044772</v>
       </c>
       <c r="CI67" s="4">
-        <f t="shared" si="107"/>
+        <f t="shared" si="112"/>
         <v>55602.561103694323</v>
       </c>
       <c r="CJ67" s="4">
-        <f t="shared" si="107"/>
+        <f t="shared" si="112"/>
         <v>55046.535492657378</v>
       </c>
       <c r="CK67" s="4">
-        <f t="shared" si="107"/>
+        <f t="shared" si="112"/>
         <v>54496.070137730807</v>
       </c>
       <c r="CL67" s="4">
-        <f t="shared" si="107"/>
+        <f t="shared" si="112"/>
         <v>53951.109436353501</v>
       </c>
       <c r="CM67" s="4">
-        <f t="shared" si="107"/>
+        <f t="shared" si="112"/>
         <v>53411.598341989964</v>
       </c>
       <c r="CN67" s="4">
-        <f t="shared" si="107"/>
+        <f t="shared" si="112"/>
         <v>52877.482358570065</v>
       </c>
       <c r="CO67" s="4">
-        <f t="shared" si="107"/>
+        <f t="shared" si="112"/>
         <v>52348.707534984365</v>
       </c>
       <c r="CP67" s="4">
-        <f t="shared" si="107"/>
+        <f t="shared" si="112"/>
         <v>51825.220459634518</v>
       </c>
       <c r="CQ67" s="4">
-        <f t="shared" ref="CQ67:DI67" si="108">CP67*(1+$BL$78)</f>
+        <f t="shared" ref="CQ67:DI67" si="113">CP67*(1+$BL$78)</f>
         <v>51306.968255038169</v>
       </c>
       <c r="CR67" s="4">
-        <f t="shared" si="108"/>
+        <f t="shared" si="113"/>
         <v>50793.898572487786</v>
       </c>
       <c r="CS67" s="4">
-        <f t="shared" si="108"/>
+        <f t="shared" si="113"/>
         <v>50285.95958676291</v>
       </c>
       <c r="CT67" s="4">
-        <f t="shared" si="108"/>
+        <f t="shared" si="113"/>
         <v>49783.09999089528</v>
       </c>
       <c r="CU67" s="4">
-        <f t="shared" si="108"/>
+        <f t="shared" si="113"/>
         <v>49285.268990986326</v>
       </c>
       <c r="CV67" s="4">
-        <f t="shared" si="108"/>
+        <f t="shared" si="113"/>
         <v>48792.416301076461</v>
       </c>
       <c r="CW67" s="4">
-        <f t="shared" si="108"/>
+        <f t="shared" si="113"/>
         <v>48304.492138065696</v>
       </c>
       <c r="CX67" s="4">
-        <f t="shared" si="108"/>
+        <f t="shared" si="113"/>
         <v>47821.447216685039</v>
       </c>
       <c r="CY67" s="4">
-        <f t="shared" si="108"/>
+        <f t="shared" si="113"/>
         <v>47343.232744518187</v>
       </c>
       <c r="CZ67" s="4">
-        <f t="shared" si="108"/>
+        <f t="shared" si="113"/>
         <v>46869.800417073006</v>
       </c>
       <c r="DA67" s="4">
-        <f t="shared" si="108"/>
+        <f t="shared" si="113"/>
         <v>46401.102412902277</v>
       </c>
       <c r="DB67" s="4">
-        <f t="shared" si="108"/>
+        <f t="shared" si="113"/>
         <v>45937.091388773253</v>
       </c>
       <c r="DC67" s="4">
-        <f t="shared" si="108"/>
+        <f t="shared" si="113"/>
         <v>45477.720474885522</v>
       </c>
       <c r="DD67" s="4">
-        <f t="shared" si="108"/>
+        <f t="shared" si="113"/>
         <v>45022.943270136668</v>
       </c>
       <c r="DE67" s="4">
-        <f t="shared" si="108"/>
+        <f t="shared" si="113"/>
         <v>44572.713837435302</v>
       </c>
       <c r="DF67" s="4">
-        <f t="shared" si="108"/>
+        <f t="shared" si="113"/>
         <v>44126.986699060952</v>
       </c>
       <c r="DG67" s="4">
-        <f t="shared" si="108"/>
+        <f t="shared" si="113"/>
         <v>43685.716832070342</v>
       </c>
       <c r="DH67" s="4">
-        <f t="shared" si="108"/>
+        <f t="shared" si="113"/>
         <v>43248.859663749638</v>
       </c>
       <c r="DI67" s="4">
-        <f t="shared" si="108"/>
+        <f t="shared" si="113"/>
         <v>42816.371067112144</v>
       </c>
     </row>
@@ -7853,118 +7934,121 @@
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" s="3">
-        <f t="shared" ref="G68:K68" si="109">G67/G69</f>
+        <f t="shared" ref="G68:K68" si="114">G67/G69</f>
         <v>-0.76069364161849706</v>
       </c>
       <c r="H68" s="3">
-        <f t="shared" si="109"/>
+        <f t="shared" si="114"/>
         <v>-0.32881355932203388</v>
       </c>
       <c r="I68" s="3">
-        <f t="shared" si="109"/>
+        <f t="shared" si="114"/>
         <v>0.15509761388286333</v>
       </c>
       <c r="J68" s="3">
-        <f t="shared" si="109"/>
+        <f t="shared" si="114"/>
         <v>9.8913043478260868E-2</v>
       </c>
       <c r="K68" s="3">
-        <f t="shared" si="109"/>
+        <f t="shared" si="114"/>
         <v>1.7112299465240642E-2</v>
       </c>
       <c r="L68" s="3">
-        <f t="shared" ref="L68" si="110">L67/L69</f>
+        <f t="shared" ref="L68" si="115">L67/L69</f>
         <v>0.10048309178743961</v>
       </c>
       <c r="M68" s="3">
-        <f t="shared" ref="M68:O68" si="111">M67/M69</f>
+        <f t="shared" ref="M68:O68" si="116">M67/M69</f>
         <v>0.27149321266968324</v>
       </c>
       <c r="N68" s="3">
-        <f t="shared" si="111"/>
+        <f t="shared" si="116"/>
         <v>0.2402135231316726</v>
       </c>
       <c r="O68" s="3">
-        <f t="shared" si="111"/>
+        <f t="shared" si="116"/>
         <v>0.29744042365401591</v>
       </c>
       <c r="P68" s="3">
-        <f t="shared" ref="P68" si="112">P67/P69</f>
+        <f t="shared" ref="P68" si="117">P67/P69</f>
         <v>1.0411081322609472</v>
       </c>
       <c r="Q68" s="3">
-        <f t="shared" ref="Q68" si="113">Q67/Q69</f>
+        <f t="shared" ref="Q68" si="118">Q67/Q69</f>
         <v>1.4861976847729297</v>
       </c>
       <c r="R68" s="3">
-        <f t="shared" ref="R68" si="114">R67/R69</f>
+        <f t="shared" ref="R68" si="119">R67/R69</f>
         <v>2.044933920704846</v>
       </c>
       <c r="S68" s="3">
-        <f t="shared" ref="S68:U68" si="115">S67/S69</f>
+        <f t="shared" ref="S68:U68" si="120">S67/S69</f>
         <v>2.867761452031115</v>
       </c>
       <c r="T68" s="3">
-        <f t="shared" si="115"/>
+        <f t="shared" si="120"/>
         <v>2.032900432900433</v>
       </c>
       <c r="U68" s="3">
-        <f t="shared" si="115"/>
+        <f t="shared" si="120"/>
         <v>0.96049596309111884</v>
       </c>
       <c r="V68" s="3">
-        <f t="shared" ref="V68:AH68" si="116">V67/V69</f>
+        <f t="shared" ref="V68:AI68" si="121">V67/V69</f>
         <v>0.99936617689426632</v>
       </c>
       <c r="W68" s="3">
-        <f t="shared" si="116"/>
+        <f t="shared" si="121"/>
         <v>0.7246251441753172</v>
       </c>
       <c r="X68" s="3">
-        <f t="shared" si="116"/>
+        <f t="shared" si="121"/>
         <v>0.77717078780908566</v>
       </c>
       <c r="Y68" s="3">
-        <f t="shared" si="116"/>
+        <f t="shared" si="121"/>
         <v>0.53048955052963065</v>
       </c>
       <c r="Z68" s="3">
-        <f t="shared" si="116"/>
+        <f t="shared" si="121"/>
         <v>0.62313860252004583</v>
       </c>
       <c r="AA68" s="3">
-        <f t="shared" si="116"/>
+        <f t="shared" si="121"/>
         <v>0.32405281285878301</v>
       </c>
       <c r="AB68" s="3">
-        <f t="shared" si="116"/>
+        <f t="shared" si="121"/>
         <v>0.60327492099971269</v>
       </c>
       <c r="AC68" s="3">
-        <f t="shared" si="116"/>
+        <f t="shared" si="121"/>
         <v>0.33240352933619532</v>
       </c>
       <c r="AD68" s="3">
-        <f t="shared" si="116"/>
+        <f t="shared" si="121"/>
         <v>0.41835212194154686</v>
       </c>
       <c r="AE68" s="3">
-        <f t="shared" si="116"/>
+        <f t="shared" si="121"/>
         <v>0.12709757613424488</v>
       </c>
       <c r="AF68" s="3">
-        <f t="shared" si="116"/>
+        <f t="shared" si="121"/>
         <v>0.36363636363636365</v>
       </c>
       <c r="AG68" s="3">
-        <f t="shared" si="116"/>
+        <f t="shared" si="121"/>
         <v>0.43043074062596837</v>
       </c>
       <c r="AH68" s="3">
-        <f t="shared" si="116"/>
+        <f t="shared" si="121"/>
         <v>0.25534552215680201</v>
       </c>
-      <c r="AI68" s="3"/>
+      <c r="AI68" s="3">
+        <f t="shared" si="121"/>
+        <v>0.14795285359801488</v>
+      </c>
       <c r="AJ68" s="3"/>
       <c r="AK68" s="3"/>
       <c r="AL68" s="3"/>
@@ -7973,51 +8057,51 @@
         <v>2.6545115210681214</v>
       </c>
       <c r="AY68" s="19">
-        <f t="shared" ref="AY68:BE68" si="117">+AY67/AY69</f>
+        <f t="shared" ref="AY68:BE68" si="122">+AY67/AY69</f>
         <v>2.2180168908351581</v>
       </c>
       <c r="AZ68" s="19">
-        <f t="shared" si="117"/>
+        <f t="shared" si="122"/>
         <v>1.1764341085271317</v>
       </c>
       <c r="BA68" s="19">
-        <f t="shared" si="117"/>
+        <f t="shared" si="122"/>
         <v>2.6078326615177851</v>
       </c>
       <c r="BB68" s="19">
-        <f t="shared" si="117"/>
+        <f t="shared" si="122"/>
         <v>3.826660585118975</v>
       </c>
       <c r="BC68" s="19">
-        <f t="shared" si="117"/>
+        <f t="shared" si="122"/>
         <v>5.9005761041243598</v>
       </c>
       <c r="BD68" s="19">
-        <f t="shared" si="117"/>
+        <f t="shared" si="122"/>
         <v>8.2982495177591495</v>
       </c>
       <c r="BE68" s="19">
-        <f t="shared" si="117"/>
+        <f t="shared" si="122"/>
         <v>10.844097344657598</v>
       </c>
       <c r="BF68" s="19">
-        <f t="shared" ref="BF68:BJ68" si="118">+BF67/BF69</f>
+        <f t="shared" ref="BF68:BJ68" si="123">+BF67/BF69</f>
         <v>12.606367672990165</v>
       </c>
       <c r="BG68" s="19">
-        <f t="shared" si="118"/>
+        <f t="shared" si="123"/>
         <v>14.592974309158242</v>
       </c>
       <c r="BH68" s="19">
-        <f t="shared" si="118"/>
+        <f t="shared" si="123"/>
         <v>16.829262504467991</v>
       </c>
       <c r="BI68" s="19">
-        <f t="shared" si="118"/>
+        <f t="shared" si="123"/>
         <v>19.343249119323097</v>
       </c>
       <c r="BJ68" s="19">
-        <f t="shared" si="118"/>
+        <f t="shared" si="123"/>
         <v>22.165891962028713</v>
       </c>
     </row>
@@ -8120,7 +8204,9 @@
       <c r="AH69" s="5">
         <v>3227</v>
       </c>
-      <c r="AI69" s="5"/>
+      <c r="AI69" s="5">
+        <v>3224</v>
+      </c>
       <c r="AJ69" s="5"/>
       <c r="AK69" s="5"/>
       <c r="AL69" s="5"/>
@@ -8135,43 +8221,43 @@
         <v>3225</v>
       </c>
       <c r="BA69" s="4">
-        <f t="shared" ref="BA69:BC69" si="119">AZ69</f>
+        <f t="shared" ref="BA69:BC69" si="124">AZ69</f>
         <v>3225</v>
       </c>
       <c r="BB69" s="4">
-        <f t="shared" si="119"/>
+        <f t="shared" si="124"/>
         <v>3225</v>
       </c>
       <c r="BC69" s="4">
-        <f t="shared" si="119"/>
+        <f t="shared" si="124"/>
         <v>3225</v>
       </c>
       <c r="BD69" s="4">
-        <f t="shared" ref="BD69:BE69" si="120">BC69</f>
+        <f t="shared" ref="BD69:BE69" si="125">BC69</f>
         <v>3225</v>
       </c>
       <c r="BE69" s="4">
-        <f t="shared" si="120"/>
+        <f t="shared" si="125"/>
         <v>3225</v>
       </c>
       <c r="BF69" s="4">
-        <f t="shared" ref="BF69" si="121">BE69</f>
+        <f t="shared" ref="BF69" si="126">BE69</f>
         <v>3225</v>
       </c>
       <c r="BG69" s="4">
-        <f t="shared" ref="BG69" si="122">BF69</f>
+        <f t="shared" ref="BG69" si="127">BF69</f>
         <v>3225</v>
       </c>
       <c r="BH69" s="4">
-        <f t="shared" ref="BH69" si="123">BG69</f>
+        <f t="shared" ref="BH69" si="128">BG69</f>
         <v>3225</v>
       </c>
       <c r="BI69" s="4">
-        <f t="shared" ref="BI69" si="124">BH69</f>
+        <f t="shared" ref="BI69" si="129">BH69</f>
         <v>3225</v>
       </c>
       <c r="BJ69" s="4">
-        <f t="shared" ref="BJ69" si="125">BI69</f>
+        <f t="shared" ref="BJ69" si="130">BI69</f>
         <v>3225</v>
       </c>
     </row>
@@ -8192,35 +8278,35 @@
         <v>0.31799163179916312</v>
       </c>
       <c r="L71" s="21">
-        <f t="shared" ref="L71" si="126">L51/H51-1</f>
+        <f t="shared" ref="L71" si="131">L51/H51-1</f>
         <v>-4.9448818897637747E-2</v>
       </c>
       <c r="M71" s="21">
-        <f t="shared" ref="M71" si="127">M51/I51-1</f>
+        <f t="shared" ref="M71" si="132">M51/I51-1</f>
         <v>0.39155957480564818</v>
       </c>
       <c r="N71" s="21">
-        <f t="shared" ref="N71" si="128">N51/J51-1</f>
+        <f t="shared" ref="N71" si="133">N51/J51-1</f>
         <v>0.45503791982665232</v>
       </c>
       <c r="O71" s="21">
-        <f t="shared" ref="O71" si="129">O51/K51-1</f>
+        <f t="shared" ref="O71" si="134">O51/K51-1</f>
         <v>0.73583959899749374</v>
       </c>
       <c r="P71" s="21">
-        <f t="shared" ref="P71:Q71" si="130">P51/L51-1</f>
+        <f t="shared" ref="P71:Q71" si="135">P51/L51-1</f>
         <v>0.98111332007952279</v>
       </c>
       <c r="Q71" s="21">
-        <f t="shared" si="130"/>
+        <f t="shared" si="135"/>
         <v>0.56846425721126437</v>
       </c>
       <c r="R71" s="21">
-        <f t="shared" ref="R71:S71" si="131">R51/N51-1</f>
+        <f t="shared" ref="R71:S71" si="136">R51/N51-1</f>
         <v>0.64919955323901712</v>
       </c>
       <c r="S71" s="21">
-        <f t="shared" si="131"/>
+        <f t="shared" si="136"/>
         <v>0.80537106555010096</v>
       </c>
       <c r="T71" s="21">
@@ -8236,15 +8322,15 @@
         <v>0.39999999999999991</v>
       </c>
       <c r="W71" s="21">
-        <f t="shared" ref="W71:AH71" si="132">W51/S51-1</f>
+        <f t="shared" ref="W71:AI71" si="137">W51/S51-1</f>
         <v>0.24381531243335464</v>
       </c>
       <c r="X71" s="21">
-        <f t="shared" si="132"/>
+        <f t="shared" si="137"/>
         <v>0.47200897602456604</v>
       </c>
       <c r="Y71" s="21">
-        <f t="shared" si="132"/>
+        <f t="shared" si="137"/>
         <v>8.8375128181224838E-2</v>
       </c>
       <c r="Z71" s="21">
@@ -8256,47 +8342,50 @@
         <v>-8.6930429936988296E-2</v>
       </c>
       <c r="AB71" s="21">
-        <f t="shared" si="132"/>
+        <f t="shared" si="137"/>
         <v>2.2987122397400306E-2</v>
       </c>
       <c r="AC71" s="21">
-        <f t="shared" si="132"/>
+        <f t="shared" si="137"/>
         <v>0.11765334961430951</v>
       </c>
       <c r="AD71" s="21">
-        <f t="shared" si="132"/>
+        <f t="shared" si="137"/>
         <v>0.13521798932415607</v>
       </c>
       <c r="AE71" s="21">
-        <f t="shared" si="132"/>
+        <f t="shared" si="137"/>
         <v>-9.2296136331627587E-2</v>
       </c>
       <c r="AF71" s="21">
-        <f t="shared" si="132"/>
+        <f t="shared" si="137"/>
         <v>-0.1178039215686274</v>
       </c>
       <c r="AG71" s="21">
-        <f t="shared" si="132"/>
+        <f t="shared" si="137"/>
         <v>7.6552038116205923E-2</v>
       </c>
       <c r="AH71" s="21">
-        <f t="shared" si="132"/>
+        <f t="shared" si="137"/>
         <v>-0.12842237096928399</v>
       </c>
-      <c r="AI71" s="21"/>
+      <c r="AI71" s="21">
+        <f t="shared" si="137"/>
+        <v>0.15784846133953967</v>
+      </c>
       <c r="AJ71" s="21"/>
       <c r="AK71" s="21"/>
       <c r="AL71" s="21"/>
       <c r="AO71" s="24">
-        <f t="shared" ref="AO71:AQ71" si="133">AO51/AN51-1</f>
+        <f t="shared" ref="AO71:AQ71" si="138">AO51/AN51-1</f>
         <v>0.58845907814070664</v>
       </c>
       <c r="AP71" s="24">
-        <f t="shared" si="133"/>
+        <f t="shared" si="138"/>
         <v>0.26503272306147285</v>
       </c>
       <c r="AQ71" s="24">
-        <f t="shared" si="133"/>
+        <f t="shared" si="138"/>
         <v>0.73012574069611524</v>
       </c>
       <c r="AR71" s="24">
@@ -8328,47 +8417,47 @@
         <v>0.18086993871917945</v>
       </c>
       <c r="AY71" s="24">
-        <f t="shared" ref="AY71:BC71" si="134">+AY51/AX51-1</f>
+        <f t="shared" ref="AY71:BC71" si="139">+AY51/AX51-1</f>
         <v>9.4757835346634955E-3</v>
       </c>
       <c r="AZ71" s="24">
-        <f t="shared" si="134"/>
+        <f t="shared" si="139"/>
         <v>-2.9306991503736279E-2</v>
       </c>
       <c r="BA71" s="24">
-        <f t="shared" si="134"/>
+        <f t="shared" si="139"/>
         <v>-7.5782275711056446E-2</v>
       </c>
       <c r="BB71" s="24">
-        <f t="shared" si="134"/>
+        <f t="shared" si="139"/>
         <v>0.24378446532674292</v>
       </c>
       <c r="BC71" s="24">
-        <f t="shared" si="134"/>
+        <f t="shared" si="139"/>
         <v>0.24313159070107093</v>
       </c>
       <c r="BD71" s="24">
-        <f t="shared" ref="BD71:BE71" si="135">+BD51/BC51-1</f>
+        <f t="shared" ref="BD71:BE71" si="140">+BD51/BC51-1</f>
         <v>0.19716426743993209</v>
       </c>
       <c r="BE71" s="24">
-        <f t="shared" si="135"/>
+        <f t="shared" si="140"/>
         <v>0.14687860251881468</v>
       </c>
       <c r="BF71" s="24">
-        <f t="shared" ref="BF71" si="136">+BF51/BE51-1</f>
+        <f t="shared" ref="BF71" si="141">+BF51/BE51-1</f>
         <v>8.189000823371706E-2</v>
       </c>
       <c r="BG71" s="24">
-        <f t="shared" ref="BG71" si="137">+BG51/BF51-1</f>
+        <f t="shared" ref="BG71" si="142">+BG51/BF51-1</f>
         <v>8.1804671913826787E-2</v>
       </c>
       <c r="BH71" s="24">
-        <f t="shared" ref="BH71" si="138">+BH51/BG51-1</f>
+        <f t="shared" ref="BH71" si="143">+BH51/BG51-1</f>
         <v>8.1725168937860637E-2</v>
       </c>
       <c r="BI71" s="24">
-        <f t="shared" ref="BI71" si="139">+BI51/BH51-1</f>
+        <f t="shared" ref="BI71" si="144">+BI51/BH51-1</f>
         <v>8.1651127218521857E-2</v>
       </c>
       <c r="BJ71" s="24">
@@ -8381,163 +8470,166 @@
         <v>89</v>
       </c>
       <c r="K72" s="16">
-        <f t="shared" ref="K72:AH72" si="140">+K37/G37-1</f>
+        <f t="shared" ref="K72:AI72" si="145">+K37/G37-1</f>
         <v>0.40427490122026688</v>
       </c>
       <c r="L72" s="16">
-        <f t="shared" si="140"/>
+        <f t="shared" si="145"/>
         <v>-4.9351902344897058E-2</v>
       </c>
       <c r="M72" s="16">
-        <f t="shared" si="140"/>
+        <f t="shared" si="145"/>
         <v>0.43333401930319182</v>
       </c>
       <c r="N72" s="16">
-        <f t="shared" si="140"/>
+        <f t="shared" si="145"/>
         <v>0.61086578348722065</v>
       </c>
       <c r="O72" s="16">
-        <f t="shared" si="140"/>
+        <f t="shared" si="145"/>
         <v>1.088229976496113</v>
       </c>
       <c r="P72" s="16">
-        <f t="shared" si="140"/>
+        <f t="shared" si="145"/>
         <v>1.2200772200772199</v>
       </c>
       <c r="Q72" s="16">
-        <f t="shared" si="140"/>
+        <f t="shared" si="145"/>
         <v>0.73223259152907394</v>
       </c>
       <c r="R72" s="16">
-        <f t="shared" si="140"/>
+        <f t="shared" si="145"/>
         <v>0.70903250816857732</v>
       </c>
       <c r="S72" s="16">
-        <f t="shared" si="140"/>
+        <f t="shared" si="145"/>
         <v>0.67774891774891777</v>
       </c>
       <c r="T72" s="16">
-        <f t="shared" si="140"/>
+        <f t="shared" si="145"/>
         <v>0.26556521739130434</v>
       </c>
       <c r="U72" s="16">
-        <f t="shared" si="140"/>
+        <f t="shared" si="145"/>
         <v>0.42490675507666809</v>
       </c>
       <c r="V72" s="16">
-        <f t="shared" si="140"/>
+        <f t="shared" si="145"/>
         <v>0.31327932598833441</v>
       </c>
       <c r="W72" s="16">
-        <f t="shared" si="140"/>
+        <f t="shared" si="145"/>
         <v>0.36390171844359576</v>
       </c>
       <c r="X72" s="16">
-        <f t="shared" si="140"/>
+        <f t="shared" si="145"/>
         <v>0.83018904964761764</v>
       </c>
       <c r="Y72" s="16">
-        <f t="shared" si="140"/>
+        <f t="shared" si="145"/>
         <v>0.26533170462146982</v>
       </c>
       <c r="Z72" s="16">
-        <f t="shared" si="140"/>
+        <f t="shared" si="145"/>
         <v>0.19549297025745282</v>
       </c>
       <c r="AA72" s="16">
-        <f t="shared" si="140"/>
+        <f t="shared" si="145"/>
         <v>-8.5285249778303318E-2</v>
       </c>
       <c r="AB72" s="16">
-        <f t="shared" si="140"/>
+        <f t="shared" si="145"/>
         <v>-4.7590852533573647E-2</v>
       </c>
       <c r="AC72" s="16">
-        <f t="shared" si="140"/>
+        <f t="shared" si="145"/>
         <v>0.10358411158026848</v>
       </c>
       <c r="AD72" s="16">
-        <f t="shared" si="140"/>
+        <f t="shared" si="145"/>
         <v>0.10948139036174909</v>
       </c>
       <c r="AE72" s="16">
-        <f t="shared" si="140"/>
+        <f t="shared" si="145"/>
         <v>-0.12959592564825106</v>
       </c>
       <c r="AF72" s="16">
-        <f t="shared" si="140"/>
+        <f t="shared" si="145"/>
         <v>-0.13477461730441753</v>
       </c>
       <c r="AG72" s="16">
-        <f t="shared" si="140"/>
+        <f t="shared" si="145"/>
         <v>3.5355018555615292E-2</v>
       </c>
       <c r="AH72" s="16">
-        <f t="shared" si="140"/>
+        <f t="shared" si="145"/>
         <v>-0.2219778011967225</v>
       </c>
-      <c r="AI72" s="16"/>
+      <c r="AI72" s="16">
+        <f t="shared" si="145"/>
+        <v>6.3389380452119282E-2</v>
+      </c>
       <c r="AJ72" s="16"/>
       <c r="AK72" s="16"/>
       <c r="AL72" s="16"/>
       <c r="AU72" s="25">
-        <f t="shared" ref="AU72:BE72" si="141">+AU37/AT37-1</f>
+        <f t="shared" ref="AU72:BE72" si="146">+AU37/AT37-1</f>
         <v>0.35729051069477991</v>
       </c>
       <c r="AV72" s="25">
-        <f t="shared" si="141"/>
+        <f t="shared" si="146"/>
         <v>0.87559116340959009</v>
       </c>
       <c r="AW72" s="25">
-        <f t="shared" si="141"/>
+        <f t="shared" si="146"/>
         <v>0.403761953095785</v>
       </c>
       <c r="AX72" s="25">
-        <f t="shared" si="141"/>
+        <f t="shared" si="146"/>
         <v>0.37654954785588313</v>
       </c>
       <c r="AY72" s="25">
-        <f t="shared" si="141"/>
+        <f t="shared" si="146"/>
         <v>2.2039764876441881E-2</v>
       </c>
       <c r="AZ72" s="25">
-        <f t="shared" si="141"/>
+        <f t="shared" si="146"/>
         <v>-0.1148603713062738</v>
       </c>
       <c r="BA72" s="25">
-        <f t="shared" si="141"/>
+        <f t="shared" si="146"/>
         <v>6.9746334182695824E-2</v>
       </c>
       <c r="BB72" s="25">
-        <f t="shared" si="141"/>
+        <f t="shared" si="146"/>
         <v>0.14867421266646974</v>
       </c>
       <c r="BC72" s="25">
-        <f t="shared" si="141"/>
+        <f t="shared" si="146"/>
         <v>0.16911212812596532</v>
       </c>
       <c r="BD72" s="25">
-        <f t="shared" si="141"/>
+        <f t="shared" si="146"/>
         <v>0.28481713304504841</v>
       </c>
       <c r="BE72" s="25">
-        <f t="shared" si="141"/>
+        <f t="shared" si="146"/>
         <v>0.24761598443127775</v>
       </c>
       <c r="BF72" s="25">
-        <f t="shared" ref="BF72:BJ72" si="142">+BF37/BE37-1</f>
+        <f t="shared" ref="BF72:BI72" si="147">+BF37/BE37-1</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BG72" s="25">
-        <f t="shared" si="142"/>
+        <f t="shared" si="147"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BH72" s="25">
-        <f t="shared" si="142"/>
+        <f t="shared" si="147"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BI72" s="25">
-        <f t="shared" si="142"/>
+        <f t="shared" si="147"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BJ72" s="25">
@@ -8550,163 +8642,166 @@
         <v>90</v>
       </c>
       <c r="K73" s="16">
-        <f t="shared" ref="K73:AH73" si="143">+K42/G42-1</f>
+        <f t="shared" ref="K73:AI73" si="148">+K42/G42-1</f>
         <v>0.33101713811610356</v>
       </c>
       <c r="L73" s="16">
-        <f t="shared" si="143"/>
+        <f t="shared" si="148"/>
         <v>-5.4866280672732248E-2</v>
       </c>
       <c r="M73" s="16">
-        <f t="shared" si="143"/>
+        <f t="shared" si="148"/>
         <v>0.50835629972440333</v>
       </c>
       <c r="N73" s="16">
-        <f t="shared" si="143"/>
+        <f t="shared" si="148"/>
         <v>0.71375046476818782</v>
       </c>
       <c r="O73" s="16">
-        <f t="shared" si="143"/>
+        <f t="shared" si="148"/>
         <v>0.75644771700171409</v>
       </c>
       <c r="P73" s="16">
-        <f t="shared" si="143"/>
+        <f t="shared" si="148"/>
         <v>1.5090067094515751</v>
       </c>
       <c r="Q73" s="16">
-        <f t="shared" si="143"/>
+        <f t="shared" si="148"/>
         <v>0.63975150996993846</v>
       </c>
       <c r="R73" s="16">
-        <f t="shared" si="143"/>
+        <f t="shared" si="148"/>
         <v>0.7014080119272128</v>
       </c>
       <c r="S73" s="16">
-        <f t="shared" si="143"/>
+        <f t="shared" si="148"/>
         <v>0.69352549102241356</v>
       </c>
       <c r="T73" s="16">
-        <f t="shared" si="143"/>
+        <f t="shared" si="148"/>
         <v>0.25268262434539124</v>
       </c>
       <c r="U73" s="16">
-        <f t="shared" si="143"/>
+        <f t="shared" si="148"/>
         <v>0.53863587626091669</v>
       </c>
       <c r="V73" s="16">
-        <f t="shared" si="143"/>
+        <f t="shared" si="148"/>
         <v>0.43768310227569973</v>
       </c>
       <c r="W73" s="16">
-        <f t="shared" si="143"/>
+        <f t="shared" si="148"/>
         <v>0.44334609226376598</v>
       </c>
       <c r="X73" s="16">
-        <f t="shared" si="143"/>
+        <f t="shared" si="148"/>
         <v>0.85513187408152214</v>
       </c>
       <c r="Y73" s="16">
-        <f t="shared" si="143"/>
+        <f t="shared" si="148"/>
         <v>0.17644422460462983</v>
       </c>
       <c r="Z73" s="16">
-        <f t="shared" si="143"/>
+        <f t="shared" si="148"/>
         <v>0.12573999149421988</v>
       </c>
       <c r="AA73" s="16">
-        <f t="shared" si="143"/>
+        <f t="shared" si="148"/>
         <v>-1.687129090216144E-2</v>
       </c>
       <c r="AB73" s="16">
-        <f t="shared" si="143"/>
+        <f t="shared" si="148"/>
         <v>-0.14356681259120285</v>
       </c>
       <c r="AC73" s="16">
-        <f t="shared" si="143"/>
+        <f t="shared" si="148"/>
         <v>1.159813978554558E-2</v>
       </c>
       <c r="AD73" s="16">
-        <f t="shared" si="143"/>
+        <f t="shared" si="148"/>
         <v>0</v>
       </c>
       <c r="AE73" s="16">
-        <f t="shared" si="143"/>
+        <f t="shared" si="148"/>
         <v>-0.16326888508921922</v>
       </c>
       <c r="AF73" s="16">
-        <f t="shared" si="143"/>
+        <f t="shared" si="148"/>
         <v>-1.4288113603890817E-3</v>
       </c>
       <c r="AG73" s="16">
-        <f t="shared" si="143"/>
+        <f t="shared" si="148"/>
         <v>2.7484881884361156E-2</v>
       </c>
       <c r="AH73" s="16">
-        <f t="shared" si="143"/>
+        <f t="shared" si="148"/>
         <v>-0.12248959067777265</v>
       </c>
-      <c r="AI73" s="16"/>
+      <c r="AI73" s="16">
+        <f t="shared" si="148"/>
+        <v>0.12622478386167146</v>
+      </c>
       <c r="AJ73" s="16"/>
       <c r="AK73" s="16"/>
       <c r="AL73" s="16"/>
       <c r="AU73" s="25">
-        <f t="shared" ref="AU73:BE73" si="144">+AU42/AT42-1</f>
+        <f t="shared" ref="AU73:BE73" si="149">+AU42/AT42-1</f>
         <v>0.39565262627590125</v>
       </c>
       <c r="AV73" s="25">
-        <f t="shared" si="144"/>
+        <f t="shared" si="149"/>
         <v>0.8252981439448186</v>
       </c>
       <c r="AW73" s="25">
-        <f t="shared" si="144"/>
+        <f t="shared" si="149"/>
         <v>0.47203204567389845</v>
       </c>
       <c r="AX73" s="25">
-        <f t="shared" si="144"/>
+        <f t="shared" si="149"/>
         <v>0.34781700789494252</v>
       </c>
       <c r="AY73" s="25">
-        <f t="shared" si="144"/>
+        <f t="shared" si="149"/>
         <v>-7.1121997199327103E-2</v>
       </c>
       <c r="AZ73" s="25">
-        <f t="shared" si="144"/>
+        <f t="shared" si="149"/>
         <v>-3.500789639038171E-2</v>
       </c>
       <c r="BA73" s="25">
-        <f t="shared" si="144"/>
+        <f t="shared" si="149"/>
         <v>0.25</v>
       </c>
       <c r="BB73" s="25">
-        <f t="shared" si="144"/>
+        <f t="shared" si="149"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="BC73" s="25">
-        <f t="shared" si="144"/>
+        <f t="shared" si="149"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="BD73" s="25">
-        <f t="shared" si="144"/>
+        <f t="shared" si="149"/>
         <v>0.14999999999999991</v>
       </c>
       <c r="BE73" s="25">
-        <f t="shared" si="144"/>
+        <f t="shared" si="149"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="BF73" s="25">
-        <f t="shared" ref="BF73:BJ73" si="145">+BF42/BE42-1</f>
+        <f t="shared" ref="BF73:BI73" si="150">+BF42/BE42-1</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BG73" s="25">
-        <f t="shared" si="145"/>
+        <f t="shared" si="150"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BH73" s="25">
-        <f t="shared" si="145"/>
+        <f t="shared" si="150"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BI73" s="25">
-        <f t="shared" si="145"/>
+        <f t="shared" si="150"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BJ73" s="25">
@@ -8719,23 +8814,23 @@
         <v>88</v>
       </c>
       <c r="K74" s="16">
-        <f t="shared" ref="K74:O74" si="146">K45/G45-1</f>
+        <f t="shared" ref="K74:O74" si="151">K45/G45-1</f>
         <v>0.39441436306640076</v>
       </c>
       <c r="L74" s="16">
-        <f t="shared" si="146"/>
+        <f t="shared" si="151"/>
         <v>-4.9729102167182626E-2</v>
       </c>
       <c r="M74" s="16">
-        <f t="shared" si="146"/>
+        <f t="shared" si="151"/>
         <v>0.43141075604053003</v>
       </c>
       <c r="N74" s="16">
-        <f t="shared" si="146"/>
+        <f t="shared" si="151"/>
         <v>0.4053394107113788</v>
       </c>
       <c r="O74" s="16">
-        <f t="shared" si="146"/>
+        <f t="shared" si="151"/>
         <v>0.67320662170447587</v>
       </c>
       <c r="P74" s="16">
@@ -8743,7 +8838,7 @@
         <v>0.9385053960496843</v>
       </c>
       <c r="Q74" s="16">
-        <f t="shared" ref="Q74" si="147">Q45/M45-1</f>
+        <f t="shared" ref="Q74" si="152">Q45/M45-1</f>
         <v>0.55091206098557044</v>
       </c>
       <c r="R74" s="16">
@@ -8751,19 +8846,19 @@
         <v>0.74041468782578468</v>
       </c>
       <c r="S74" s="16">
-        <f t="shared" ref="S74:U74" si="148">S45/O45-1</f>
+        <f t="shared" ref="S74:U74" si="153">S45/O45-1</f>
         <v>0.89495541712470983</v>
       </c>
       <c r="T74" s="16">
-        <f t="shared" si="148"/>
+        <f t="shared" si="153"/>
         <v>0.43592436974789917</v>
       </c>
       <c r="U74" s="16">
-        <f t="shared" si="148"/>
+        <f t="shared" si="153"/>
         <v>0.561046256473273</v>
       </c>
       <c r="V74" s="16">
-        <f t="shared" ref="V74" si="149">V45/R45-1</f>
+        <f t="shared" ref="V74" si="154">V45/R45-1</f>
         <v>0.39999999999999991</v>
       </c>
       <c r="W74" s="16">
@@ -8771,19 +8866,19 @@
         <v>0.21683640582699493</v>
       </c>
       <c r="X74" s="16">
-        <f t="shared" ref="X74" si="150">X45/T45-1</f>
+        <f t="shared" ref="X74" si="155">X45/T45-1</f>
         <v>0.49370885149963417</v>
       </c>
       <c r="Y74" s="16">
-        <f t="shared" ref="Y74" si="151">Y45/U45-1</f>
+        <f t="shared" ref="Y74" si="156">Y45/U45-1</f>
         <v>4.4813044700590332E-2</v>
       </c>
       <c r="Z74" s="16">
-        <f t="shared" ref="Z74:AH74" si="152">Z45/V45-1</f>
+        <f t="shared" ref="Z74:AI74" si="157">Z45/V45-1</f>
         <v>-1.9253624910862799E-2</v>
       </c>
       <c r="AA74" s="16">
-        <f t="shared" si="152"/>
+        <f t="shared" si="157"/>
         <v>-0.12808560228837795</v>
       </c>
       <c r="AB74" s="16">
@@ -8791,30 +8886,33 @@
         <v>-9.2511876193741127E-2</v>
       </c>
       <c r="AC74" s="16">
-        <f t="shared" si="152"/>
+        <f t="shared" si="157"/>
         <v>6.7657179716614557E-2</v>
       </c>
       <c r="AD74" s="16">
-        <f t="shared" si="152"/>
+        <f t="shared" si="157"/>
         <v>0.16495545987983684</v>
       </c>
       <c r="AE74" s="16">
-        <f t="shared" si="152"/>
+        <f t="shared" si="157"/>
         <v>-0.21476306196840822</v>
       </c>
       <c r="AF74" s="16">
-        <f t="shared" si="152"/>
+        <f t="shared" si="157"/>
         <v>-0.14803022126281706</v>
       </c>
       <c r="AG74" s="16">
-        <f t="shared" si="152"/>
+        <f t="shared" si="157"/>
         <v>2.6200357716555045E-2</v>
       </c>
       <c r="AH74" s="16">
-        <f t="shared" si="152"/>
+        <f t="shared" si="157"/>
         <v>-0.30304255404600933</v>
       </c>
-      <c r="AI74" s="16"/>
+      <c r="AI74" s="16">
+        <f t="shared" si="157"/>
+        <v>0.19713733075435202</v>
+      </c>
       <c r="AJ74" s="16"/>
       <c r="AK74" s="16"/>
       <c r="AL74" s="16"/>
@@ -8828,67 +8926,67 @@
       <c r="E75" s="16"/>
       <c r="F75" s="16"/>
       <c r="G75" s="16">
-        <f t="shared" ref="G75:K75" si="153">G53/G45</f>
+        <f t="shared" ref="G75:K75" si="158">G53/G45</f>
         <v>0.18609290396124251</v>
       </c>
       <c r="H75" s="16">
-        <f t="shared" si="153"/>
+        <f t="shared" si="158"/>
         <v>0.17685758513931887</v>
       </c>
       <c r="I75" s="16">
-        <f t="shared" si="153"/>
+        <f t="shared" si="158"/>
         <v>0.21784879189399844</v>
       </c>
       <c r="J75" s="16">
-        <f t="shared" si="153"/>
+        <f t="shared" si="158"/>
         <v>0.21618101904606871</v>
       </c>
       <c r="K75" s="16">
-        <f t="shared" si="153"/>
+        <f t="shared" si="158"/>
         <v>0.2440220723482526</v>
       </c>
       <c r="L75" s="16">
-        <f t="shared" ref="L75" si="154">L53/L45</f>
+        <f t="shared" ref="L75" si="159">L53/L45</f>
         <v>0.24373854612095297</v>
       </c>
       <c r="M75" s="16">
-        <f t="shared" ref="M75" si="155">M53/M45</f>
+        <f t="shared" ref="M75" si="160">M53/M45</f>
         <v>0.27021508303838826</v>
       </c>
       <c r="N75" s="16">
-        <f t="shared" ref="N75:U75" si="156">N53/N45</f>
+        <f t="shared" ref="N75:U75" si="161">N53/N45</f>
         <v>0.19819298042395458</v>
       </c>
       <c r="O75" s="16">
-        <f t="shared" si="156"/>
+        <f t="shared" si="161"/>
         <v>0.21131061438866497</v>
       </c>
       <c r="P75" s="16">
-        <f t="shared" si="156"/>
+        <f t="shared" si="161"/>
         <v>0.25220588235294117</v>
       </c>
       <c r="Q75" s="16">
-        <f t="shared" si="156"/>
+        <f t="shared" si="161"/>
         <v>0.28464846835776353</v>
       </c>
       <c r="R75" s="16">
-        <f t="shared" si="156"/>
+        <f t="shared" si="161"/>
         <v>0.28858569051580701</v>
       </c>
       <c r="S75" s="16">
-        <f t="shared" si="156"/>
+        <f t="shared" si="161"/>
         <v>0.29650638133298957</v>
       </c>
       <c r="T75" s="16">
-        <f t="shared" si="156"/>
+        <f t="shared" si="161"/>
         <v>0.25727871250914414</v>
       </c>
       <c r="U75" s="16">
-        <f t="shared" si="156"/>
+        <f t="shared" si="161"/>
         <v>0.26348046106269329</v>
       </c>
       <c r="V75" s="16">
-        <f t="shared" ref="V75:AD75" si="157">V53/V45</f>
+        <f t="shared" ref="V75:AD75" si="162">V53/V45</f>
         <v>0.26631804135963871</v>
       </c>
       <c r="W75" s="16">
@@ -8896,71 +8994,74 @@
         <v>0.1830702404915775</v>
       </c>
       <c r="X75" s="16">
-        <f t="shared" si="157"/>
+        <f t="shared" si="162"/>
         <v>0.17522895342573094</v>
       </c>
       <c r="Y75" s="16">
-        <f t="shared" si="157"/>
+        <f t="shared" si="162"/>
         <v>0.15746421267893659</v>
       </c>
       <c r="Z75" s="16">
-        <f t="shared" si="157"/>
+        <f t="shared" si="162"/>
         <v>0.16616577799321378</v>
       </c>
       <c r="AA75" s="16">
-        <f t="shared" si="157"/>
+        <f t="shared" si="162"/>
         <v>0.15571081409477522</v>
       </c>
       <c r="AB75" s="16">
-        <f t="shared" si="157"/>
+        <f t="shared" si="162"/>
         <v>0.13858607663248787</v>
       </c>
       <c r="AC75" s="16">
-        <f t="shared" si="157"/>
+        <f t="shared" si="162"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="AD75" s="16">
-        <f t="shared" si="157"/>
+        <f t="shared" si="162"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="AE75" s="16">
-        <f t="shared" ref="AE75:AF75" si="158">AE53/AE45</f>
+        <f t="shared" ref="AE75:AF75" si="163">AE53/AE45</f>
         <v>0.1132688588007737</v>
       </c>
       <c r="AF75" s="16">
-        <f t="shared" si="158"/>
+        <f t="shared" si="163"/>
         <v>0.14062203078482297</v>
       </c>
       <c r="AG75" s="16">
-        <f t="shared" ref="AG75:AH75" si="159">AG53/AG45</f>
+        <f t="shared" ref="AG75:AH75" si="164">AG53/AG45</f>
         <v>0.14706026818606022</v>
       </c>
       <c r="AH75" s="16">
-        <f t="shared" si="159"/>
+        <f t="shared" si="164"/>
         <v>0.39289552238805969</v>
       </c>
-      <c r="AI75" s="16"/>
+      <c r="AI75" s="16">
+        <f t="shared" ref="AI75" si="165">AI53/AI45</f>
+        <v>0.18464421896206296</v>
+      </c>
       <c r="AJ75" s="16"/>
       <c r="AK75" s="16"/>
       <c r="AL75" s="16"/>
       <c r="AU75" s="16">
-        <f t="shared" ref="AU75:AY75" si="160">AU53/AU45</f>
+        <f t="shared" ref="AU75:AY75" si="166">AU53/AU45</f>
         <v>0</v>
       </c>
       <c r="AV75" s="16">
-        <f t="shared" si="160"/>
+        <f t="shared" si="166"/>
         <v>0.38841926345609062</v>
       </c>
       <c r="AW75" s="16">
-        <f t="shared" si="160"/>
+        <f t="shared" si="166"/>
         <v>0.27064584436209632</v>
       </c>
       <c r="AX75" s="16">
-        <f t="shared" si="160"/>
+        <f t="shared" si="166"/>
         <v>0.17052821969455731</v>
       </c>
       <c r="AY75" s="16">
-        <f t="shared" si="160"/>
+        <f t="shared" si="166"/>
         <v>0.20971302428256069</v>
       </c>
       <c r="AZ75" s="16"/>
@@ -8976,31 +9077,31 @@
       <c r="E76" s="16"/>
       <c r="F76" s="16"/>
       <c r="G76" s="16">
-        <f t="shared" ref="G76:K76" si="161">+G59/G51</f>
+        <f t="shared" ref="G76:K76" si="167">+G59/G51</f>
         <v>0.1246421493063202</v>
       </c>
       <c r="H76" s="16">
-        <f t="shared" si="161"/>
+        <f t="shared" si="167"/>
         <v>0.14503937007874015</v>
       </c>
       <c r="I76" s="16">
-        <f t="shared" si="161"/>
+        <f t="shared" si="167"/>
         <v>0.18895763921941933</v>
       </c>
       <c r="J76" s="16">
-        <f t="shared" si="161"/>
+        <f t="shared" si="167"/>
         <v>0.18838028169014084</v>
       </c>
       <c r="K76" s="16">
-        <f t="shared" si="161"/>
+        <f t="shared" si="167"/>
         <v>0.20618212197159566</v>
       </c>
       <c r="L76" s="16">
-        <f t="shared" ref="L76" si="162">+L59/L51</f>
+        <f t="shared" ref="L76" si="168">+L59/L51</f>
         <v>0.20990722332670642</v>
       </c>
       <c r="M76" s="16">
-        <f t="shared" ref="M76" si="163">+M59/M51</f>
+        <f t="shared" ref="M76" si="169">+M59/M51</f>
         <v>0.23520693193478509</v>
       </c>
       <c r="N76" s="16">
@@ -9008,147 +9109,150 @@
         <v>0.19229337304542071</v>
       </c>
       <c r="O76" s="16">
-        <f t="shared" ref="O76:AD76" si="164">+O59/O51</f>
+        <f t="shared" ref="O76:AD76" si="170">+O59/O51</f>
         <v>0.21320627586870727</v>
       </c>
       <c r="P76" s="16">
-        <f t="shared" si="164"/>
+        <f t="shared" si="170"/>
         <v>0.24117745442381669</v>
       </c>
       <c r="Q76" s="16">
-        <f t="shared" si="164"/>
+        <f t="shared" si="170"/>
         <v>0.26604637639020134</v>
       </c>
       <c r="R76" s="16">
-        <f t="shared" si="164"/>
+        <f t="shared" si="170"/>
         <v>0.27354816863254133</v>
       </c>
       <c r="S76" s="16">
-        <f t="shared" si="164"/>
+        <f t="shared" si="170"/>
         <v>0.29110684580934099</v>
       </c>
       <c r="T76" s="16">
-        <f t="shared" si="164"/>
+        <f t="shared" si="170"/>
         <v>0.24997047360340144</v>
       </c>
       <c r="U76" s="16">
-        <f t="shared" si="164"/>
+        <f t="shared" si="170"/>
         <v>0.25086231005873033</v>
       </c>
       <c r="V76" s="16">
-        <f t="shared" si="164"/>
+        <f t="shared" si="170"/>
         <v>0.25257794296679104</v>
       </c>
       <c r="W76" s="16">
-        <f t="shared" si="164"/>
+        <f t="shared" si="170"/>
         <v>0.19336448197522396</v>
       </c>
       <c r="X76" s="16">
-        <f t="shared" si="164"/>
+        <f t="shared" si="170"/>
         <v>0.18185100493440848</v>
       </c>
       <c r="Y76" s="16">
-        <f t="shared" si="164"/>
+        <f t="shared" si="170"/>
         <v>0.17892933618843684</v>
       </c>
       <c r="Z76" s="16">
-        <f t="shared" si="164"/>
+        <f t="shared" si="170"/>
         <v>0.17634203520483172</v>
       </c>
       <c r="AA76" s="16">
-        <f t="shared" si="164"/>
+        <f t="shared" si="170"/>
         <v>0.1735129806112389</v>
       </c>
       <c r="AB76" s="40">
-        <f t="shared" si="164"/>
+        <f t="shared" si="170"/>
         <v>0.17952941176470588</v>
       </c>
       <c r="AC76" s="16">
-        <f t="shared" si="164"/>
+        <f t="shared" si="170"/>
         <v>0.15717279857679209</v>
       </c>
       <c r="AD76" s="16">
-        <f t="shared" si="164"/>
+        <f t="shared" si="170"/>
         <v>0.15511900037130005</v>
       </c>
       <c r="AE76" s="16">
-        <f t="shared" ref="AE76:AF76" si="165">+AE59/AE51</f>
+        <f t="shared" ref="AE76:AF76" si="171">+AE59/AE51</f>
         <v>0.16307214895267649</v>
       </c>
       <c r="AF76" s="16">
-        <f t="shared" si="165"/>
+        <f t="shared" si="171"/>
         <v>0.17238620199146515</v>
       </c>
       <c r="AG76" s="16">
-        <f t="shared" ref="AG76:AH76" si="166">+AG59/AG51</f>
+        <f t="shared" ref="AG76:AH76" si="172">+AG59/AG51</f>
         <v>0.1798896600818651</v>
       </c>
       <c r="AH76" s="16">
-        <f t="shared" si="166"/>
+        <f t="shared" si="172"/>
         <v>0.20115658005702583</v>
       </c>
-      <c r="AI76" s="16"/>
+      <c r="AI76" s="16">
+        <f t="shared" ref="AI76" si="173">+AI59/AI51</f>
+        <v>0.21083664626792334</v>
+      </c>
       <c r="AJ76" s="16"/>
       <c r="AK76" s="16"/>
       <c r="AL76" s="16"/>
       <c r="AU76" s="16">
-        <f t="shared" ref="AU76:BJ76" si="167">+AU59/AU51</f>
+        <f t="shared" ref="AU76:BI76" si="174">+AU59/AU51</f>
         <v>0</v>
       </c>
       <c r="AV76" s="16">
-        <f t="shared" si="167"/>
+        <f t="shared" si="174"/>
         <v>0</v>
       </c>
       <c r="AW76" s="16">
-        <f t="shared" si="167"/>
+        <f t="shared" si="174"/>
         <v>0.25</v>
       </c>
       <c r="AX76" s="16">
-        <f t="shared" si="167"/>
+        <f t="shared" si="174"/>
         <v>0.18248891736331416</v>
       </c>
       <c r="AY76" s="16">
-        <f t="shared" si="167"/>
+        <f t="shared" si="174"/>
         <v>0.17862626676220697</v>
       </c>
       <c r="AZ76" s="16">
-        <f t="shared" si="167"/>
+        <f t="shared" si="174"/>
         <v>0.18026511436616155</v>
       </c>
       <c r="BA76" s="16">
-        <f t="shared" si="167"/>
+        <f t="shared" si="174"/>
         <v>0.22441699797887588</v>
       </c>
       <c r="BB76" s="16">
-        <f t="shared" si="167"/>
+        <f t="shared" si="174"/>
         <v>0.21999999999999997</v>
       </c>
       <c r="BC76" s="16">
-        <f t="shared" si="167"/>
+        <f t="shared" si="174"/>
         <v>0.23000000000000004</v>
       </c>
       <c r="BD76" s="16">
-        <f t="shared" si="167"/>
+        <f t="shared" si="174"/>
         <v>0.24</v>
       </c>
       <c r="BE76" s="16">
-        <f t="shared" si="167"/>
+        <f t="shared" si="174"/>
         <v>0.25</v>
       </c>
       <c r="BF76" s="16">
-        <f t="shared" si="167"/>
+        <f t="shared" si="174"/>
         <v>0.24999999999999997</v>
       </c>
       <c r="BG76" s="16">
-        <f t="shared" si="167"/>
+        <f t="shared" si="174"/>
         <v>0.25000000000000006</v>
       </c>
       <c r="BH76" s="16">
-        <f t="shared" si="167"/>
+        <f t="shared" si="174"/>
         <v>0.24999999999999997</v>
       </c>
       <c r="BI76" s="16">
-        <f t="shared" si="167"/>
+        <f t="shared" si="174"/>
         <v>0.25000000000000006</v>
       </c>
       <c r="BJ76" s="16">
@@ -9203,27 +9307,27 @@
       <c r="K79" s="5"/>
       <c r="L79" s="5"/>
       <c r="M79" s="5">
-        <f t="shared" ref="M79:R79" si="168">M67</f>
+        <f t="shared" ref="M79:R79" si="175">M67</f>
         <v>300</v>
       </c>
       <c r="N79" s="5">
-        <f t="shared" si="168"/>
+        <f t="shared" si="175"/>
         <v>270</v>
       </c>
       <c r="O79" s="5">
-        <f t="shared" si="168"/>
+        <f t="shared" si="175"/>
         <v>337</v>
       </c>
       <c r="P79" s="5">
-        <f t="shared" si="168"/>
+        <f t="shared" si="175"/>
         <v>1165</v>
       </c>
       <c r="Q79" s="5">
-        <f t="shared" si="168"/>
+        <f t="shared" si="175"/>
         <v>1669</v>
       </c>
       <c r="R79" s="5">
-        <f t="shared" si="168"/>
+        <f t="shared" si="175"/>
         <v>2321</v>
       </c>
       <c r="S79" s="5">
@@ -9239,31 +9343,31 @@
         <v>3331</v>
       </c>
       <c r="V79" s="5">
-        <f t="shared" ref="V79:AD79" si="169">V67</f>
+        <f t="shared" ref="V79:AD79" si="176">V67</f>
         <v>3468.7999999999984</v>
       </c>
       <c r="W79" s="5">
-        <f t="shared" si="169"/>
+        <f t="shared" si="176"/>
         <v>2513</v>
       </c>
       <c r="X79" s="5">
-        <f t="shared" si="169"/>
+        <f t="shared" si="176"/>
         <v>2703</v>
       </c>
       <c r="Y79" s="5">
-        <f t="shared" si="169"/>
+        <f t="shared" si="176"/>
         <v>1853</v>
       </c>
       <c r="Z79" s="5">
-        <f t="shared" si="169"/>
+        <f t="shared" si="176"/>
         <v>2176</v>
       </c>
       <c r="AA79" s="5">
-        <f t="shared" si="169"/>
+        <f t="shared" si="176"/>
         <v>1129</v>
       </c>
       <c r="AB79" s="5">
-        <f t="shared" si="169"/>
+        <f t="shared" si="176"/>
         <v>2100</v>
       </c>
       <c r="AC79" s="5">
@@ -9271,7 +9375,7 @@
         <v>1157.0966856192958</v>
       </c>
       <c r="AD79" s="5">
-        <f t="shared" si="169"/>
+        <f t="shared" si="176"/>
         <v>1456.2837364785246</v>
       </c>
       <c r="AE79" s="5"/>
@@ -9363,7 +9467,7 @@
       </c>
       <c r="BL80" s="4">
         <f>NPV(BL79,AZ67:DJ67)+Main!K5-Main!K6</f>
-        <v>577814.90996205888</v>
+        <v>579383.90996205888</v>
       </c>
     </row>
     <row r="81" spans="2:64" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -9516,7 +9620,7 @@
       </c>
       <c r="BL82" s="19">
         <f>BL80/Main!K3</f>
-        <v>179.16741394172368</v>
+        <v>154.26690828785343</v>
       </c>
     </row>
     <row r="83" spans="2:64" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -9821,59 +9925,59 @@
       <c r="L88" s="5"/>
       <c r="M88" s="5"/>
       <c r="N88" s="5">
-        <f t="shared" ref="N88:R88" si="170">SUM(N80:N87)</f>
+        <f t="shared" ref="N88:R88" si="177">SUM(N80:N87)</f>
         <v>3019</v>
       </c>
       <c r="O88" s="5">
-        <f t="shared" si="170"/>
+        <f t="shared" si="177"/>
         <v>1641</v>
       </c>
       <c r="P88" s="5">
-        <f t="shared" si="170"/>
+        <f t="shared" si="177"/>
         <v>2124</v>
       </c>
       <c r="Q88" s="5">
-        <f t="shared" si="170"/>
+        <f t="shared" si="177"/>
         <v>3147</v>
       </c>
       <c r="R88" s="5">
-        <f t="shared" si="170"/>
+        <f t="shared" si="177"/>
         <v>4585</v>
       </c>
       <c r="S88" s="5">
-        <f t="shared" ref="S88:AA88" si="171">SUM(S80:S87)</f>
+        <f t="shared" ref="S88:AA88" si="178">SUM(S80:S87)</f>
         <v>3995</v>
       </c>
       <c r="T88" s="5">
-        <f t="shared" si="171"/>
+        <f t="shared" si="178"/>
         <v>2351</v>
       </c>
       <c r="U88" s="5">
-        <f t="shared" si="171"/>
+        <f t="shared" si="178"/>
         <v>5100</v>
       </c>
       <c r="V88" s="5">
-        <f t="shared" si="171"/>
+        <f t="shared" si="178"/>
         <v>3278</v>
       </c>
       <c r="W88" s="5">
-        <f t="shared" si="171"/>
+        <f t="shared" si="178"/>
         <v>2513</v>
       </c>
       <c r="X88" s="5">
-        <f t="shared" si="171"/>
+        <f t="shared" si="178"/>
         <v>3065</v>
       </c>
       <c r="Y88" s="5">
-        <f t="shared" si="171"/>
+        <f t="shared" si="178"/>
         <v>3308</v>
       </c>
       <c r="Z88" s="5">
-        <f t="shared" si="171"/>
+        <f t="shared" si="178"/>
         <v>4370</v>
       </c>
       <c r="AA88" s="5">
-        <f t="shared" si="171"/>
+        <f t="shared" si="178"/>
         <v>242</v>
       </c>
       <c r="AB88" s="5">
@@ -10045,59 +10149,59 @@
         <v>1868</v>
       </c>
       <c r="O91" s="5">
-        <f t="shared" ref="O91:R91" si="172">O88-O90</f>
+        <f t="shared" ref="O91:R91" si="179">O88-O90</f>
         <v>293</v>
       </c>
       <c r="P91" s="5">
-        <f t="shared" si="172"/>
+        <f t="shared" si="179"/>
         <v>619</v>
       </c>
       <c r="Q91" s="5">
-        <f t="shared" si="172"/>
+        <f t="shared" si="179"/>
         <v>1328</v>
       </c>
       <c r="R91" s="5">
-        <f t="shared" si="172"/>
+        <f t="shared" si="179"/>
         <v>2775</v>
       </c>
       <c r="S91" s="5">
-        <f t="shared" ref="S91" si="173">S88-S90</f>
+        <f t="shared" ref="S91" si="180">S88-S90</f>
         <v>2228</v>
       </c>
       <c r="T91" s="5">
-        <f t="shared" ref="T91:AB91" si="174">T88-T90</f>
+        <f t="shared" ref="T91:AB91" si="181">T88-T90</f>
         <v>621</v>
       </c>
       <c r="U91" s="5">
-        <f t="shared" si="174"/>
+        <f t="shared" si="181"/>
         <v>3297</v>
       </c>
       <c r="V91" s="5">
-        <f t="shared" si="174"/>
+        <f t="shared" si="181"/>
         <v>1420</v>
       </c>
       <c r="W91" s="5">
-        <f t="shared" si="174"/>
+        <f t="shared" si="181"/>
         <v>441</v>
       </c>
       <c r="X91" s="5">
-        <f t="shared" si="174"/>
+        <f t="shared" si="181"/>
         <v>1005</v>
       </c>
       <c r="Y91" s="5">
-        <f t="shared" si="174"/>
+        <f t="shared" si="181"/>
         <v>848</v>
       </c>
       <c r="Z91" s="5">
-        <f t="shared" si="174"/>
+        <f t="shared" si="181"/>
         <v>2064</v>
       </c>
       <c r="AA91" s="5">
-        <f t="shared" si="174"/>
+        <f t="shared" si="181"/>
         <v>-2531</v>
       </c>
       <c r="AB91" s="5">
-        <f t="shared" si="174"/>
+        <f t="shared" si="181"/>
         <v>1342</v>
       </c>
       <c r="AC91" s="5"/>
@@ -10142,51 +10246,51 @@
       <c r="O92" s="5"/>
       <c r="P92" s="5"/>
       <c r="Q92" s="7">
-        <f t="shared" ref="Q92:V92" si="175">SUM(N91:Q91)</f>
+        <f t="shared" ref="Q92:V92" si="182">SUM(N91:Q91)</f>
         <v>4108</v>
       </c>
       <c r="R92" s="7">
-        <f t="shared" si="175"/>
+        <f t="shared" si="182"/>
         <v>5015</v>
       </c>
       <c r="S92" s="7">
-        <f t="shared" si="175"/>
+        <f t="shared" si="182"/>
         <v>6950</v>
       </c>
       <c r="T92" s="7">
-        <f t="shared" si="175"/>
+        <f t="shared" si="182"/>
         <v>6952</v>
       </c>
       <c r="U92" s="7">
-        <f t="shared" si="175"/>
+        <f t="shared" si="182"/>
         <v>8921</v>
       </c>
       <c r="V92" s="7">
-        <f t="shared" si="175"/>
+        <f t="shared" si="182"/>
         <v>7566</v>
       </c>
       <c r="W92" s="7">
-        <f t="shared" ref="W92:AB92" si="176">SUM(T91:W91)</f>
+        <f t="shared" ref="W92:AB92" si="183">SUM(T91:W91)</f>
         <v>5779</v>
       </c>
       <c r="X92" s="7">
-        <f t="shared" si="176"/>
+        <f t="shared" si="183"/>
         <v>6163</v>
       </c>
       <c r="Y92" s="7">
-        <f t="shared" si="176"/>
+        <f t="shared" si="183"/>
         <v>3714</v>
       </c>
       <c r="Z92" s="7">
-        <f t="shared" si="176"/>
+        <f t="shared" si="183"/>
         <v>4358</v>
       </c>
       <c r="AA92" s="7">
-        <f t="shared" si="176"/>
+        <f t="shared" si="183"/>
         <v>1386</v>
       </c>
       <c r="AB92" s="7">
-        <f t="shared" si="176"/>
+        <f t="shared" si="183"/>
         <v>1723</v>
       </c>
       <c r="AC92" s="5"/>
@@ -10267,23 +10371,23 @@
         <v>19726</v>
       </c>
       <c r="X94" s="5">
-        <f t="shared" ref="X94:AB94" si="177">X95-X112</f>
+        <f t="shared" ref="X94:AB94" si="184">X95-X112</f>
         <v>25105</v>
       </c>
       <c r="Y94" s="5">
-        <f t="shared" si="177"/>
+        <f t="shared" si="184"/>
         <v>26958</v>
       </c>
       <c r="Z94" s="5">
-        <f t="shared" si="177"/>
+        <f t="shared" si="184"/>
         <v>23864</v>
       </c>
       <c r="AA94" s="5">
-        <f t="shared" si="177"/>
+        <f t="shared" si="184"/>
         <v>21503</v>
       </c>
       <c r="AB94" s="5">
-        <f t="shared" si="177"/>
+        <f t="shared" si="184"/>
         <v>22975</v>
       </c>
       <c r="AC94" s="5"/>
@@ -10305,47 +10409,47 @@
         <v>30955</v>
       </c>
       <c r="AZ94" s="4">
-        <f t="shared" ref="AZ94:BE94" si="178">AY94+AZ67</f>
+        <f t="shared" ref="AZ94:BE94" si="185">AY94+AZ67</f>
         <v>34749</v>
       </c>
       <c r="BA94" s="4">
-        <f t="shared" si="178"/>
+        <f t="shared" si="185"/>
         <v>43159.260333394857</v>
       </c>
       <c r="BB94" s="4">
-        <f t="shared" si="178"/>
+        <f t="shared" si="185"/>
         <v>55500.240720403555</v>
       </c>
       <c r="BC94" s="4">
-        <f t="shared" si="178"/>
+        <f t="shared" si="185"/>
         <v>74529.598656204616</v>
       </c>
       <c r="BD94" s="4">
-        <f t="shared" si="178"/>
+        <f t="shared" si="185"/>
         <v>101291.45335097787</v>
       </c>
       <c r="BE94" s="4">
-        <f t="shared" si="178"/>
+        <f t="shared" si="185"/>
         <v>136263.66728749863</v>
       </c>
       <c r="BF94" s="4">
-        <f t="shared" ref="BF94" si="179">BE94+BF67</f>
+        <f t="shared" ref="BF94" si="186">BE94+BF67</f>
         <v>176919.20303289191</v>
       </c>
       <c r="BG94" s="4">
-        <f t="shared" ref="BG94" si="180">BF94+BG67</f>
+        <f t="shared" ref="BG94" si="187">BF94+BG67</f>
         <v>223981.54517992723</v>
       </c>
       <c r="BH94" s="4">
-        <f t="shared" ref="BH94" si="181">BG94+BH67</f>
+        <f t="shared" ref="BH94" si="188">BG94+BH67</f>
         <v>278255.91675683646</v>
       </c>
       <c r="BI94" s="4">
-        <f t="shared" ref="BI94" si="182">BH94+BI67</f>
+        <f t="shared" ref="BI94" si="189">BH94+BI67</f>
         <v>340637.89516665344</v>
       </c>
       <c r="BJ94" s="4">
-        <f t="shared" ref="BJ94" si="183">BI94+BJ67</f>
+        <f t="shared" ref="BJ94" si="190">BI94+BJ67</f>
         <v>412122.89674419607</v>
       </c>
     </row>
@@ -10391,7 +10495,7 @@
         <v>25105</v>
       </c>
       <c r="Y95" s="5">
-        <f t="shared" ref="Y95" si="184">X95+Y67</f>
+        <f t="shared" ref="Y95" si="191">X95+Y67</f>
         <v>26958</v>
       </c>
       <c r="Z95" s="35">
@@ -10998,39 +11102,39 @@
         <v>62131</v>
       </c>
       <c r="T106" s="5">
-        <f t="shared" ref="T106:AB106" si="185">SUM(T95:T105)</f>
+        <f t="shared" ref="T106:AB106" si="192">SUM(T95:T105)</f>
         <v>68513</v>
       </c>
       <c r="U106" s="5">
-        <f t="shared" si="185"/>
+        <f t="shared" si="192"/>
         <v>74426</v>
       </c>
       <c r="V106" s="5">
-        <f t="shared" si="185"/>
+        <f t="shared" si="192"/>
         <v>0</v>
       </c>
       <c r="W106" s="5">
-        <f t="shared" si="185"/>
+        <f t="shared" si="192"/>
         <v>86833</v>
       </c>
       <c r="X106" s="5">
-        <f t="shared" si="185"/>
+        <f t="shared" si="192"/>
         <v>25105</v>
       </c>
       <c r="Y106" s="5">
-        <f t="shared" si="185"/>
+        <f t="shared" si="192"/>
         <v>26958</v>
       </c>
       <c r="Z106" s="5">
-        <f t="shared" si="185"/>
+        <f t="shared" si="192"/>
         <v>106618</v>
       </c>
       <c r="AA106" s="5">
-        <f t="shared" si="185"/>
+        <f t="shared" si="192"/>
         <v>109226</v>
       </c>
       <c r="AB106" s="5">
-        <f t="shared" si="185"/>
+        <f t="shared" si="192"/>
         <v>112832</v>
       </c>
       <c r="AC106" s="5"/>
@@ -11340,51 +11444,51 @@
         <v>1201</v>
       </c>
       <c r="AY118" s="4">
-        <f t="shared" ref="AY118:BE118" si="186">+AY37*AY123*8/1000</f>
+        <f t="shared" ref="AY118:BE118" si="193">+AY37*AY123*8/1000</f>
         <v>1774.5040319999998</v>
       </c>
       <c r="AZ118" s="4">
-        <f t="shared" si="186"/>
+        <f t="shared" si="193"/>
         <v>2094.24512</v>
       </c>
       <c r="BA118" s="4">
-        <f t="shared" si="186"/>
+        <f t="shared" si="193"/>
         <v>2800.3888000000002</v>
       </c>
       <c r="BB118" s="4">
-        <f t="shared" si="186"/>
+        <f t="shared" si="193"/>
         <v>3860.0812799999999</v>
       </c>
       <c r="BC118" s="4">
-        <f t="shared" si="186"/>
+        <f t="shared" si="193"/>
         <v>5265.0124800000003</v>
       </c>
       <c r="BD118" s="4">
-        <f t="shared" si="186"/>
+        <f t="shared" si="193"/>
         <v>7730.9465600000003</v>
       </c>
       <c r="BE118" s="4">
-        <f t="shared" si="186"/>
+        <f t="shared" si="193"/>
         <v>10850.909065919999</v>
       </c>
       <c r="BF118" s="4">
-        <f t="shared" ref="BF118:BJ118" si="187">+BF37*BF123*8/1000</f>
+        <f t="shared" ref="BF118:BJ118" si="194">+BF37*BF123*8/1000</f>
         <v>11709.939366971999</v>
       </c>
       <c r="BG118" s="4">
-        <f t="shared" si="187"/>
+        <f t="shared" si="194"/>
         <v>12627.745425464402</v>
       </c>
       <c r="BH118" s="4">
-        <f t="shared" si="187"/>
+        <f t="shared" si="194"/>
         <v>13608.057241388613</v>
       </c>
       <c r="BI118" s="4">
-        <f t="shared" si="187"/>
+        <f t="shared" si="194"/>
         <v>14654.830875341582</v>
       </c>
       <c r="BJ118" s="4">
-        <f t="shared" si="187"/>
+        <f t="shared" si="194"/>
         <v>15772.261729586378</v>
       </c>
     </row>
@@ -11430,47 +11534,47 @@
         <v>221.81300399999998</v>
       </c>
       <c r="AZ121" s="4">
-        <f t="shared" ref="AZ121:BE121" si="188">+AZ118/8</f>
+        <f t="shared" ref="AZ121:BE121" si="195">+AZ118/8</f>
         <v>261.78064000000001</v>
       </c>
       <c r="BA121" s="4">
-        <f t="shared" si="188"/>
+        <f t="shared" si="195"/>
         <v>350.04860000000002</v>
       </c>
       <c r="BB121" s="4">
-        <f t="shared" si="188"/>
+        <f t="shared" si="195"/>
         <v>482.51015999999998</v>
       </c>
       <c r="BC121" s="4">
-        <f t="shared" si="188"/>
+        <f t="shared" si="195"/>
         <v>658.12656000000004</v>
       </c>
       <c r="BD121" s="4">
-        <f t="shared" si="188"/>
+        <f t="shared" si="195"/>
         <v>966.36832000000004</v>
       </c>
       <c r="BE121" s="4">
-        <f t="shared" si="188"/>
+        <f t="shared" si="195"/>
         <v>1356.3636332399999</v>
       </c>
       <c r="BF121" s="4">
-        <f t="shared" ref="BF121:BJ121" si="189">+BF118/8</f>
+        <f t="shared" ref="BF121:BJ121" si="196">+BF118/8</f>
         <v>1463.7424208714999</v>
       </c>
       <c r="BG121" s="4">
-        <f t="shared" si="189"/>
+        <f t="shared" si="196"/>
         <v>1578.4681781830502</v>
       </c>
       <c r="BH121" s="4">
-        <f t="shared" si="189"/>
+        <f t="shared" si="196"/>
         <v>1701.0071551735766</v>
       </c>
       <c r="BI121" s="4">
-        <f t="shared" si="189"/>
+        <f t="shared" si="196"/>
         <v>1831.8538594176978</v>
       </c>
       <c r="BJ121" s="4">
-        <f t="shared" si="189"/>
+        <f t="shared" si="196"/>
         <v>1971.5327161982973</v>
       </c>
     </row>

--- a/TSLA.xlsx
+++ b/TSLA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BBF530E-7689-4017-AA09-39AAEEA2B7DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E99E29B2-9C69-43CE-B25D-5CD93FE27A15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -932,16 +932,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>547688</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>113110</xdr:rowOff>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>5954</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>136923</xdr:rowOff>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>17860</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>23813</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -956,7 +956,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="21895594" y="113110"/>
+          <a:off x="22467094" y="160735"/>
           <a:ext cx="17860" cy="12078891"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1314,18 +1314,18 @@
         <v>0</v>
       </c>
       <c r="K2" s="41">
-        <v>373.72</v>
+        <v>352.05</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J3" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="K3" s="4">
-        <v>3755.7238710000001</v>
+      <c r="K3" s="5">
+        <v>3237</v>
       </c>
       <c r="L3" s="47" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="K4" s="10">
         <f>K2*K3</f>
-        <v>1403589.1250701202</v>
+        <v>1139585.8500000001</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
@@ -1351,11 +1351,10 @@
         <v>3</v>
       </c>
       <c r="K5" s="10">
-        <f>16603+28140</f>
-        <v>44743</v>
+        <v>43524</v>
       </c>
       <c r="L5" s="47" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
@@ -1366,11 +1365,11 @@
         <v>4</v>
       </c>
       <c r="K6" s="17">
-        <f>1447+7782</f>
-        <v>9229</v>
+        <f>1418+7924</f>
+        <v>9342</v>
       </c>
       <c r="L6" s="47" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
@@ -1379,7 +1378,7 @@
       </c>
       <c r="K7" s="10">
         <f>K4-K5+K6</f>
-        <v>1368075.1250701202</v>
+        <v>1105403.8500000001</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
@@ -2882,7 +2881,9 @@
       <c r="AI35" s="5">
         <v>16130</v>
       </c>
-      <c r="AJ35" s="5"/>
+      <c r="AJ35" s="5">
+        <v>12465</v>
+      </c>
       <c r="AK35" s="5"/>
       <c r="AL35" s="5"/>
       <c r="AT35" s="4">
@@ -3022,7 +3023,9 @@
       <c r="AI36" s="5">
         <v>341893</v>
       </c>
-      <c r="AJ36" s="5"/>
+      <c r="AJ36" s="5">
+        <v>467762</v>
+      </c>
       <c r="AK36" s="5"/>
       <c r="AL36" s="5"/>
       <c r="AT36" s="4">
@@ -3188,7 +3191,9 @@
       <c r="AI37" s="7">
         <v>358023</v>
       </c>
-      <c r="AJ37" s="7"/>
+      <c r="AJ37" s="7">
+        <v>480126</v>
+      </c>
       <c r="AK37" s="7"/>
       <c r="AL37" s="7"/>
       <c r="AT37" s="6">
@@ -3224,39 +3229,35 @@
         <v>1750243</v>
       </c>
       <c r="BB37" s="6">
-        <f t="shared" si="14"/>
-        <v>2010459</v>
+        <v>1824568</v>
       </c>
       <c r="BC37" s="6">
-        <f t="shared" si="14"/>
-        <v>2350452</v>
+        <v>2065389</v>
       </c>
       <c r="BD37" s="6">
-        <f t="shared" si="14"/>
-        <v>3019901</v>
+        <v>2365715</v>
       </c>
       <c r="BE37" s="6">
-        <f t="shared" ref="BE37" si="15">BE42</f>
-        <v>3767676.7590000001</v>
+        <v>2649054</v>
       </c>
       <c r="BF37" s="6">
-        <f t="shared" ref="BF37:BJ37" si="16">BF42</f>
+        <f t="shared" ref="BF37:BJ37" si="15">BF42</f>
         <v>3956060.5969500002</v>
       </c>
       <c r="BG37" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>4153863.6267975005</v>
       </c>
       <c r="BH37" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>4361556.8081373759</v>
       </c>
       <c r="BI37" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>4579634.6485442445</v>
       </c>
       <c r="BJ37" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>4808616.3809714569</v>
       </c>
     </row>
@@ -3269,91 +3270,91 @@
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
       <c r="G38" s="5">
-        <f t="shared" ref="G38:AB38" si="17">G45*1000000/G37</f>
+        <f t="shared" ref="G38:AB38" si="16">G45*1000000/G37</f>
         <v>55681.619828940478</v>
       </c>
       <c r="H38" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>54196.904232560089</v>
       </c>
       <c r="I38" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>52805.95970613051</v>
       </c>
       <c r="J38" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>54801.730674873994</v>
       </c>
       <c r="K38" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>55290.634604953899</v>
       </c>
       <c r="L38" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>54175.399889685606</v>
       </c>
       <c r="M38" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>52735.10409188801</v>
       </c>
       <c r="N38" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>47809.713684443705</v>
       </c>
       <c r="O38" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>44301.948051948049</v>
       </c>
       <c r="P38" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>47304.34782608696</v>
       </c>
       <c r="Q38" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>47215.084956485705</v>
       </c>
       <c r="R38" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>48687.621516526247</v>
       </c>
       <c r="S38" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>50037.413561771078</v>
       </c>
       <c r="T38" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>53672.039105596894</v>
       </c>
       <c r="U38" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>51726.143733821948</v>
       </c>
       <c r="V38" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>51902.644604444358</v>
       </c>
       <c r="W38" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>44642.033697901272</v>
       </c>
       <c r="X38" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>43804.436435405674</v>
       </c>
       <c r="Y38" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>42711.448332295156</v>
       </c>
       <c r="Z38" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>42579.364178432923</v>
       </c>
       <c r="AA38" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>42553.191489361699</v>
       </c>
       <c r="AB38" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>41738.370469145593</v>
       </c>
       <c r="AC38" s="5">
@@ -3361,11 +3362,11 @@
         <v>41320.986764454137</v>
       </c>
       <c r="AD38" s="5">
-        <f>+Z38*1.05</f>
+        <f t="shared" ref="AD38:AJ38" si="17">+Z38*1.05</f>
         <v>44708.332387354574</v>
       </c>
       <c r="AE38" s="5">
-        <f>+AA38*1.05</f>
+        <f t="shared" si="17"/>
         <v>44680.851063829788</v>
       </c>
       <c r="AF38" s="5">
@@ -3373,18 +3374,21 @@
         <v>43825.288992602873</v>
       </c>
       <c r="AG38" s="5">
-        <f>+AC38*1.05</f>
+        <f t="shared" si="17"/>
         <v>43387.036102676844</v>
       </c>
       <c r="AH38" s="5">
-        <f>+AD38*1.05</f>
+        <f t="shared" si="17"/>
         <v>46943.749006722304</v>
       </c>
       <c r="AI38" s="5">
-        <f>+AE38*1.05</f>
+        <f t="shared" si="17"/>
         <v>46914.893617021276</v>
       </c>
-      <c r="AJ38" s="5"/>
+      <c r="AJ38" s="5">
+        <f>+AF38*1.05</f>
+        <v>46016.553442233017</v>
+      </c>
       <c r="AK38" s="5"/>
       <c r="AL38" s="5"/>
       <c r="AT38" s="5">
@@ -3591,7 +3595,9 @@
       <c r="AI40" s="5">
         <v>13775</v>
       </c>
-      <c r="AJ40" s="5"/>
+      <c r="AJ40" s="5">
+        <v>8822</v>
+      </c>
       <c r="AK40" s="5"/>
       <c r="AL40" s="5"/>
       <c r="AT40" s="4">
@@ -3719,7 +3725,9 @@
       <c r="AI41" s="5">
         <v>394611</v>
       </c>
-      <c r="AJ41" s="5"/>
+      <c r="AJ41" s="5">
+        <v>442936</v>
+      </c>
       <c r="AK41" s="5"/>
       <c r="AL41" s="5"/>
       <c r="AT41" s="4">
@@ -3873,7 +3881,9 @@
       <c r="AI42" s="7">
         <v>408386</v>
       </c>
-      <c r="AJ42" s="7"/>
+      <c r="AJ42" s="7">
+        <v>451758</v>
+      </c>
       <c r="AK42" s="7"/>
       <c r="AL42" s="7"/>
       <c r="AT42" s="6">
@@ -4031,19 +4041,19 @@
       </c>
       <c r="BB44" s="4">
         <f t="shared" si="30"/>
-        <v>2659.0812799999999</v>
+        <v>2302.17056</v>
       </c>
       <c r="BC44" s="4">
         <f t="shared" si="30"/>
-        <v>4064.0124800000003</v>
+        <v>3425.4713600000005</v>
       </c>
       <c r="BD44" s="4">
         <f t="shared" si="30"/>
-        <v>6529.9465600000003</v>
+        <v>4855.2304000000004</v>
       </c>
       <c r="BE44" s="4">
         <f t="shared" si="30"/>
-        <v>9649.9090659199992</v>
+        <v>6428.2755199999992</v>
       </c>
       <c r="BF44" s="4">
         <f t="shared" si="30"/>
@@ -4169,7 +4179,9 @@
       <c r="AI45" s="5">
         <v>15473</v>
       </c>
-      <c r="AJ45" s="5"/>
+      <c r="AJ45" s="5">
+        <v>20006</v>
+      </c>
       <c r="AK45" s="5"/>
       <c r="AL45" s="5"/>
       <c r="AT45" s="4">
@@ -4338,7 +4350,9 @@
       <c r="AI46" s="5">
         <v>380</v>
       </c>
-      <c r="AJ46" s="5"/>
+      <c r="AJ46" s="5">
+        <v>146</v>
+      </c>
       <c r="AK46" s="5"/>
       <c r="AL46" s="5"/>
       <c r="AT46" s="4">
@@ -4467,7 +4481,9 @@
       <c r="AI47" s="5">
         <v>381</v>
       </c>
-      <c r="AJ47" s="5"/>
+      <c r="AJ47" s="5">
+        <v>364</v>
+      </c>
       <c r="AK47" s="5"/>
       <c r="AL47" s="5"/>
       <c r="AT47" s="4">
@@ -4620,7 +4636,9 @@
       <c r="AI48" s="7">
         <v>16234</v>
       </c>
-      <c r="AJ48" s="7"/>
+      <c r="AJ48" s="7">
+        <v>20516</v>
+      </c>
       <c r="AK48" s="7"/>
       <c r="AL48" s="7"/>
       <c r="AT48" s="6">
@@ -4791,7 +4809,9 @@
       <c r="AI49" s="5">
         <v>2408</v>
       </c>
-      <c r="AJ49" s="5"/>
+      <c r="AJ49" s="5">
+        <v>3139</v>
+      </c>
       <c r="AK49" s="5"/>
       <c r="AL49" s="5"/>
       <c r="AN49" s="4">
@@ -4929,7 +4949,9 @@
       <c r="AI50" s="5">
         <v>3745</v>
       </c>
-      <c r="AJ50" s="5"/>
+      <c r="AJ50" s="5">
+        <v>4581</v>
+      </c>
       <c r="AK50" s="5"/>
       <c r="AL50" s="5"/>
       <c r="AN50" s="4">
@@ -5037,7 +5059,7 @@
         <v>21454</v>
       </c>
       <c r="V51" s="7">
-        <f t="shared" ref="V51:AI51" si="48">SUM(V48:V50)</f>
+        <f t="shared" ref="V51:AJ51" si="48">SUM(V48:V50)</f>
         <v>24806.6</v>
       </c>
       <c r="W51" s="7">
@@ -5092,7 +5114,10 @@
         <f t="shared" si="48"/>
         <v>22387</v>
       </c>
-      <c r="AJ51" s="7"/>
+      <c r="AJ51" s="7">
+        <f t="shared" si="48"/>
+        <v>28236</v>
+      </c>
       <c r="AK51" s="7"/>
       <c r="AL51" s="7"/>
       <c r="AN51" s="6">
@@ -5150,19 +5175,19 @@
       </c>
       <c r="BB51" s="6">
         <f t="shared" ref="BB51:BE51" si="50">SUM(BB48:BB50)+BB44</f>
-        <v>109006.25828165848</v>
+        <v>108649.34756165848</v>
       </c>
       <c r="BC51" s="6">
         <f t="shared" si="50"/>
-        <v>135509.12325404989</v>
+        <v>134870.58213404988</v>
       </c>
       <c r="BD51" s="6">
         <f t="shared" si="50"/>
-        <v>162226.6802718621</v>
+        <v>160551.96411186209</v>
       </c>
       <c r="BE51" s="6">
         <f t="shared" si="50"/>
-        <v>186054.30836145976</v>
+        <v>182832.67481553977</v>
       </c>
       <c r="BF51" s="6">
         <f t="shared" ref="BF51" si="51">SUM(BF48:BF50)+BF44</f>
@@ -5283,7 +5308,9 @@
       <c r="AI52" s="5">
         <v>12616</v>
       </c>
-      <c r="AJ52" s="5"/>
+      <c r="AJ52" s="5">
+        <v>16866</v>
+      </c>
       <c r="AK52" s="5"/>
       <c r="AL52" s="5"/>
       <c r="AN52" s="4">
@@ -5313,19 +5340,19 @@
       </c>
       <c r="BB52" s="4">
         <f>BB51*0.78</f>
-        <v>85024.881459693614</v>
+        <v>84746.491098093611</v>
       </c>
       <c r="BC52" s="4">
         <f>BC51*0.77</f>
-        <v>104342.02490561841</v>
+        <v>103850.34824321841</v>
       </c>
       <c r="BD52" s="4">
         <f>BD51*0.76</f>
-        <v>123292.2770066152</v>
+        <v>122019.4927250152</v>
       </c>
       <c r="BE52" s="4">
         <f>BE51*0.75</f>
-        <v>139540.73127109482</v>
+        <v>137124.50611165483</v>
       </c>
       <c r="BF52" s="4">
         <f t="shared" ref="BF52:BJ52" si="58">BF51*0.75</f>
@@ -5437,7 +5464,7 @@
         <v>3428</v>
       </c>
       <c r="AA53" s="5">
-        <f t="shared" ref="AA53:AI53" si="62">AA45-AA52</f>
+        <f t="shared" ref="AA53:AG53" si="62">AA45-AA52</f>
         <v>2563</v>
       </c>
       <c r="AB53" s="5">
@@ -5472,7 +5499,10 @@
         <f>AI45-AI52</f>
         <v>2857</v>
       </c>
-      <c r="AJ53" s="5"/>
+      <c r="AJ53" s="5">
+        <f>AJ45-AJ52</f>
+        <v>3140</v>
+      </c>
       <c r="AK53" s="5"/>
       <c r="AL53" s="5"/>
       <c r="AV53" s="4">
@@ -5593,7 +5623,9 @@
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="AJ54" s="5"/>
+      <c r="AJ54" s="5">
+        <v>0</v>
+      </c>
       <c r="AK54" s="5"/>
       <c r="AL54" s="5"/>
       <c r="AW54" s="4">
@@ -5708,7 +5740,9 @@
       <c r="AI55" s="5">
         <v>196</v>
       </c>
-      <c r="AJ55" s="5"/>
+      <c r="AJ55" s="5">
+        <v>187</v>
+      </c>
       <c r="AK55" s="5"/>
       <c r="AL55" s="5"/>
       <c r="AW55" s="4">
@@ -5795,7 +5829,7 @@
         <v>5212</v>
       </c>
       <c r="V56" s="5">
-        <f t="shared" ref="V56:AI56" si="67">V48-V55-V52</f>
+        <f t="shared" ref="V56:AG56" si="67">V48-V55-V52</f>
         <v>6568.7999999999993</v>
       </c>
       <c r="W56" s="5">
@@ -5850,7 +5884,10 @@
         <f>AI48-AI55-AI52</f>
         <v>3422</v>
       </c>
-      <c r="AJ56" s="5"/>
+      <c r="AJ56" s="5">
+        <f>AJ48-AJ55-AJ52</f>
+        <v>3463</v>
+      </c>
       <c r="AK56" s="5"/>
       <c r="AL56" s="5"/>
       <c r="AW56" s="4">
@@ -5875,19 +5912,19 @@
       </c>
       <c r="BB56" s="4">
         <f t="shared" si="68"/>
-        <v>23981.376821964863</v>
+        <v>23902.856463564865</v>
       </c>
       <c r="BC56" s="4">
         <f t="shared" si="68"/>
-        <v>31167.098348431478</v>
+        <v>31020.23389083147</v>
       </c>
       <c r="BD56" s="4">
         <f t="shared" si="68"/>
-        <v>38934.403265246903</v>
+        <v>38532.471386846897</v>
       </c>
       <c r="BE56" s="4">
         <f t="shared" si="68"/>
-        <v>46513.577090364939</v>
+        <v>45708.168703884934</v>
       </c>
       <c r="BF56" s="4">
         <f t="shared" si="68"/>
@@ -6008,7 +6045,9 @@
       <c r="AI57" s="5">
         <v>1456</v>
       </c>
-      <c r="AJ57" s="5"/>
+      <c r="AJ57" s="5">
+        <v>2499</v>
+      </c>
       <c r="AK57" s="5"/>
       <c r="AL57" s="5"/>
       <c r="AW57" s="4">
@@ -6124,7 +6163,9 @@
       <c r="AI58" s="5">
         <v>3399</v>
       </c>
-      <c r="AJ58" s="5"/>
+      <c r="AJ58" s="5">
+        <v>3933</v>
+      </c>
       <c r="AK58" s="5"/>
       <c r="AL58" s="5"/>
       <c r="AW58" s="4">
@@ -6266,7 +6307,10 @@
         <f>+AI51-AI52-AI54-AI55-AI57-AI58</f>
         <v>4720</v>
       </c>
-      <c r="AJ59" s="46"/>
+      <c r="AJ59" s="46">
+        <f>+AJ51-AJ52-AJ54-AJ55-AJ57-AJ58</f>
+        <v>4751</v>
+      </c>
       <c r="AK59" s="46"/>
       <c r="AL59" s="46"/>
       <c r="AW59" s="5">
@@ -6291,19 +6335,19 @@
       </c>
       <c r="BB59" s="4">
         <f t="shared" si="74"/>
-        <v>23981.376821964863</v>
+        <v>23902.856463564865</v>
       </c>
       <c r="BC59" s="4">
         <f t="shared" si="74"/>
-        <v>31167.098348431478</v>
+        <v>31020.23389083147</v>
       </c>
       <c r="BD59" s="4">
         <f t="shared" si="74"/>
-        <v>38934.403265246903</v>
+        <v>38532.471386846897</v>
       </c>
       <c r="BE59" s="4">
         <f t="shared" si="74"/>
-        <v>46513.577090364939</v>
+        <v>45708.168703884934</v>
       </c>
       <c r="BF59" s="4">
         <f t="shared" si="74"/>
@@ -6424,7 +6468,9 @@
       <c r="AI60" s="5">
         <v>1946</v>
       </c>
-      <c r="AJ60" s="5"/>
+      <c r="AJ60" s="5">
+        <v>2371</v>
+      </c>
       <c r="AK60" s="5"/>
       <c r="AL60" s="5"/>
       <c r="AW60" s="4">
@@ -6583,7 +6629,9 @@
       <c r="AI61" s="5">
         <v>1833</v>
       </c>
-      <c r="AJ61" s="5"/>
+      <c r="AJ61" s="5">
+        <v>1982</v>
+      </c>
       <c r="AK61" s="5"/>
       <c r="AL61" s="5"/>
       <c r="AW61" s="4">
@@ -6712,7 +6760,7 @@
         <v>1694</v>
       </c>
       <c r="V62" s="5">
-        <f t="shared" ref="V62:AI62" si="85">V60+V61</f>
+        <f t="shared" ref="V62:AJ62" si="85">V60+V61</f>
         <v>2602.8000000000002</v>
       </c>
       <c r="W62" s="5">
@@ -6767,7 +6815,10 @@
         <f t="shared" si="85"/>
         <v>3779</v>
       </c>
-      <c r="AJ62" s="5"/>
+      <c r="AJ62" s="5">
+        <f t="shared" si="85"/>
+        <v>4353</v>
+      </c>
       <c r="AK62" s="5"/>
       <c r="AL62" s="5"/>
       <c r="AW62" s="4">
@@ -6951,7 +7002,10 @@
         <f>AI59-AI62</f>
         <v>941</v>
       </c>
-      <c r="AJ63" s="5"/>
+      <c r="AJ63" s="5">
+        <f>AJ59-AJ62</f>
+        <v>398</v>
+      </c>
       <c r="AK63" s="5"/>
       <c r="AL63" s="5"/>
       <c r="AW63" s="5">
@@ -6976,19 +7030,19 @@
       </c>
       <c r="BB63" s="5">
         <f t="shared" si="97"/>
-        <v>10202.874421964862</v>
+        <v>10124.354063564864</v>
       </c>
       <c r="BC63" s="5">
         <f t="shared" si="97"/>
-        <v>16837.455852431478</v>
+        <v>16690.59139483147</v>
       </c>
       <c r="BD63" s="5">
         <f t="shared" si="97"/>
-        <v>24031.575069406899</v>
+        <v>23629.643191006893</v>
       </c>
       <c r="BE63" s="5">
         <f t="shared" si="97"/>
-        <v>31014.635766691335</v>
+        <v>30209.22738021133</v>
       </c>
       <c r="BF63" s="5">
         <f t="shared" ref="BF63:BJ63" si="98">BF59-BF62</f>
@@ -7129,7 +7183,10 @@
         <f>434-92-535</f>
         <v>-193</v>
       </c>
-      <c r="AJ64" s="5"/>
+      <c r="AJ64" s="5">
+        <f>422-81+590</f>
+        <v>931</v>
+      </c>
       <c r="AK64" s="5"/>
       <c r="AL64" s="5"/>
       <c r="AX64" s="4">
@@ -7154,35 +7211,35 @@
       </c>
       <c r="BC64" s="4">
         <f t="shared" si="99"/>
-        <v>5550.0240720403563</v>
+        <v>5543.3498415763561</v>
       </c>
       <c r="BD64" s="4">
         <f t="shared" si="99"/>
-        <v>7452.9598656204616</v>
+        <v>7433.2348466710218</v>
       </c>
       <c r="BE64" s="4">
         <f t="shared" si="99"/>
-        <v>10129.145335097788</v>
+        <v>10073.579479873646</v>
       </c>
       <c r="BF64" s="4">
         <f t="shared" si="99"/>
-        <v>13626.366728749863</v>
+        <v>13497.61806298087</v>
       </c>
       <c r="BG64" s="4">
         <f t="shared" si="99"/>
-        <v>17691.920303289193</v>
+        <v>17552.228000929834</v>
       </c>
       <c r="BH64" s="4">
         <f t="shared" si="99"/>
-        <v>22398.154517992723</v>
+        <v>22246.588369932822</v>
       </c>
       <c r="BI64" s="4">
         <f t="shared" si="99"/>
-        <v>27825.591675683649</v>
+        <v>27661.142405038659</v>
       </c>
       <c r="BJ64" s="4">
         <f t="shared" si="99"/>
-        <v>34063.789516665347</v>
+        <v>33885.362058015533</v>
       </c>
     </row>
     <row r="65" spans="2:113" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -7254,7 +7311,7 @@
         <v>3636</v>
       </c>
       <c r="V65" s="5">
-        <f t="shared" ref="V65:AI65" si="102">V63+V64</f>
+        <f t="shared" ref="V65:AJ65" si="102">V63+V64</f>
         <v>3744.7999999999984</v>
       </c>
       <c r="W65" s="5">
@@ -7309,7 +7366,10 @@
         <f t="shared" si="102"/>
         <v>748</v>
       </c>
-      <c r="AJ65" s="5"/>
+      <c r="AJ65" s="5">
+        <f t="shared" si="102"/>
+        <v>1329</v>
+      </c>
       <c r="AK65" s="5"/>
       <c r="AL65" s="5"/>
       <c r="AX65" s="4">
@@ -7330,39 +7390,39 @@
       </c>
       <c r="BB65" s="4">
         <f t="shared" si="103"/>
-        <v>14518.800455304347</v>
+        <v>14440.280096904349</v>
       </c>
       <c r="BC65" s="4">
         <f t="shared" si="103"/>
-        <v>22387.479924471834</v>
+        <v>22233.941236407827</v>
       </c>
       <c r="BD65" s="4">
         <f t="shared" si="103"/>
-        <v>31484.534935027361</v>
+        <v>31062.878037677914</v>
       </c>
       <c r="BE65" s="4">
         <f t="shared" si="103"/>
-        <v>41143.781101789122</v>
+        <v>40282.80686008498</v>
       </c>
       <c r="BF65" s="4">
         <f t="shared" si="103"/>
-        <v>47830.042053403864</v>
+        <v>47701.293387634869</v>
       </c>
       <c r="BG65" s="4">
         <f t="shared" si="103"/>
-        <v>55367.461349453326</v>
+        <v>55227.769047093971</v>
       </c>
       <c r="BH65" s="4">
         <f t="shared" si="103"/>
-        <v>63852.201855187377</v>
+        <v>63700.635707127483</v>
       </c>
       <c r="BI65" s="4">
         <f t="shared" si="103"/>
-        <v>73390.562835078817</v>
+        <v>73226.113564433836</v>
       </c>
       <c r="BJ65" s="4">
         <f t="shared" si="103"/>
-        <v>84100.001855932467</v>
+        <v>83921.57439728266</v>
       </c>
     </row>
     <row r="66" spans="2:113" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -7485,7 +7545,10 @@
         <f>257+14</f>
         <v>271</v>
       </c>
-      <c r="AJ66" s="5"/>
+      <c r="AJ66" s="5">
+        <f>201+14</f>
+        <v>215</v>
+      </c>
       <c r="AK66" s="5"/>
       <c r="AL66" s="5"/>
       <c r="AX66" s="4">
@@ -7506,39 +7569,39 @@
       </c>
       <c r="BB66" s="4">
         <f t="shared" si="104"/>
-        <v>2177.8200682956517</v>
+        <v>2166.0420145356525</v>
       </c>
       <c r="BC66" s="4">
         <f t="shared" si="104"/>
-        <v>3358.121988670775</v>
+        <v>3335.0911854611741</v>
       </c>
       <c r="BD66" s="4">
         <f t="shared" si="104"/>
-        <v>4722.6802402541043</v>
+        <v>4659.4317056516866</v>
       </c>
       <c r="BE66" s="4">
         <f t="shared" si="104"/>
-        <v>6171.5671652683677</v>
+        <v>6042.4210290127467</v>
       </c>
       <c r="BF66" s="4">
         <f t="shared" ref="BF66:BJ66" si="105">+BF65*0.15</f>
-        <v>7174.5063080105792</v>
+        <v>7155.1940081452303</v>
       </c>
       <c r="BG66" s="4">
         <f t="shared" si="105"/>
-        <v>8305.1192024179982</v>
+        <v>8284.1653570640956</v>
       </c>
       <c r="BH66" s="4">
         <f t="shared" si="105"/>
-        <v>9577.8302782781066</v>
+        <v>9555.0953560691214</v>
       </c>
       <c r="BI66" s="4">
         <f t="shared" si="105"/>
-        <v>11008.584425261823</v>
+        <v>10983.917034665075</v>
       </c>
       <c r="BJ66" s="4">
         <f t="shared" si="105"/>
-        <v>12615.000278389869</v>
+        <v>12588.236159592399</v>
       </c>
     </row>
     <row r="67" spans="2:113" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -7610,7 +7673,7 @@
         <v>3331</v>
       </c>
       <c r="V67" s="5">
-        <f t="shared" ref="V67:AI67" si="108">V65-V66</f>
+        <f t="shared" ref="V67:AJ67" si="108">V65-V66</f>
         <v>3468.7999999999984</v>
       </c>
       <c r="W67" s="5">
@@ -7665,7 +7728,10 @@
         <f t="shared" si="108"/>
         <v>477</v>
       </c>
-      <c r="AJ67" s="5"/>
+      <c r="AJ67" s="5">
+        <f t="shared" si="108"/>
+        <v>1114</v>
+      </c>
       <c r="AK67" s="5"/>
       <c r="AL67" s="5"/>
       <c r="AX67" s="4">
@@ -7686,243 +7752,243 @@
       </c>
       <c r="BB67" s="4">
         <f t="shared" si="110"/>
-        <v>12340.980387008694</v>
+        <v>12274.238082368696</v>
       </c>
       <c r="BC67" s="4">
         <f t="shared" si="110"/>
-        <v>19029.357935801061</v>
+        <v>18898.850050946654</v>
       </c>
       <c r="BD67" s="4">
         <f t="shared" si="110"/>
-        <v>26761.854694773258</v>
+        <v>26403.446332026229</v>
       </c>
       <c r="BE67" s="4">
         <f t="shared" si="110"/>
-        <v>34972.213936520755</v>
+        <v>34240.385831072235</v>
       </c>
       <c r="BF67" s="4">
         <f t="shared" ref="BF67:BJ67" si="111">+BF65-BF66</f>
-        <v>40655.535745393281</v>
+        <v>40546.099379489635</v>
       </c>
       <c r="BG67" s="4">
         <f t="shared" si="111"/>
-        <v>47062.342147035328</v>
+        <v>46943.603690029879</v>
       </c>
       <c r="BH67" s="4">
         <f t="shared" si="111"/>
-        <v>54274.371576909267</v>
+        <v>54145.540351058364</v>
       </c>
       <c r="BI67" s="4">
         <f t="shared" si="111"/>
-        <v>62381.978409816991</v>
+        <v>62242.196529768757</v>
       </c>
       <c r="BJ67" s="4">
         <f t="shared" si="111"/>
-        <v>71485.0015775426</v>
+        <v>71333.338237690259</v>
       </c>
       <c r="BK67" s="4">
         <f t="shared" ref="BK67:CP67" si="112">BJ67*(1+$BL$78)</f>
-        <v>70770.151561767168</v>
+        <v>70620.004855313353</v>
       </c>
       <c r="BL67" s="4">
         <f t="shared" si="112"/>
-        <v>70062.45004614949</v>
+        <v>69913.804806760221</v>
       </c>
       <c r="BM67" s="4">
         <f t="shared" si="112"/>
-        <v>69361.825545688</v>
+        <v>69214.66675869262</v>
       </c>
       <c r="BN67" s="4">
         <f t="shared" si="112"/>
-        <v>68668.207290231119</v>
+        <v>68522.520091105689</v>
       </c>
       <c r="BO67" s="4">
         <f t="shared" si="112"/>
-        <v>67981.525217328803</v>
+        <v>67837.294890194637</v>
       </c>
       <c r="BP67" s="4">
         <f t="shared" si="112"/>
-        <v>67301.709965155518</v>
+        <v>67158.92194129269</v>
       </c>
       <c r="BQ67" s="4">
         <f t="shared" si="112"/>
-        <v>66628.692865503966</v>
+        <v>66487.332721879764</v>
       </c>
       <c r="BR67" s="4">
         <f t="shared" si="112"/>
-        <v>65962.405936848925</v>
+        <v>65822.459394660968</v>
       </c>
       <c r="BS67" s="4">
         <f t="shared" si="112"/>
-        <v>65302.781877480433</v>
+        <v>65164.234800714359</v>
       </c>
       <c r="BT67" s="4">
         <f t="shared" si="112"/>
-        <v>64649.754058705628</v>
+        <v>64512.592452707213</v>
       </c>
       <c r="BU67" s="4">
         <f t="shared" si="112"/>
-        <v>64003.256518118571</v>
+        <v>63867.466528180143</v>
       </c>
       <c r="BV67" s="4">
         <f t="shared" si="112"/>
-        <v>63363.223952937384</v>
+        <v>63228.791862898339</v>
       </c>
       <c r="BW67" s="4">
         <f t="shared" si="112"/>
-        <v>62729.591713408008</v>
+        <v>62596.503944269352</v>
       </c>
       <c r="BX67" s="4">
         <f t="shared" si="112"/>
-        <v>62102.295796273931</v>
+        <v>61970.538904826659</v>
       </c>
       <c r="BY67" s="4">
         <f t="shared" si="112"/>
-        <v>61481.27283831119</v>
+        <v>61350.833515778395</v>
       </c>
       <c r="BZ67" s="4">
         <f t="shared" si="112"/>
-        <v>60866.460109928077</v>
+        <v>60737.32518062061</v>
       </c>
       <c r="CA67" s="4">
         <f t="shared" si="112"/>
-        <v>60257.795508828793</v>
+        <v>60129.9519288144</v>
       </c>
       <c r="CB67" s="4">
         <f t="shared" si="112"/>
-        <v>59655.217553740506</v>
+        <v>59528.652409526258</v>
       </c>
       <c r="CC67" s="4">
         <f t="shared" si="112"/>
-        <v>59058.665378203099</v>
+        <v>58933.365885430998</v>
       </c>
       <c r="CD67" s="4">
         <f t="shared" si="112"/>
-        <v>58468.078724421066</v>
+        <v>58344.032226576688</v>
       </c>
       <c r="CE67" s="4">
         <f t="shared" si="112"/>
-        <v>57883.397937176858</v>
+        <v>57760.591904310924</v>
       </c>
       <c r="CF67" s="4">
         <f t="shared" si="112"/>
-        <v>57304.56395780509</v>
+        <v>57182.985985267813</v>
       </c>
       <c r="CG67" s="4">
         <f t="shared" si="112"/>
-        <v>56731.518318227041</v>
+        <v>56611.156125415131</v>
       </c>
       <c r="CH67" s="4">
         <f t="shared" si="112"/>
-        <v>56164.203135044772</v>
+        <v>56045.044564160977</v>
       </c>
       <c r="CI67" s="4">
         <f t="shared" si="112"/>
-        <v>55602.561103694323</v>
+        <v>55484.594118519366</v>
       </c>
       <c r="CJ67" s="4">
         <f t="shared" si="112"/>
-        <v>55046.535492657378</v>
+        <v>54929.748177334171</v>
       </c>
       <c r="CK67" s="4">
         <f t="shared" si="112"/>
-        <v>54496.070137730807</v>
+        <v>54380.45069556083</v>
       </c>
       <c r="CL67" s="4">
         <f t="shared" si="112"/>
-        <v>53951.109436353501</v>
+        <v>53836.64618860522</v>
       </c>
       <c r="CM67" s="4">
         <f t="shared" si="112"/>
-        <v>53411.598341989964</v>
+        <v>53298.279726719171</v>
       </c>
       <c r="CN67" s="4">
         <f t="shared" si="112"/>
-        <v>52877.482358570065</v>
+        <v>52765.296929451979</v>
       </c>
       <c r="CO67" s="4">
         <f t="shared" si="112"/>
-        <v>52348.707534984365</v>
+        <v>52237.64396015746</v>
       </c>
       <c r="CP67" s="4">
         <f t="shared" si="112"/>
-        <v>51825.220459634518</v>
+        <v>51715.267520555884</v>
       </c>
       <c r="CQ67" s="4">
         <f t="shared" ref="CQ67:DI67" si="113">CP67*(1+$BL$78)</f>
-        <v>51306.968255038169</v>
+        <v>51198.114845350327</v>
       </c>
       <c r="CR67" s="4">
         <f t="shared" si="113"/>
-        <v>50793.898572487786</v>
+        <v>50686.133696896824</v>
       </c>
       <c r="CS67" s="4">
         <f t="shared" si="113"/>
-        <v>50285.95958676291</v>
+        <v>50179.272359927854</v>
       </c>
       <c r="CT67" s="4">
         <f t="shared" si="113"/>
-        <v>49783.09999089528</v>
+        <v>49677.479636328579</v>
       </c>
       <c r="CU67" s="4">
         <f t="shared" si="113"/>
-        <v>49285.268990986326</v>
+        <v>49180.704839965292</v>
       </c>
       <c r="CV67" s="4">
         <f t="shared" si="113"/>
-        <v>48792.416301076461</v>
+        <v>48688.897791565636</v>
       </c>
       <c r="CW67" s="4">
         <f t="shared" si="113"/>
-        <v>48304.492138065696</v>
+        <v>48202.008813649976</v>
       </c>
       <c r="CX67" s="4">
         <f t="shared" si="113"/>
-        <v>47821.447216685039</v>
+        <v>47719.988725513474</v>
       </c>
       <c r="CY67" s="4">
         <f t="shared" si="113"/>
-        <v>47343.232744518187</v>
+        <v>47242.788838258341</v>
       </c>
       <c r="CZ67" s="4">
         <f t="shared" si="113"/>
-        <v>46869.800417073006</v>
+        <v>46770.360949875758</v>
       </c>
       <c r="DA67" s="4">
         <f t="shared" si="113"/>
-        <v>46401.102412902277</v>
+        <v>46302.657340377002</v>
       </c>
       <c r="DB67" s="4">
         <f t="shared" si="113"/>
-        <v>45937.091388773253</v>
+        <v>45839.630766973234</v>
       </c>
       <c r="DC67" s="4">
         <f t="shared" si="113"/>
-        <v>45477.720474885522</v>
+        <v>45381.234459303501</v>
       </c>
       <c r="DD67" s="4">
         <f t="shared" si="113"/>
-        <v>45022.943270136668</v>
+        <v>44927.422114710469</v>
       </c>
       <c r="DE67" s="4">
         <f t="shared" si="113"/>
-        <v>44572.713837435302</v>
+        <v>44478.147893563364</v>
       </c>
       <c r="DF67" s="4">
         <f t="shared" si="113"/>
-        <v>44126.986699060952</v>
+        <v>44033.36641462773</v>
       </c>
       <c r="DG67" s="4">
         <f t="shared" si="113"/>
-        <v>43685.716832070342</v>
+        <v>43593.032750481449</v>
       </c>
       <c r="DH67" s="4">
         <f t="shared" si="113"/>
-        <v>43248.859663749638</v>
+        <v>43157.102422976634</v>
       </c>
       <c r="DI67" s="4">
         <f t="shared" si="113"/>
-        <v>42816.371067112144</v>
+        <v>42725.531398746869</v>
       </c>
     </row>
     <row r="68" spans="2:113" x14ac:dyDescent="0.2">
@@ -7994,7 +8060,7 @@
         <v>0.96049596309111884</v>
       </c>
       <c r="V68" s="3">
-        <f t="shared" ref="V68:AI68" si="121">V67/V69</f>
+        <f t="shared" ref="V68:AJ68" si="121">V67/V69</f>
         <v>0.99936617689426632</v>
       </c>
       <c r="W68" s="3">
@@ -8049,7 +8115,10 @@
         <f t="shared" si="121"/>
         <v>0.14795285359801488</v>
       </c>
-      <c r="AJ68" s="3"/>
+      <c r="AJ68" s="3">
+        <f>AJ67/AJ69</f>
+        <v>0.34414581402533212</v>
+      </c>
       <c r="AK68" s="3"/>
       <c r="AL68" s="3"/>
       <c r="AX68" s="19">
@@ -8070,39 +8139,39 @@
       </c>
       <c r="BB68" s="19">
         <f t="shared" si="122"/>
-        <v>3.826660585118975</v>
+        <v>3.8059652968585103</v>
       </c>
       <c r="BC68" s="19">
         <f t="shared" si="122"/>
-        <v>5.9005761041243598</v>
+        <v>5.8601085429291953</v>
       </c>
       <c r="BD68" s="19">
         <f t="shared" si="122"/>
-        <v>8.2982495177591495</v>
+        <v>8.1871151417135604</v>
       </c>
       <c r="BE68" s="19">
         <f t="shared" si="122"/>
-        <v>10.844097344657598</v>
+        <v>10.61717390110767</v>
       </c>
       <c r="BF68" s="19">
         <f t="shared" ref="BF68:BJ68" si="123">+BF67/BF69</f>
-        <v>12.606367672990165</v>
+        <v>12.572433916120817</v>
       </c>
       <c r="BG68" s="19">
         <f t="shared" si="123"/>
-        <v>14.592974309158242</v>
+        <v>14.556156182955002</v>
       </c>
       <c r="BH68" s="19">
         <f t="shared" si="123"/>
-        <v>16.829262504467991</v>
+        <v>16.789314837537479</v>
       </c>
       <c r="BI68" s="19">
         <f t="shared" si="123"/>
-        <v>19.343249119323097</v>
+        <v>19.299905900703489</v>
       </c>
       <c r="BJ68" s="19">
         <f t="shared" si="123"/>
-        <v>22.165891962028713</v>
+        <v>22.118864569826435</v>
       </c>
     </row>
     <row r="69" spans="2:113" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -8207,7 +8276,9 @@
       <c r="AI69" s="5">
         <v>3224</v>
       </c>
-      <c r="AJ69" s="5"/>
+      <c r="AJ69" s="5">
+        <v>3237</v>
+      </c>
       <c r="AK69" s="5"/>
       <c r="AL69" s="5"/>
       <c r="AX69" s="4">
@@ -8322,7 +8393,7 @@
         <v>0.39999999999999991</v>
       </c>
       <c r="W71" s="21">
-        <f t="shared" ref="W71:AI71" si="137">W51/S51-1</f>
+        <f t="shared" ref="W71:AJ71" si="137">W51/S51-1</f>
         <v>0.24381531243335464</v>
       </c>
       <c r="X71" s="21">
@@ -8373,7 +8444,10 @@
         <f t="shared" si="137"/>
         <v>0.15784846133953967</v>
       </c>
-      <c r="AJ71" s="21"/>
+      <c r="AJ71" s="21">
+        <f t="shared" si="137"/>
+        <v>0.25515647226173543</v>
+      </c>
       <c r="AK71" s="21"/>
       <c r="AL71" s="21"/>
       <c r="AO71" s="24">
@@ -8430,23 +8504,23 @@
       </c>
       <c r="BB71" s="24">
         <f t="shared" si="139"/>
-        <v>0.24378446532674292</v>
+        <v>0.23971203851343525</v>
       </c>
       <c r="BC71" s="24">
         <f t="shared" si="139"/>
-        <v>0.24313159070107093</v>
+        <v>0.24133816871298608</v>
       </c>
       <c r="BD71" s="24">
         <f t="shared" ref="BD71:BE71" si="140">+BD51/BC51-1</f>
-        <v>0.19716426743993209</v>
+        <v>0.19041500059877481</v>
       </c>
       <c r="BE71" s="24">
         <f t="shared" si="140"/>
-        <v>0.14687860251881468</v>
+        <v>0.13877569687128788</v>
       </c>
       <c r="BF71" s="24">
         <f t="shared" ref="BF71" si="141">+BF51/BE51-1</f>
-        <v>8.189000823371706E-2</v>
+        <v>0.10095363100813581</v>
       </c>
       <c r="BG71" s="24">
         <f t="shared" ref="BG71" si="142">+BG51/BF51-1</f>
@@ -8470,7 +8544,7 @@
         <v>89</v>
       </c>
       <c r="K72" s="16">
-        <f t="shared" ref="K72:AI72" si="145">+K37/G37-1</f>
+        <f t="shared" ref="K72:AJ72" si="145">+K37/G37-1</f>
         <v>0.40427490122026688</v>
       </c>
       <c r="L72" s="16">
@@ -8569,7 +8643,10 @@
         <f t="shared" si="145"/>
         <v>6.3389380452119282E-2</v>
       </c>
-      <c r="AJ72" s="16"/>
+      <c r="AJ72" s="16">
+        <f t="shared" si="145"/>
+        <v>0.24993101150155428</v>
+      </c>
       <c r="AK72" s="16"/>
       <c r="AL72" s="16"/>
       <c r="AU72" s="25">
@@ -8602,23 +8679,23 @@
       </c>
       <c r="BB72" s="25">
         <f t="shared" si="146"/>
-        <v>0.14867421266646974</v>
+        <v>4.2465531928995048E-2</v>
       </c>
       <c r="BC72" s="25">
         <f t="shared" si="146"/>
-        <v>0.16911212812596532</v>
+        <v>0.13198795550508402</v>
       </c>
       <c r="BD72" s="25">
         <f t="shared" si="146"/>
-        <v>0.28481713304504841</v>
+        <v>0.14540892780972503</v>
       </c>
       <c r="BE72" s="25">
         <f t="shared" si="146"/>
-        <v>0.24761598443127775</v>
+        <v>0.11976886480408666</v>
       </c>
       <c r="BF72" s="25">
         <f t="shared" ref="BF72:BI72" si="147">+BF37/BE37-1</f>
-        <v>5.0000000000000044E-2</v>
+        <v>0.49338616613704378</v>
       </c>
       <c r="BG72" s="25">
         <f t="shared" si="147"/>
@@ -8642,7 +8719,7 @@
         <v>90</v>
       </c>
       <c r="K73" s="16">
-        <f t="shared" ref="K73:AI73" si="148">+K42/G42-1</f>
+        <f t="shared" ref="K73:AJ73" si="148">+K42/G42-1</f>
         <v>0.33101713811610356</v>
       </c>
       <c r="L73" s="16">
@@ -8741,7 +8818,10 @@
         <f t="shared" si="148"/>
         <v>0.12622478386167146</v>
       </c>
-      <c r="AJ73" s="16"/>
+      <c r="AJ73" s="16">
+        <f t="shared" si="148"/>
+        <v>0.10119343610144216</v>
+      </c>
       <c r="AK73" s="16"/>
       <c r="AL73" s="16"/>
       <c r="AU73" s="25">
@@ -8874,7 +8954,7 @@
         <v>4.4813044700590332E-2</v>
       </c>
       <c r="Z74" s="16">
-        <f t="shared" ref="Z74:AI74" si="157">Z45/V45-1</f>
+        <f t="shared" ref="Z74:AJ74" si="157">Z45/V45-1</f>
         <v>-1.9253624910862799E-2</v>
       </c>
       <c r="AA74" s="16">
@@ -8913,7 +8993,10 @@
         <f t="shared" si="157"/>
         <v>0.19713733075435202</v>
       </c>
-      <c r="AJ74" s="16"/>
+      <c r="AJ74" s="16">
+        <f t="shared" si="157"/>
+        <v>0.26724520174827382</v>
+      </c>
       <c r="AK74" s="16"/>
       <c r="AL74" s="16"/>
     </row>
@@ -9038,10 +9121,13 @@
         <v>0.39289552238805969</v>
       </c>
       <c r="AI75" s="16">
-        <f t="shared" ref="AI75" si="165">AI53/AI45</f>
+        <f t="shared" ref="AI75:AJ75" si="165">AI53/AI45</f>
         <v>0.18464421896206296</v>
       </c>
-      <c r="AJ75" s="16"/>
+      <c r="AJ75" s="16">
+        <f t="shared" si="165"/>
+        <v>0.15695291412576226</v>
+      </c>
       <c r="AK75" s="16"/>
       <c r="AL75" s="16"/>
       <c r="AU75" s="16">
@@ -9189,10 +9275,13 @@
         <v>0.20115658005702583</v>
       </c>
       <c r="AI76" s="16">
-        <f t="shared" ref="AI76" si="173">+AI59/AI51</f>
+        <f t="shared" ref="AI76:AJ76" si="173">+AI59/AI51</f>
         <v>0.21083664626792334</v>
       </c>
-      <c r="AJ76" s="16"/>
+      <c r="AJ76" s="16">
+        <f t="shared" si="173"/>
+        <v>0.16826037682391273</v>
+      </c>
       <c r="AK76" s="16"/>
       <c r="AL76" s="16"/>
       <c r="AU76" s="16">
@@ -9225,19 +9314,19 @@
       </c>
       <c r="BB76" s="16">
         <f t="shared" si="174"/>
-        <v>0.21999999999999997</v>
+        <v>0.22</v>
       </c>
       <c r="BC76" s="16">
         <f t="shared" si="174"/>
-        <v>0.23000000000000004</v>
+        <v>0.22999999999999998</v>
       </c>
       <c r="BD76" s="16">
         <f t="shared" si="174"/>
-        <v>0.24</v>
+        <v>0.23999999999999996</v>
       </c>
       <c r="BE76" s="16">
         <f t="shared" si="174"/>
-        <v>0.25</v>
+        <v>0.24999999999999997</v>
       </c>
       <c r="BF76" s="16">
         <f t="shared" si="174"/>
@@ -9467,7 +9556,7 @@
       </c>
       <c r="BL80" s="4">
         <f>NPV(BL79,AZ67:DJ67)+Main!K5-Main!K6</f>
-        <v>579383.90996205888</v>
+        <v>576168.60932272719</v>
       </c>
     </row>
     <row r="81" spans="2:64" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -9620,7 +9709,7 @@
       </c>
       <c r="BL82" s="19">
         <f>BL80/Main!K3</f>
-        <v>154.26690828785343</v>
+        <v>177.99462753250762</v>
       </c>
     </row>
     <row r="83" spans="2:64" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -10418,39 +10507,39 @@
       </c>
       <c r="BB94" s="4">
         <f t="shared" si="185"/>
-        <v>55500.240720403555</v>
+        <v>55433.498415763555</v>
       </c>
       <c r="BC94" s="4">
         <f t="shared" si="185"/>
-        <v>74529.598656204616</v>
+        <v>74332.348466710217</v>
       </c>
       <c r="BD94" s="4">
         <f t="shared" si="185"/>
-        <v>101291.45335097787</v>
+        <v>100735.79479873645</v>
       </c>
       <c r="BE94" s="4">
         <f t="shared" si="185"/>
-        <v>136263.66728749863</v>
+        <v>134976.18062980869</v>
       </c>
       <c r="BF94" s="4">
         <f t="shared" ref="BF94" si="186">BE94+BF67</f>
-        <v>176919.20303289191</v>
+        <v>175522.28000929832</v>
       </c>
       <c r="BG94" s="4">
         <f t="shared" ref="BG94" si="187">BF94+BG67</f>
-        <v>223981.54517992723</v>
+        <v>222465.8836993282</v>
       </c>
       <c r="BH94" s="4">
         <f t="shared" ref="BH94" si="188">BG94+BH67</f>
-        <v>278255.91675683646</v>
+        <v>276611.42405038659</v>
       </c>
       <c r="BI94" s="4">
         <f t="shared" ref="BI94" si="189">BH94+BI67</f>
-        <v>340637.89516665344</v>
+        <v>338853.62058015534</v>
       </c>
       <c r="BJ94" s="4">
         <f t="shared" ref="BJ94" si="190">BI94+BJ67</f>
-        <v>412122.89674419607</v>
+        <v>410186.95881784562</v>
       </c>
     </row>
     <row r="95" spans="2:64" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -11457,19 +11546,19 @@
       </c>
       <c r="BB118" s="4">
         <f t="shared" si="193"/>
-        <v>3860.0812799999999</v>
+        <v>3503.17056</v>
       </c>
       <c r="BC118" s="4">
         <f t="shared" si="193"/>
-        <v>5265.0124800000003</v>
+        <v>4626.4713600000005</v>
       </c>
       <c r="BD118" s="4">
         <f t="shared" si="193"/>
-        <v>7730.9465600000003</v>
+        <v>6056.2304000000004</v>
       </c>
       <c r="BE118" s="4">
         <f t="shared" si="193"/>
-        <v>10850.909065919999</v>
+        <v>7629.2755199999992</v>
       </c>
       <c r="BF118" s="4">
         <f t="shared" ref="BF118:BJ118" si="194">+BF37*BF123*8/1000</f>
@@ -11543,19 +11632,19 @@
       </c>
       <c r="BB121" s="4">
         <f t="shared" si="195"/>
-        <v>482.51015999999998</v>
+        <v>437.89632</v>
       </c>
       <c r="BC121" s="4">
         <f t="shared" si="195"/>
-        <v>658.12656000000004</v>
+        <v>578.30892000000006</v>
       </c>
       <c r="BD121" s="4">
         <f t="shared" si="195"/>
-        <v>966.36832000000004</v>
+        <v>757.02880000000005</v>
       </c>
       <c r="BE121" s="4">
         <f t="shared" si="195"/>
-        <v>1356.3636332399999</v>
+        <v>953.6594399999999</v>
       </c>
       <c r="BF121" s="4">
         <f t="shared" ref="BF121:BJ121" si="196">+BF118/8</f>
